--- a/docs/product/Pumdoki_MasterTracker_V4.xlsx
+++ b/docs/product/Pumdoki_MasterTracker_V4.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R6421955959de4969"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" r:id="R20d0c0fdfeb14b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" r:id="R4cd1a1055c6f4d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Assumptions" sheetId="4" r:id="R076da55cc33d442b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💸 Expense Tracker" sheetId="5" r:id="R1e27f58481f74e43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Overview 2026-08-16" sheetId="6" r:id="R29640443d6f442fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="7" r:id="R87000df78c0e4744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="8" r:id="Rd8f3a2a75f5648fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Tracker" sheetId="9" r:id="R0593aec6001b46a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Blocker Queue" sheetId="10" r:id="R00052de970b041f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="11" r:id="R4e9f5169e21d4e63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Register" sheetId="12" r:id="R543c9fb70a2d4cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Budget" sheetId="13" r:id="R0d00416ae27b4ce4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R463b69d9d498496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" r:id="R723d300d33c6492f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" r:id="Re3e41bcb8c174859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Assumptions" sheetId="4" r:id="Rc9c5c67bfc244714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💸 Expense Tracker" sheetId="5" r:id="R10f5e7b319bc4d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Overview 2026-08-16" sheetId="6" r:id="R5cba30f21af54714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="7" r:id="R821888b8c9da4f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="8" r:id="Rb66976c9c95344fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Tracker" sheetId="9" r:id="Refbf8927fd154fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Blocker Queue" sheetId="10" r:id="Rbf04dc1fb8054323"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="11" r:id="R6298a8167dd44592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Register" sheetId="12" r:id="R7c354f8b579a4c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Budget" sheetId="13" r:id="R7443d5d0881e4ea1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4678,7 +4678,7 @@
         <x:v>Latest merge</x:v>
       </x:c>
       <x:c r="H38" s="111" t="str">
-        <x:v>Slice 3: PR #15; Slice 4 reconciliation in HANDOFF.md</x:v>
+        <x:v>Slice 3: PR #15; Slice 4: PR #17 merged in dev 56cb0ad</x:v>
       </x:c>
       <x:c r="I38" s="111" t="str">
         <x:v>Next founder task</x:v>
@@ -5821,23 +5821,23 @@
         <x:v>Truthful prototype copy</x:v>
       </x:c>
       <x:c r="E5" s="111" t="str">
-        <x:v>Publish verified legal UI cleanup</x:v>
+        <x:v>Release verified legal UI cleanup</x:v>
       </x:c>
       <x:c r="F5" s="111" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Deferred</x:v>
       </x:c>
       <x:c r="G5" s="111" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="H5" s="111" t="str">
-        <x:v>Publication checks</x:v>
+        <x:v>Approved website release</x:v>
       </x:c>
       <x:c r="I5" s="111" t="str">
-        <x:v>Local cleanup verified: web219/contracts24/non-database API273 and builds passed. See HANDOFF.md for release proof; final counsel copy remains future work.</x:v>
+        <x:v>Cleanup source is pushed to dev in 56cb0ad. Deploy in an approved website release; final counsel policies and actual processes remain future work. CI/main evidence is in HANDOFF.md.</x:v>
       </x:c>
       <x:c r="J5" s="112"/>
       <x:c r="K5" s="111" t="str">
-        <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md</x:v>
+        <x:v>https://github.com/QK-Connoisseur/PDoki/commit/56cb0adaffa4896aa9d54257b4eecfe18804bb54</x:v>
       </x:c>
       <x:c r="L5" s="112" t="n">
         <x:v>46271.666666666664</x:v>
@@ -5857,19 +5857,17 @@
         <x:v>Branch reconciliation</x:v>
       </x:c>
       <x:c r="E6" s="111" t="str">
-        <x:v>Publish locally integrated Slice 4 source</x:v>
+        <x:v>Slice 4 source published to dev</x:v>
       </x:c>
       <x:c r="F6" s="111" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="G6" s="111" t="str">
         <x:v>Engineering</x:v>
       </x:c>
-      <x:c r="H6" s="111" t="str">
-        <x:v>Publication checks</x:v>
-      </x:c>
+      <x:c r="H6" s="111"/>
       <x:c r="I6" s="111" t="str">
-        <x:v>PR17 source25057bd integrated locally with317abda ancestry. Original CI33337682290 green; final current-head publication checks recorded in HANDOFF.md.</x:v>
+        <x:v>PR #17 merged through dev 56cb0ad, preserving 317abda/25057bd ancestry. Final CI and main-publication evidence is in HANDOFF.md; no deployment or operations activation is implied.</x:v>
       </x:c>
       <x:c r="J6" s="112"/>
       <x:c r="K6" s="111" t="str">
@@ -5959,7 +5957,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6bac1ca91f24b1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279de878b6de4fc5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7057,7 +7055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e632e6626a8499c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0ebf8501b84402"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7529,7 +7527,7 @@
         <x:v>Slice 3 merged in PR #15. Provider-neutral dormant foundation exists; no operational provider/session/hosting activation. G1–G12 remain NOT EVALUATED.</x:v>
       </x:c>
       <x:c r="H16" s="111" t="str">
-        <x:v>Park additional operations work while founder completes the initial business definition. Confirm current Slice 4 integration in HANDOFF.md; production activation stays separately evaluated.</x:v>
+        <x:v>Park additional operations work while founder completes the initial business definition. Slice 4 source is pushed to dev in 56cb0ad and PR #17 is merged. Final CI/main evidence is in HANDOFF.md; activation remains separate.</x:v>
       </x:c>
       <x:c r="I16" s="111" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/pull/15</x:v>
@@ -7858,13 +7856,13 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="G27" s="173" t="str">
-        <x:v>Truthful prototype legal cleanup complete locally; web219, contracts24 and non-database API273 tests and builds passed. Production policies and processes remain unfinished.</x:v>
+        <x:v>Truthful prototype legal cleanup is pushed to dev in 56cb0ad. Local web219, contracts24, non-database API273 and builds passed. Production policies and processes remain unfinished.</x:v>
       </x:c>
       <x:c r="H27" s="173" t="str">
         <x:v>Ship truthful placeholder copy with the next approved website release. Before public launch, counsel approves final policies and operators verify actual contacts/processes; deployment is separate from a Git merge.</x:v>
       </x:c>
       <x:c r="I27" s="173" t="str">
-        <x:v>September 6, 2026 local verification; HANDOFF.md for publication evidence</x:v>
+        <x:v>https://github.com/QK-Connoisseur/PDoki/commit/56cb0adaffa4896aa9d54257b4eecfe18804bb54</x:v>
       </x:c>
       <x:c r="J27" s="174" t="n">
         <x:v>46271.666666666664</x:v>
@@ -7894,7 +7892,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6baf1d96d7624d96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbae23f22bfbd44ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18964,7 +18962,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra367d6caad5d49e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f8bb2389d85457d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26662,7 +26660,7 @@
       </x:c>
       <x:c r="N149" s="112"/>
       <x:c r="O149" s="111" t="str">
-        <x:v>HANDOFF.md — September 6, 2026: web219/contracts24/non-database API273 and builds passed</x:v>
+        <x:v>https://github.com/QK-Connoisseur/PDoki/commit/56cb0adaffa4896aa9d54257b4eecfe18804bb54</x:v>
       </x:c>
       <x:c r="P149" s="112" t="n">
         <x:v>46271.666666666664</x:v>
@@ -26671,7 +26669,7 @@
         <x:v>Replace unconfigured production-looking emails with .example sample addresses until real domains and mailboxes are operational.</x:v>
       </x:c>
       <x:c r="R149" s="111" t="str">
-        <x:v>Prototype legal claims and unconfigured production-looking contacts corrected locally. Source integration does not deploy the website or establish final operating policies.</x:v>
+        <x:v>Prototype legal claims and unconfigured production-looking contacts corrected and pushed to dev in 56cb0ad. Final CI/main publication evidence is in HANDOFF.md. A source merge does not deploy the website or establish final policies.</x:v>
       </x:c>
       <x:c r="S149" s="111" t="str">
         <x:v>Preserved Master Tracker row 162; legacy status: 📋 Not Started</x:v>
@@ -27529,7 +27527,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a16687151ed4743"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79e8f6906de846af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/product/Pumdoki_MasterTracker_V4.xlsx
+++ b/docs/product/Pumdoki_MasterTracker_V4.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R463b69d9d498496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" r:id="R723d300d33c6492f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" r:id="Re3e41bcb8c174859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Assumptions" sheetId="4" r:id="Rc9c5c67bfc244714"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💸 Expense Tracker" sheetId="5" r:id="R10f5e7b319bc4d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Overview 2026-08-16" sheetId="6" r:id="R5cba30f21af54714"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="7" r:id="R821888b8c9da4f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="8" r:id="Rb66976c9c95344fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Tracker" sheetId="9" r:id="Refbf8927fd154fb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Blocker Queue" sheetId="10" r:id="Rbf04dc1fb8054323"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="11" r:id="R6298a8167dd44592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Register" sheetId="12" r:id="R7c354f8b579a4c9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Budget" sheetId="13" r:id="R7443d5d0881e4ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7795711c1c2c4fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" r:id="R2044898aa65d4e38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" r:id="R404a5f97f40147d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Assumptions" sheetId="4" r:id="Rb807e3ab990a40b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💸 Expense Tracker" sheetId="5" r:id="R7bfc52ffe2bc40f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Overview 2026-08-16" sheetId="6" r:id="R9494421699b1422d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="7" r:id="R362a974d66b74322"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="8" r:id="R8c78190525054a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Tracker" sheetId="9" r:id="R778bb3c34800408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Blocker Queue" sheetId="10" r:id="Rd242103954474179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="11" r:id="R429c6bd7ab0245a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Register" sheetId="12" r:id="R8635ba7f128346ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Budget" sheetId="13" r:id="Rd60094f2100c445e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3379,7 +3379,7 @@
     </x:row>
     <x:row r="2" ht="21.75" customHeight="1">
       <x:c r="A2" s="92" t="str">
-        <x:v>Refreshed September 6, 2026. Start with the initial business definition. Record counts are navigation metrics, not launch readiness.</x:v>
+        <x:v>Updated September 8, 2026. Founder reports LLC filed and CCBill sales inquiry sent. Await responses. Record counts are navigation metrics, not launch readiness.</x:v>
       </x:c>
       <x:c r="B2" s="92"/>
       <x:c r="C2" s="92"/>
@@ -3421,12 +3421,12 @@
         <x:v>Phase</x:v>
       </x:c>
       <x:c r="B5" s="109" t="str">
-        <x:v>P00 — Initial business definition</x:v>
+        <x:v>P06 — Await CCBill sales response</x:v>
       </x:c>
       <x:c r="D5"/>
       <x:c r="E5"/>
       <x:c r="I5" s="130" t="str">
-        <x:v>Complete the one-page initial business definition. This is the only founder assignment now; no purchase is required.</x:v>
+        <x:v>Founder reports Kiban Digital Holdings LLC filed in Maryland and preliminary inquiry sent to CCBill sales. Await state approval and sales response. Next: share and review the response when received. No duplicate inquiry or new founder assignment.</x:v>
       </x:c>
       <x:c r="J5" s="130"/>
       <x:c r="K5" s="130"/>
@@ -3439,7 +3439,7 @@
         <x:v>Work</x:v>
       </x:c>
       <x:c r="B6" s="111" t="str">
-        <x:v>Founder definition and current instruction reconciliation</x:v>
+        <x:v>Await Maryland and CCBill responses</x:v>
       </x:c>
       <x:c r="D6"/>
       <x:c r="E6"/>
@@ -3486,7 +3486,7 @@
         <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md</x:v>
       </x:c>
       <x:c r="I9" s="131" t="str">
-        <x:v>Use Launch Budget for current funding. $1,000–$5,000 is available now; another $5,000 is possible and uncommitted. Local CI or a Git merge does not establish launch readiness or deploy the site.</x:v>
+        <x:v>Funding notes: founder reports a $1,800 monthly ceiling; this is not lump-sum cash or funded runway. Existing $1,000–$5,000 cash assumptions remain until clarified. See Launch Budget.</x:v>
       </x:c>
       <x:c r="J9" s="131"/>
       <x:c r="K9" s="131"/>
@@ -3556,7 +3556,7 @@
       <x:c r="D13" s="151"/>
       <x:c r="E13" s="150" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F13" s="151"/>
       <x:c r="G13" s="150" t="n">
@@ -3571,7 +3571,7 @@
       <x:c r="J13" s="151"/>
       <x:c r="K13" s="150" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="L13" s="151"/>
       <x:c r="M13" s="158" t="n">
@@ -3925,7 +3925,7 @@
       </x:c>
       <x:c r="H22" s="111" t="n">
         <x:f>'Phase Roadmap'!H8</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I22" s="111" t="n">
         <x:f>'Phase Roadmap'!I8</x:f>
@@ -3937,11 +3937,11 @@
       </x:c>
       <x:c r="K22" s="111" t="n">
         <x:f>'Phase Roadmap'!K8</x:f>
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L22" s="111" t="str">
         <x:f>'Phase Roadmap'!L8</x:f>
-        <x:v>Slices 1–3 are published, including PR #15. The private router remains dormant. Founder business definition is the next active task.</x:v>
+        <x:v>Slices 1–4 have published source; operations remain dormant. Founder reports Maryland LLC filed and CCBill inquiry sent. Await approval/response; review what arrives before another founder task.</x:v>
       </x:c>
       <x:c r="M22" s="111" t="str">
         <x:f>'Phase Roadmap'!M8</x:f>
@@ -4347,7 +4347,7 @@
       </x:c>
       <x:c r="L29" s="111" t="str">
         <x:f>'Phase Roadmap'!L15</x:f>
-        <x:v>Slice 3 is published in PR #15. Dormant private-operations foundation remains; further work is parked during founder business definition.</x:v>
+        <x:v>Dormant operations foundation has published source. Further operations work stays parked while Maryland approval and CCBill sales response are pending.</x:v>
       </x:c>
       <x:c r="M29" s="111" t="str">
         <x:f>'Phase Roadmap'!M15</x:f>
@@ -4556,7 +4556,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B35" s="109" t="str">
-        <x:v>Start with the one-page initial business definition; review other decisions only when they become the next step.</x:v>
+        <x:v>LLC filed and CCBill inquiry sent, per founder report. Wait for Maryland approval and CCBill sales response. Review the response when received, then choose one next action.</x:v>
       </x:c>
       <x:c r="C35" s="109" t="str">
         <x:v>2</x:v>
@@ -4684,7 +4684,7 @@
         <x:v>Next founder task</x:v>
       </x:c>
       <x:c r="J38" s="111" t="str">
-        <x:v>Complete the initial business definition.</x:v>
+        <x:v>Share and review Maryland/CCBill responses when received.</x:v>
       </x:c>
       <x:c r="K38" s="111" t="str"/>
       <x:c r="L38" s="111" t="str"/>
@@ -5773,38 +5773,38 @@
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="109" t="str">
-        <x:v>DEC-SEQUENTIAL</x:v>
+        <x:v>DEC-CCBILL</x:v>
       </x:c>
       <x:c r="B4" s="109" t="str">
-        <x:v>P00</x:v>
+        <x:v>P06</x:v>
       </x:c>
       <x:c r="C4" s="109" t="str">
-        <x:v>Baseline, tracker, and scope control</x:v>
+        <x:v>Wallet, payments and payouts</x:v>
       </x:c>
       <x:c r="D4" s="109" t="str">
-        <x:v>Founder definition</x:v>
+        <x:v>Await processor response</x:v>
       </x:c>
       <x:c r="E4" s="109" t="str">
-        <x:v>Complete the one-page initial business definition</x:v>
+        <x:v>Review CCBill response when received</x:v>
       </x:c>
       <x:c r="F4" s="109" t="str">
-        <x:v>Ready</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="G4" s="109" t="str">
         <x:v>Founder</x:v>
       </x:c>
       <x:c r="H4" s="109" t="str">
-        <x:v>Founder</x:v>
+        <x:v>Awaiting CCBill sales response</x:v>
       </x:c>
       <x:c r="I4" s="109" t="str">
-        <x:v>Fill the template. This is the only active founder assignment; $0 spending.</x:v>
+        <x:v>Founder reports CCBill sales inquiry sent and Maryland LLC filed. Wait for sales response and state approval; share/review what arrives before the next founder action. No reply or approval evidenced.</x:v>
       </x:c>
       <x:c r="J4" s="110"/>
       <x:c r="K4" s="109" t="str">
-        <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md</x:v>
+        <x:v>docs/product/initial-ccbill-inquiry.md</x:v>
       </x:c>
       <x:c r="L4" s="110" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
@@ -5957,7 +5957,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279de878b6de4fc5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9807d8f6f37d41c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7055,7 +7055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0ebf8501b84402"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48a368095cad4ec5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7285,7 +7285,7 @@
         <x:v>Local Mailpit and provider-neutral mail exist. Production startup correctly fails closed without approved delivery.</x:v>
       </x:c>
       <x:c r="H8" s="111" t="str">
-        <x:v>Choose email after business definition, counsel/entity and processor fit, country/data boundaries and funded staging scope. Then configure/test verified sender, SPF/DKIM/DMARC, bounce/complaint handling and deliverability before external account flows.</x:v>
+        <x:v>Choose email after entity, processor fit, country/data boundaries and funded staging scope are known. Configure and test sender authentication, bounce handling and delivery before external account flows.</x:v>
       </x:c>
       <x:c r="I8" s="111" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/tree/dev/docs/operations</x:v>
@@ -7302,26 +7302,26 @@
         <x:v>P04</x:v>
       </x:c>
       <x:c r="C9" s="111" t="str">
-        <x:v>LLC attorney/CPA shortlist and entity state</x:v>
+        <x:v>Maryland LLC filed; approval pending</x:v>
       </x:c>
       <x:c r="D9" s="111" t="str">
         <x:v>Founder</x:v>
       </x:c>
-      <x:c r="E9" s="112" t="n">
-        <x:v>46233.666666666664</x:v>
-      </x:c>
+      <x:c r="E9" s="112"/>
       <x:c r="F9" s="111" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="G9" s="111" t="str">
-        <x:v>No entity is filed.</x:v>
+        <x:v>Founder reports Kiban Digital Holdings LLC filed in Maryland through Northwest; state approval pending. Exact filing date, filing ID, EIN, bank account and actual cost have not been supplied.</x:v>
       </x:c>
       <x:c r="H9" s="111" t="str">
-        <x:v>Obtain qualified privacy-focused adult-platform legal and tax advice.</x:v>
-      </x:c>
-      <x:c r="I9" s="111" t="str"/>
+        <x:v>Await Maryland approval and approved formation documents. Record invoice when available. Next founder action is to share and review the received Maryland or CCBill response.</x:v>
+      </x:c>
+      <x:c r="I9" s="111" t="str">
+        <x:v>Founder report, September 8, 2026: LLC filed and CCBill sales inquiry sent. Exact event times, state approval and processor response not supplied.</x:v>
+      </x:c>
       <x:c r="J9" s="112" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="55" customHeight="1">
@@ -7332,26 +7332,26 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C10" s="111" t="str">
-        <x:v>CCBill requirements and fee quote</x:v>
+        <x:v>Preliminary CCBill model fit and costs</x:v>
       </x:c>
       <x:c r="D10" s="111" t="str">
         <x:v>Founder</x:v>
       </x:c>
-      <x:c r="E10" s="112" t="n">
-        <x:v>46233.666666666664</x:v>
-      </x:c>
+      <x:c r="E10" s="112"/>
       <x:c r="F10" s="111" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="G10" s="111" t="str">
-        <x:v>Merchant application and concrete pricing have not started.</x:v>
+        <x:v>Founder reports the preliminary inquiry was sent to CCBill sales. No reply, quote, formal merchant approval or activation is evidenced. Epoch remains a possible later provider.</x:v>
       </x:c>
       <x:c r="H10" s="111" t="str">
-        <x:v>Request the merchant package, technical documents, and complete fee quote.</x:v>
-      </x:c>
-      <x:c r="I10" s="111" t="str"/>
+        <x:v>Await and review the sales response for model eligibility, countries, Veso, creator payouts, complete fees/reserves and required documents. Do not send a duplicate inquiry or assume approval.</x:v>
+      </x:c>
+      <x:c r="I10" s="111" t="str">
+        <x:v>Founder report, September 8, 2026: LLC filed and CCBill sales inquiry sent. Exact event times, state approval and processor response not supplied.</x:v>
+      </x:c>
       <x:c r="J10" s="112" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="55" customHeight="1">
@@ -7434,12 +7434,14 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="G13" s="111" t="str">
-        <x:v>Payment, payout, identity, adult-content law, privacy, tax, sanctions, and support coverage remain open.</x:v>
+        <x:v>Operating location is confirmed as Maryland, USA. Creator/member countries remain unanswered; eligibility and service coverage remain unresolved.</x:v>
       </x:c>
       <x:c r="H13" s="111" t="str">
-        <x:v>Start with the US and only supported Latin American countries after review.</x:v>
-      </x:c>
-      <x:c r="I13" s="111" t="str"/>
+        <x:v>Use CCBill eligibility to narrow proposed creator/member countries. Obtain targeted legal review of unresolved country obligations before real launch.</x:v>
+      </x:c>
+      <x:c r="I13" s="111" t="str">
+        <x:v>docs/product/initial-business-definition.md — founder answers reviewed September 6, 2026</x:v>
+      </x:c>
       <x:c r="J13" s="112" t="n">
         <x:v>46255.666666666664</x:v>
       </x:c>
@@ -7464,12 +7466,14 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="G14" s="111" t="str">
-        <x:v>Veso remains. Proposed founding cohort ~500 pays necessary processing fees only; platform commission duration, fee definition, refunds/reserves, payouts and Plus revenue remain unresolved.</x:v>
+        <x:v>Founder corrected the offer: Pumdoki should recover costs without profit on founding creator sales. Processing-fees-only is superseded. Duration, fee allocation and no-loss economics are unproven.</x:v>
       </x:c>
       <x:c r="H14" s="111" t="str">
-        <x:v>Use written processor terms to model a fees-only cohort. Zero platform commission provides no contribution toward operations before other revenue.</x:v>
-      </x:c>
-      <x:c r="I14" s="111" t="str"/>
+        <x:v>After counsel/processor fit, define attributable costs, refunds, chargebacks, reserves and payout allocation before quoting founder fees. No loss-free promise is supported yet.</x:v>
+      </x:c>
+      <x:c r="I14" s="111" t="str">
+        <x:v>docs/product/initial-business-definition.md — founder answers reviewed September 6, 2026</x:v>
+      </x:c>
       <x:c r="J14" s="112" t="n">
         <x:v>46271.666666666664</x:v>
       </x:c>
@@ -7527,7 +7531,7 @@
         <x:v>Slice 3 merged in PR #15. Provider-neutral dormant foundation exists; no operational provider/session/hosting activation. G1–G12 remain NOT EVALUATED.</x:v>
       </x:c>
       <x:c r="H16" s="111" t="str">
-        <x:v>Park additional operations work while founder completes the initial business definition. Slice 4 source is pushed to dev in 56cb0ad and PR #17 is merged. Final CI/main evidence is in HANDOFF.md; activation remains separate.</x:v>
+        <x:v>Operations work stays parked while awaiting CCBill response. Slice 4 is published; final CI/main evidence is in HANDOFF.md. Deployment and activation remain separate.</x:v>
       </x:c>
       <x:c r="I16" s="111" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/pull/15</x:v>
@@ -7606,26 +7610,26 @@
         <x:v>P00</x:v>
       </x:c>
       <x:c r="C19" s="173" t="str">
-        <x:v>One founder task at a time</x:v>
+        <x:v>Initial business definition and sequential workflow</x:v>
       </x:c>
       <x:c r="D19" s="173" t="str">
         <x:v>Founder</x:v>
       </x:c>
       <x:c r="E19" s="173"/>
       <x:c r="F19" s="173" t="str">
-        <x:v>Ready</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="G19" s="173" t="str">
-        <x:v>Founder has limited time. Work is sequential; no parallel founder assignments.</x:v>
+        <x:v>Business definition answered/reviewed and operating location confirmed as Maryland, USA. Work remains sequential, one founder assignment at a time.</x:v>
       </x:c>
       <x:c r="H19" s="173" t="str">
-        <x:v>Complete the one-page initial business definition next. No purchases required.</x:v>
+        <x:v>Current: await Maryland approval and CCBill sales response. Founder reports filing and inquiry completed. Share/review the response when received, then choose one next action.</x:v>
       </x:c>
       <x:c r="I19" s="173" t="str">
-        <x:v>Founder decision, September 6, 2026</x:v>
+        <x:v>Founder report, September 8, 2026: LLC filed and CCBill sales inquiry sent. Exact event times, state approval and processor response not supplied.</x:v>
       </x:c>
       <x:c r="J19" s="174" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="95" customHeight="1">
@@ -7736,13 +7740,13 @@
         <x:v>In Progress</x:v>
       </x:c>
       <x:c r="G23" s="173" t="str">
-        <x:v>Target around 500 founding creators; necessary processing fees only and founder profile tag. Recruitment relationship via former Epal contact and Discord servers.</x:v>
+        <x:v>Two contacts could help recruit 50–100 creators; these are prospects, not commitments. Founder badge and cost recovery with no profit on founder sales remain the direction. About 500 is a longer target.</x:v>
       </x:c>
       <x:c r="H23" s="173" t="str">
-        <x:v>Define eligibility, number, duration and covered fees. Validate unit economics before making public commitments.</x:v>
+        <x:v>Define first-cohort eligibility, countries, duration and cost allocation after counsel/processor fit. No-loss economics and Plus/top 100 benefits remain unproven.</x:v>
       </x:c>
       <x:c r="I23" s="173" t="str">
-        <x:v>Founder direction, September 6, 2026; commercial terms provisional</x:v>
+        <x:v>docs/product/initial-business-definition.md — founder answers reviewed September 6, 2026</x:v>
       </x:c>
       <x:c r="J23" s="174" t="n">
         <x:v>46271.666666666664</x:v>
@@ -7796,16 +7800,16 @@
         <x:v>In Progress</x:v>
       </x:c>
       <x:c r="G25" s="173" t="str">
-        <x:v>Available now: $1,000–$5,000 total. Another $5,000 may become available over coming months; it is uncommitted. No expense was recorded as paid.</x:v>
+        <x:v>Founder now reports a $1,800 monthly ceiling and proposed recruiter/helper $300–$400/month. Inclusion in that ceiling and overlap with budget backup allowance are unconfirmed. Earlier cash assumptions remain.</x:v>
       </x:c>
       <x:c r="H25" s="173" t="str">
-        <x:v>Use Launch Budget. First step costs $0; seek and approve one scoped quote at a time after the definition.</x:v>
+        <x:v>Keep cost allowances until actual quotes/invoices support changes. LLC filing is reported but amount/payment details were not supplied; actual cost remains blank. Monthly funding and helper overlap remain unresolved.</x:v>
       </x:c>
       <x:c r="I25" s="173" t="str">
-        <x:v>Founder funding statement, September 6, 2026; docs/product/launch-budget.md</x:v>
+        <x:v>Founder funding statements September 6 and filed-LLC/sent-inquiry report September 8, 2026</x:v>
       </x:c>
       <x:c r="J25" s="174" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="95" customHeight="1">
@@ -7826,16 +7830,16 @@
         <x:v>Ready</x:v>
       </x:c>
       <x:c r="G26" s="173" t="str">
-        <x:v>Fiverr may source technical reviewers. Relevant experience, written scope, findings and a retest matter more than marketplace or low price.</x:v>
+        <x:v>Use DIY work, suitable Fiverr specialists and drafts to control cost. Necessary legal work uses a qualified lawyer reviewing the actual model. Record the reviewed version, corrections and remaining limitations.</x:v>
       </x:c>
       <x:c r="H26" s="173" t="str">
-        <x:v>Counsel discovery after definition; architecture/ledger/entitlement review before money/media design locks; independent integrated review and retest before real users, identity, content or money.</x:v>
+        <x:v>Buy targeted legal advice only for unresolved requirements or necessary document/workflow review. Technical design review precedes fixed money/media designs; independent integrated assessment and retest precede real launch.</x:v>
       </x:c>
       <x:c r="I26" s="173" t="str">
-        <x:v>Founder direction and staged budget, September 6, 2026</x:v>
+        <x:v>Founder instruction, September 8, 2026</x:v>
       </x:c>
       <x:c r="J26" s="174" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="95" customHeight="1">
@@ -7892,7 +7896,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbae23f22bfbd44ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45740b3e98174502"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7917,7 +7921,7 @@
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
       <x:c r="A2" s="177" t="str">
-        <x:v>September 6, 2026</x:v>
+        <x:v>September 8, 2026</x:v>
       </x:c>
       <x:c r="B2" s="179"/>
       <x:c r="C2" s="179"/>
@@ -7956,7 +7960,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="D5" s="177" t="str">
-        <x:v>Founder total cash range, not a monthly allowance.</x:v>
+        <x:v>Earlier total-cash assumption retained. New user-reported $1,800 monthly ceiling is not lump-sum cash or funded runway; sustainability is unconfirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -8121,12 +8125,12 @@
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="177" t="str">
-        <x:v>Next action costs $0</x:v>
+        <x:v>Current: await CCBill response</x:v>
       </x:c>
       <x:c r="B17" s="179"/>
       <x:c r="C17" s="179"/>
       <x:c r="D17" s="177" t="str">
-        <x:v>Complete the initial business definition. Then seek one scoped counsel consultation with a spending cap you approve.</x:v>
+        <x:v>Founder reports Kiban Digital Holdings LLC filed in Maryland and preliminary inquiry sent to CCBill sales. Await state approval and sales response; review what arrives before another founder task.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
@@ -8136,7 +8140,7 @@
       <x:c r="B18" s="179"/>
       <x:c r="C18" s="179"/>
       <x:c r="D18" s="177" t="str">
-        <x:v>25 invited creators, founder runs moderation/support with paid backup allowance. 500 creators is an aspiration, not a day-one staffing or cost assumption.</x:v>
+        <x:v>Pilot counts remain planning assumptions. Two contacts may help recruit 50–100 creators; no committed cohort or creator/member countries were supplied.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="32" customHeight="1">
@@ -8161,7 +8165,7 @@
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
       <x:c r="A21" s="177" t="str">
-        <x:v>Counsel discovery consultation</x:v>
+        <x:v>Targeted legal advice allowance</x:v>
       </x:c>
       <x:c r="B21" s="190" t="n">
         <x:v>300</x:v>
@@ -8170,12 +8174,12 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="D21" s="177" t="str">
-        <x:v>After definition. Adult-platform business, country and Veso fit. Unquoted scoped allowance.</x:v>
+        <x:v>Optional scoped advice for unresolved material issues. DIY/Fiverr drafts first where suitable; use a qualified lawyer when needed. Unquoted allowance unchanged; no legal engagement.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
       <x:c r="A22" s="177" t="str">
-        <x:v>CPA / entity consultation</x:v>
+        <x:v>Targeted tax / accounting advice</x:v>
       </x:c>
       <x:c r="B22" s="190" t="n">
         <x:v>100</x:v>
@@ -8184,12 +8188,12 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="D22" s="177" t="str">
-        <x:v>After counsel direction. Entity, banking, tax and records scope. Unquoted.</x:v>
+        <x:v>Use when a specific tax or accounting question needs professional advice. Founder reports LLC filed; state approval pending. Unquoted allowance unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
       <x:c r="A23" s="200" t="str">
-        <x:v>Discovery subtotal</x:v>
+        <x:v>Initial advice allowances subtotal</x:v>
       </x:c>
       <x:c r="B23" s="201" t="n">
         <x:f>SUM(B21:B22)</x:f>
@@ -8200,7 +8204,7 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="D23" s="200" t="str">
-        <x:v>Do not spend the whole available budget on build work before these answers.</x:v>
+        <x:v>Reserve for necessary questions. This is not a required discovery purchase or a commitment to spend.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -8214,12 +8218,12 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="D24" s="177" t="str">
-        <x:v>Only after advice; jurisdiction and registered-agent/filing costs are unknown. Allowance.</x:v>
+        <x:v>Founder reports Maryland LLC filed through Northwest; state approval pending. Actual invoice and recurring charges not supplied; this allowance is not amount paid.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
       <x:c r="A25" s="177" t="str">
-        <x:v>Adult legal documents / consent</x:v>
+        <x:v>Legal document drafting / review</x:v>
       </x:c>
       <x:c r="B25" s="190" t="n">
         <x:v>2000</x:v>
@@ -8228,7 +8232,7 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="D25" s="177" t="str">
-        <x:v>Before real activity. Qualified adult-platform counsel, usable scope and revisions; unquoted, not a guaranteed market minimum.</x:v>
+        <x:v>Prepare suitable drafts yourself or with Fiverr specialists; qualified adult-platform counsel reviews and corrects necessary final documents/workflows. Unquoted allowance unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -8488,7 +8492,7 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="D44" s="177" t="str">
-        <x:v>Unquoted limited-hours allowance. Founder supplies daily unpaid coverage; define capacity and qualified backup before any real activity. Not 24/7 staffing.</x:v>
+        <x:v>Proposed Discord recruiter/helper: $300–$400/month. Inclusion in $1,800 ceiling and overlap with this $100–$600 backup allowance are unconfirmed; no amount added. Scope/coverage remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="48" customHeight="1">
@@ -8562,7 +8566,7 @@
       <x:c r="B51" s="179"/>
       <x:c r="C51" s="179"/>
       <x:c r="D51" s="177" t="str">
-        <x:v>Fees-only creators yield no platform commission to cover operations. Plus revenue is unproven and excluded. Define duration, necessary fees and who absorbs losses before promising benefits.</x:v>
+        <x:v>Founder correction: recover attributable costs without profit on founding creator sales. Processing-fees-only is superseded. Duration, cost allocation and no-loss economics are unproven; Plus revenue excluded.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="32" customHeight="1">
@@ -8596,7 +8600,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="D54" s="177" t="str">
-        <x:v>Planning assumption; ~500 is the longer recruitment target. Counts are not existing commitments.</x:v>
+        <x:v>Unchanged planning counts. Two contacts could recruit 50–100 prospects, not commitments; ~500 remains the longer target.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="64" customHeight="1">
@@ -8722,7 +8726,7 @@
       <x:c r="B66" s="179"/>
       <x:c r="C66" s="179"/>
       <x:c r="D66" s="177" t="str">
-        <x:v>Planning judgment, September 6, 2026. No lawyer, reviewer, provider or operator has quoted or accepted this scope.</x:v>
+        <x:v>Planning allowances remain unquoted. Founder answers reviewed September 6, 2026 in initial-business-definition.md; new funding/helper statements are notes only, not formula changes.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="64" customHeight="1">
@@ -8742,7 +8746,7 @@
       <x:c r="B68" s="179"/>
       <x:c r="C68" s="179"/>
       <x:c r="D68" s="177" t="str">
-        <x:v>After definition: one counsel discovery quote, then entity/processor fit and cash terms, then funded technical review/design. No paid platform, reward or production commitment implied.</x:v>
+        <x:v>Current: wait for Maryland approval and CCBill sales response, then review the response. DIY/Fiverr and targeted qualified review remain the approach. Costs/formulas unchanged; actual filing expense unknown.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="32" customHeight="1">
@@ -15334,7 +15338,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="13" t="str">
-        <x:v>Historical estimates only. Corrected arithmetic below; use Launch Budget for current planning. No listed amount is confirmed spent.</x:v>
+        <x:v>Historical estimates; use Launch Budget for current planning. Maryland LLC filing reported September 8, 2026; exact filing date and actual invoice amount unverified.</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -15503,10 +15507,8 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LLC Formation (state TBD)</x:t>
-        </x:is>
+      <x:c r="A10" s="41" t="str">
+        <x:v>LLC formation — Maryland / Northwest</x:v>
       </x:c>
       <x:c r="B10" s="21" t="s">
         <x:v>478</x:v>
@@ -15521,13 +15523,11 @@
       <x:c r="F10" s="21" t="s">
         <x:v>470</x:v>
       </x:c>
-      <x:c r="G10" s="24" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="H10" s="43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wyoming is a candidate for privacy/tax evaluation. Confirm state, registered agent, foreign qualification, and total cost with an attorney and CPA before filing.</x:t>
-        </x:is>
+      <x:c r="G10" s="24" t="str">
+        <x:v>Filed</x:v>
+      </x:c>
+      <x:c r="H10" s="43" t="str">
+        <x:v>Founder reports Kiban Digital Holdings LLC filed, awaiting Maryland approval. September 8 is the report date; filing date and payment amount unverified. D10 is historical, not the Northwest price.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -18282,7 +18282,7 @@
       </x:c>
       <x:c r="H8" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I8" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"In Review")</x:f>
@@ -18294,10 +18294,10 @@
       </x:c>
       <x:c r="K8" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L8" s="111" t="str">
-        <x:v>Slices 1–3 are published, including PR #15. The private router remains dormant. Founder business definition is the next active task.</x:v>
+        <x:v>Slices 1–4 have published source; operations remain dormant. Founder reports Maryland LLC filed and CCBill inquiry sent. Await approval/response; review what arrives before another founder task.</x:v>
       </x:c>
       <x:c r="M8" s="111" t="str">
         <x:v>Resolve business/legal/provider prerequisites in sequence. G1–G12 apply to operations activation, not all synthetic local product work.</x:v>
@@ -18696,7 +18696,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="L15" s="111" t="str">
-        <x:v>Slice 3 is published in PR #15. Dormant private-operations foundation remains; further work is parked during founder business definition.</x:v>
+        <x:v>Dormant operations foundation has published source. Further operations work stays parked while Maryland approval and CCBill sales response are pending.</x:v>
       </x:c>
       <x:c r="M15" s="111" t="str">
         <x:v>Evaluate provider, restricted hosting, MFA/recovery, session, permission, audit and deployment controls when activating real operations.</x:v>
@@ -18962,7 +18962,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f8bb2389d85457d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f70c7d9d6084912"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19857,18 +19857,18 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M18" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Review the CCBill sales response for account-specific compliance requirements when received; assemble requested evidence in sequence afterward.</x:v>
       </x:c>
       <x:c r="N18" s="112"/>
       <x:c r="O18" s="111" t="str"/>
       <x:c r="P18" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
       <x:c r="Q18" s="111" t="str">
         <x:v>Document policies/controls required by CCBill and Epoch for merchant onboarding.</x:v>
       </x:c>
       <x:c r="R18" s="111" t="str">
-        <x:v>CCBill/Epoch applications have not started. Assemble the compliance package in parallel with product development.</x:v>
+        <x:v>Founder reports preliminary inquiry sent to CCBill sales. No response, formal merchant application or approval evidenced. Epoch may follow later. Await response before choosing another founder task.</x:v>
       </x:c>
       <x:c r="S18" s="111" t="str">
         <x:v>Preserved Master Tracker row 20; legacy status: 📋 Not Started</x:v>
@@ -20117,21 +20117,21 @@
         <x:v>Founder</x:v>
       </x:c>
       <x:c r="L23" s="111" t="str">
-        <x:v>Counsel / founder decision</x:v>
+        <x:v>Northwest / founder records</x:v>
       </x:c>
       <x:c r="M23" s="111" t="str">
-        <x:v>Close the remaining gap: Entity not filed.</x:v>
+        <x:v>Review the approved filing and published address details when Northwest supplies them; actual state approval remains pending.</x:v>
       </x:c>
       <x:c r="N23" s="112"/>
       <x:c r="O23" s="111" t="str"/>
       <x:c r="P23" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
       <x:c r="Q23" s="111" t="str">
         <x:v>Manage privacy concerns — MD biz records may expose personal identity linked to NSFW platform.</x:v>
       </x:c>
       <x:c r="R23" s="111" t="str">
-        <x:v>Entity not filed. Evaluate Wyoming and other privacy/no-individual-income-tax candidates with an attorney and CPA; account for foreign qualification where the founder operates.</x:v>
+        <x:v>Founder reports Kiban Digital Holdings LLC filed in Maryland through Northwest, awaiting approval. Final published address/privacy details remain unverified. State-comparison task is superseded.</x:v>
       </x:c>
       <x:c r="S23" s="111" t="str">
         <x:v>Preserved Master Tracker row 25; legacy status: 🔄 In Progress</x:v>
@@ -20999,7 +20999,7 @@
       </x:c>
       <x:c r="L40" s="111" t="str"/>
       <x:c r="M40" s="111" t="str">
-        <x:v>Define founding creator tag and fees-only offer with duration, eligibility and necessary fees before publication.</x:v>
+        <x:v>Define founder badge and a fee that recovers attributable costs without profit on founding creator sales. Duration, covered costs and no-loss economics need validation.</x:v>
       </x:c>
       <x:c r="N40" s="112"/>
       <x:c r="O40" s="111" t="str"/>
@@ -21010,7 +21010,7 @@
         <x:v>Define badge visuals, eligibility window (first N users or date window), locked-in fee reduction for Founding Creators, badge display on profiles and posts.</x:v>
       </x:c>
       <x:c r="R40" s="111" t="str">
-        <x:v>September 6, 2026: approximately500 creators is an acquisition target; Plus top100 leaderboard rewards are provisional. No public price/benefit promise yet.</x:v>
+        <x:v>Founder answers reviewed September 6, 2026: processing-fees-only superseded. Two contacts may recruit 50–100 prospects, not commitments. Longer target ~500; Plus/top 100 rewards remain provisional.</x:v>
       </x:c>
       <x:c r="S40" s="111" t="str">
         <x:v>Preserved Master Tracker row 43; legacy status: 📋 Not Started</x:v>
@@ -26426,10 +26426,10 @@
         <x:v>Legal &amp; compliance</x:v>
       </x:c>
       <x:c r="G145" s="111" t="str">
-        <x:v>Choose LLC state and privacy structure</x:v>
+        <x:v>Complete Maryland LLC formation</x:v>
       </x:c>
       <x:c r="H145" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I145" s="111" t="str">
         <x:v>N/A</x:v>
@@ -26441,21 +26441,21 @@
         <x:v>Founder</x:v>
       </x:c>
       <x:c r="L145" s="111" t="str">
-        <x:v>Counsel / founder decision</x:v>
+        <x:v>Northwest / state approval</x:v>
       </x:c>
       <x:c r="M145" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Await Maryland approval and approved documents. Filing is reported complete; exact filing date/ID, EIN, bank setup and actual invoice remain unverified.</x:v>
       </x:c>
       <x:c r="N145" s="112"/>
       <x:c r="O145" s="111" t="str"/>
       <x:c r="P145" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46273.666666666664</x:v>
       </x:c>
       <x:c r="Q145" s="111" t="str">
-        <x:v>Compare Wyoming and other candidates with an adult-platform attorney and CPA; include registered agent, taxes, and foreign qualification.</x:v>
+        <x:v>Maryland LLC selected and filing reported by founder for Kiban Digital Holdings LLC through Northwest. Record approved filing and address details once returned.</x:v>
       </x:c>
       <x:c r="R145" s="111" t="str">
-        <x:v>No entity filed. A no-income-tax state does not by itself remove taxes or disclosure duties elsewhere.</x:v>
+        <x:v>Founder reported filing complete September 8, 2026; this is the report date, not a verified filing date. State approval pending. Filing ID and actual cost were not supplied.</x:v>
       </x:c>
       <x:c r="S145" s="111" t="str">
         <x:v>Preserved Master Tracker row 158; legacy status: 📋 Not Started</x:v>
@@ -27527,7 +27527,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79e8f6906de846af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc07a6951aab4717"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/product/Pumdoki_MasterTracker_V4.xlsx
+++ b/docs/product/Pumdoki_MasterTracker_V4.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7795711c1c2c4fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" r:id="R2044898aa65d4e38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" r:id="R404a5f97f40147d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Assumptions" sheetId="4" r:id="Rb807e3ab990a40b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💸 Expense Tracker" sheetId="5" r:id="R7bfc52ffe2bc40f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Overview 2026-08-16" sheetId="6" r:id="R9494421699b1422d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="7" r:id="R362a974d66b74322"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="8" r:id="R8c78190525054a80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Tracker" sheetId="9" r:id="R778bb3c34800408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Blocker Queue" sheetId="10" r:id="Rd242103954474179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="11" r:id="R429c6bd7ab0245a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Register" sheetId="12" r:id="R8635ba7f128346ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Budget" sheetId="13" r:id="Rd60094f2100c445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Re81aaddfa62f47b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" r:id="Rb5047abd3826488d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" r:id="R005d9f5f39f94900"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Assumptions" sheetId="4" r:id="Recd0c28599924730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💸 Expense Tracker" sheetId="5" r:id="R39c9842b214f462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Overview 2026-08-16" sheetId="6" r:id="Refdec6ae1cc1424c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="7" r:id="R8a341beb143b467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="8" r:id="R760da7d95eb34f00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Tracker" sheetId="9" r:id="R322ee4ad41984bca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Blocker Queue" sheetId="10" r:id="R7ce6841af0e74069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="11" r:id="R445718308a854512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Register" sheetId="12" r:id="R4e090ff29e2949a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Budget" sheetId="13" r:id="Rb6b02667adec4c3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -205,9 +205,6 @@
     <x:t xml:space="preserve">Finalize Trademark Filing Plan</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Decide classes (IC 009, 035, 042), timing, filing sequence for 'Pumdoki' and 'Veso'.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Trademark timing/classes already considered.</x:t>
   </x:si>
   <x:si>
@@ -241,9 +238,6 @@
     <x:t xml:space="preserve">Prohibit trafficking, exploitation, coercive content. Include reporting mechanisms and creator guidance.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Required by CCBill/Epoch for merchant onboarding.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Draft Non-Consensual Content Policy</x:t>
   </x:si>
   <x:si>
@@ -361,15 +355,6 @@
     <x:t xml:space="preserve">Ensure primary flows work cleanly on mobile and desktop.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Implement Dark Knight theme</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Second default theme (dark/charcoal). Near-black backgrounds, deep tones, pink accent. Toggle in Settings. All users get this free alongside Sakura Pink.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Committed as a default theme — not premium. CSS variable overrides over existing system. Do not skip.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Design Founding Creator / Member badge program</x:t>
   </x:si>
   <x:si>
@@ -394,18 +379,9 @@
     <x:t xml:space="preserve">Set up Cloudflare R2 media storage</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Configure R2 buckets, access policies, signed URLs for private media, CDN caching.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">R2 chosen for NSFW-safe media delivery.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Define RDS PostgreSQL schema</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Model users, creators, posts, subscriptions, plans, transactions, Veso wallets, moderation.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Set up local / staging / prod environments</x:t>
   </x:si>
   <x:si>
@@ -586,21 +562,12 @@
     <x:t xml:space="preserve">Build Chat UI</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Build Veso wallet page</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Member-facing wallet: Veso balance display, add funds flow, transaction history. 1 Veso = 1 USD. Keep it simple for MVP.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Implement NSFW +18 content toggle</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Build settings page</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Account info, password change, notification preferences, theme toggle (Sakura Pink / Dark Knight), NSFW content toggle, payment/billing section.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Build help / support page</x:t>
   </x:si>
   <x:si>
@@ -613,9 +580,6 @@
     <x:t xml:space="preserve">Build 'Your Activity' page</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Member activity history: posts liked, content purchased, subscriptions, Veso spent. Lower priority.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Nice-to-have post-launch. Defer if time is tight.</x:t>
   </x:si>
   <x:si>
@@ -745,9 +709,6 @@
     <x:t xml:space="preserve">Create the actual subscription/payment flow through CCBill/Epoch.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Implementation not confirmed.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Build renewal / cancel logic</x:t>
   </x:si>
   <x:si>
@@ -775,12 +736,6 @@
     <x:t xml:space="preserve">Needed once monetization is live.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Define Veso wallet / display logic</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Where Veso (1 = $1 USD) appears: balance display, purchase flow, spend flow.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Define platform commission model</x:t>
   </x:si>
   <x:si>
@@ -793,9 +748,6 @@
     <x:t xml:space="preserve">Track chargebacks from CCBill/Epoch, alert admin, manage dispute responses.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Critical for high-risk adult processing.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Plan crypto payment integration</x:t>
   </x:si>
   <x:si>
@@ -856,27 +808,9 @@
     <x:t xml:space="preserve">View all transactions, subscription events, payout queue. Manually trigger or block payouts. View CCBill/Epoch transaction IDs. Filter by date, creator, status.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Needed for business operations and dispute resolution.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Build chargeback alert dashboard</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Real-time view of incoming chargebacks from CCBill/Epoch webhooks. Show chargeback rate %, alert when approaching 1% threshold. Log dispute responses.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Adult platforms live and die by chargeback rate. Exceeding 1% risks losing your merchant account.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Build Veso / wallet admin view</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">View all Veso balances across users. See top-up history, spend history, manual adjustments. Ability to issue Veso credits (e.g., for promotions or support resolutions).</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Needed once Veso is live. Also useful for resolving billing disputes.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Build Founding Badge admin management</x:t>
   </x:si>
   <x:si>
@@ -1054,9 +988,6 @@
     <x:t xml:space="preserve">CCBill → Epoch cascade, subscription lifecycle, renewal, cancel, chargebacks.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Critical for revenue reliability.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Prepare soft-launch go/no-go checklist</x:t>
   </x:si>
   <x:si>
@@ -1147,9 +1078,6 @@
     <x:t xml:space="preserve">Low</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Multiple themes (beyond Sakura &amp; Dark Knight)</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Design</x:t>
   </x:si>
   <x:si>
@@ -1213,9 +1141,6 @@
     <x:t xml:space="preserve">UX</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Activity history for members — posts liked, content purchased, Veso spent.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Nice-to-have. Build post-launch if time is tight during MVP push.</x:t>
   </x:si>
   <x:si>
@@ -1315,15 +1240,9 @@
     <x:t xml:space="preserve">10.0</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Phase 6 expanded — added: Veso wallet, NSFW toggle, Settings, Help/Support, Activity, modal/drawer/chat fixes, creator dashboard.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">11.0</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dark Knight theme added to Phase 3 — default theme #2, not premium. Must ship before or at launch.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">12.0</x:t>
   </x:si>
   <x:si>
@@ -1351,21 +1270,12 @@
     <x:t xml:space="preserve">Creator themes: Floral (Petal→Bloom→Sakura→Golden Sakura→Eternal Sakura), Ember (Ember→Ignite→Flare→Inferno→Eternal Flame).</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Currency: Veso (1 Veso = 1 USD). Wallet page and admin Veso view both required.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Infrastructure: AWS for app layer + RDS PostgreSQL for database.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Media storage/CDN: Cloudflare R2 (NSFW-safe, free egress, no restrictive AUP on legal adult content).</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Primary processor: CCBill (industry standard for adult, recurring billing, multi-currency).</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cascade fallback: Epoch (catches transactions CCBill declines).</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Future payment rail: Crypto (USDT/BTC) — planned post-MVP.</x:t>
   </x:si>
   <x:si>
@@ -1375,9 +1285,6 @@
     <x:t xml:space="preserve">NSFW content allowed from day 1. +18 toggle required in settings and feed.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dark Knight theme: second default theme. Charcoal/near-black + pink accent. CSS variable swap.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Founding Creator/Member badge: first 500 creators = reduced fee + permanent badge. First 500 members = badge + discount.</x:t>
   </x:si>
   <x:si>
@@ -1460,18 +1367,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Per class (IC 009, 035, 042). May need 2–3 classes.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">USPTO Trademark — 'Veso'</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Optional; consider after launch.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ToS Lawyer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ToS, Privacy Policy, etc. </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Registered Agent (annual)</x:t>
@@ -1673,7 +1568,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="7">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="164" formatCode="0.0%"/>
     <x:numFmt numFmtId="165" formatCode="\$#,##0"/>
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
@@ -1681,8 +1576,9 @@
     <x:numFmt numFmtId="202" formatCode="0"/>
     <x:numFmt numFmtId="203" formatCode="&quot;$&quot;0.00"/>
     <x:numFmt numFmtId="204" formatCode="0%"/>
+    <x:numFmt numFmtId="205" formatCode="$#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="29">
+  <x:fonts count="31">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -1834,8 +1730,19 @@
       <x:color rgb="FF28232A"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF9C0006"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1915,6 +1822,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF9E4ED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFC7CE"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -2053,7 +1990,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="202">
+  <x:cellXfs count="220">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -2650,11 +2587,65 @@
     <x:xf numFmtId="201" fontId="28" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="205" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="34">
+  <x:dxfs count="70">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -3029,6 +3020,402 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF246B3B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF3E4"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF805E00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF245B84"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDEBFA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A2432"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF9D7DC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5D535C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFECE8EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF246B3B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF3E4"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF805E00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF245B84"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDEBFA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A2432"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF9D7DC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5D535C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFECE8EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF3D1A3E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFAE1EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF246B3B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF3E4"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF805E00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF245B84"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDEBFA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A2432"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF9D7DC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5D535C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFECE8EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF3D1A3E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFAE1EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF246B3B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF3E4"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF805E00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF245B84"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDEBFA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A2432"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF9D7DC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5D535C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFECE8EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF3D1A3E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFAE1EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF246B3B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDF3E4"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF805E00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1C9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF245B84"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDDEBFA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF8A2432"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF9D7DC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5D535C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFECE8EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF3D1A3E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFAE1EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
@@ -3129,8 +3516,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DecisionRegisterTable" displayName="DecisionRegisterTable" ref="A3:J27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:J27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DecisionRegisterTable" displayName="DecisionRegisterTable" ref="A3:J28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:J28"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Decision ID"/>
     <x:tableColumn id="2" name="Phase"/>
@@ -3379,7 +3766,7 @@
     </x:row>
     <x:row r="2" ht="21.75" customHeight="1">
       <x:c r="A2" s="92" t="str">
-        <x:v>Updated September 8, 2026. Founder reports LLC filed and CCBill sales inquiry sent. Await responses. Record counts are navigation metrics, not launch readiness.</x:v>
+        <x:v>Updated September 9, 2026. Private R2 photo/video flow verified with real cloud storage. Next: founder reviews the working local upload/publish flow. LLC awaits Maryland approval. Record counts are not launch readiness.</x:v>
       </x:c>
       <x:c r="B2" s="92"/>
       <x:c r="C2" s="92"/>
@@ -3421,12 +3808,12 @@
         <x:v>Phase</x:v>
       </x:c>
       <x:c r="B5" s="109" t="str">
-        <x:v>P06 — Await CCBill sales response</x:v>
+        <x:v>P05 — First functioning content flow</x:v>
       </x:c>
       <x:c r="D5"/>
       <x:c r="E5"/>
       <x:c r="I5" s="130" t="str">
-        <x:v>Founder reports Kiban Digital Holdings LLC filed in Maryland and preliminary inquiry sent to CCBill sales. Await state approval and sales response. Next: share and review the response when received. No duplicate inquiry or new founder assignment.</x:v>
+        <x:v>R2 connection verified: safe photo/video upload, private drafts, publish/member read and removal. Public Access Disabled confirmed in Cloudflare. Next: founder reviews this working local flow. No hosted deployment or processor approval is claimed.</x:v>
       </x:c>
       <x:c r="J5" s="130"/>
       <x:c r="K5" s="130"/>
@@ -3439,7 +3826,7 @@
         <x:v>Work</x:v>
       </x:c>
       <x:c r="B6" s="111" t="str">
-        <x:v>Await Maryland and CCBill responses</x:v>
+        <x:v>Review the working local R2 content flow</x:v>
       </x:c>
       <x:c r="D6"/>
       <x:c r="E6"/>
@@ -3469,7 +3856,7 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B8" s="111" t="str">
-        <x:v>Veso, Connect discovery, real-time chat and tipping stay. Old Oasis game cancelled; replacement concept is post-launch.</x:v>
+        <x:v>Payment method unresolved. Subscriptions, PPV, Store, Connect, chat and tipping remain launch scope; old Oasis cancelled.</x:v>
       </x:c>
       <x:c r="I8" s="131"/>
       <x:c r="J8" s="131"/>
@@ -3546,22 +3933,22 @@
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="150" t="n">
         <x:f>COUNTA('Delivery Tracker'!$A$4:$A$400)</x:f>
-        <x:v>161</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B13" s="151"/>
       <x:c r="C13" s="150" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"Done")</x:f>
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D13" s="151"/>
       <x:c r="E13" s="150" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F13" s="151"/>
       <x:c r="G13" s="150" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"In Review")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H13" s="151"/>
       <x:c r="I13" s="150" t="n">
@@ -3571,12 +3958,12 @@
       <x:c r="J13" s="151"/>
       <x:c r="K13" s="150" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L13" s="151"/>
       <x:c r="M13" s="158" t="n">
         <x:f>IF(A13=0,0,C13/A13)</x:f>
-        <x:v>0.19254658385093168</x:v>
+        <x:v>0.20512820512820512</x:v>
       </x:c>
       <x:c r="N13" s="151"/>
     </x:row>
@@ -3739,7 +4126,7 @@
       </x:c>
       <x:c r="E19" s="111" t="n">
         <x:f>'Phase Roadmap'!E5</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F19" s="111" t="n">
         <x:f>'Phase Roadmap'!F5</x:f>
@@ -3747,7 +4134,7 @@
       </x:c>
       <x:c r="G19" s="119" t="n">
         <x:f>'Phase Roadmap'!G5</x:f>
-        <x:v>0.375</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="H19" s="111" t="n">
         <x:f>'Phase Roadmap'!H5</x:f>
@@ -3763,7 +4150,7 @@
       </x:c>
       <x:c r="K19" s="111" t="n">
         <x:f>'Phase Roadmap'!K5</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L19" s="111" t="str">
         <x:f>'Phase Roadmap'!L5</x:f>
@@ -3925,7 +4312,7 @@
       </x:c>
       <x:c r="H22" s="111" t="n">
         <x:f>'Phase Roadmap'!H8</x:f>
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I22" s="111" t="n">
         <x:f>'Phase Roadmap'!I8</x:f>
@@ -3937,11 +4324,11 @@
       </x:c>
       <x:c r="K22" s="111" t="n">
         <x:f>'Phase Roadmap'!K8</x:f>
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L22" s="111" t="str">
         <x:f>'Phase Roadmap'!L8</x:f>
-        <x:v>Slices 1–4 have published source; operations remain dormant. Founder reports Maryland LLC filed and CCBill inquiry sent. Await approval/response; review what arrives before another founder task.</x:v>
+        <x:v>Slices 1–4 published; operations dormant. Maryland approval pending. Initial CCBill reply retained; proposed follow-up cancelled. Founder/provider work now accompanies each functional code slice.</x:v>
       </x:c>
       <x:c r="M22" s="111" t="str">
         <x:f>'Phase Roadmap'!M8</x:f>
@@ -3963,11 +4350,11 @@
       </x:c>
       <x:c r="C23" s="111" t="str">
         <x:f>'Phase Roadmap'!C9</x:f>
-        <x:v>Not Started</x:v>
+        <x:v>Partially Complete</x:v>
       </x:c>
       <x:c r="D23" s="111" t="str">
         <x:f>'Phase Roadmap'!D9</x:f>
-        <x:v>UI Prototype</x:v>
+        <x:v>Backend Implemented</x:v>
       </x:c>
       <x:c r="E23" s="111" t="n">
         <x:f>'Phase Roadmap'!E9</x:f>
@@ -3983,11 +4370,11 @@
       </x:c>
       <x:c r="H23" s="111" t="n">
         <x:f>'Phase Roadmap'!H9</x:f>
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I23" s="111" t="n">
         <x:f>'Phase Roadmap'!I9</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J23" s="111" t="n">
         <x:f>'Phase Roadmap'!J9</x:f>
@@ -3995,19 +4382,19 @@
       </x:c>
       <x:c r="K23" s="111" t="n">
         <x:f>'Phase Roadmap'!K9</x:f>
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L23" s="111" t="str">
         <x:f>'Phase Roadmap'!L9</x:f>
-        <x:v>UI seams exist; secure R2 upload, quarantine, moderation, entitlement, and signed delivery are absent.</x:v>
+        <x:v>Safe photo/video flow now uses private R2 storage. Cloud upload/read, private drafts, publish/feed, ranges, restart persistence and removal are verified. Test accounts only. Hosted review deployment and production media controls remain open.</x:v>
       </x:c>
       <x:c r="M23" s="111" t="str">
         <x:f>'Phase Roadmap'!M9</x:f>
-        <x:v>After the business definition, authorize a bounded synthetic content/media slice. Real identity/content exposure requires applicable safeguards.</x:v>
+        <x:v>Founder reviews the working local R2 upload/publish flow for this slice. No new signup, paperwork or payment task. Real identity, adult uploads and payments remain disabled. Full P05 exit, deployment and processor approval remain open.</x:v>
       </x:c>
       <x:c r="N23" s="111" t="str">
         <x:f>'Phase Roadmap'!O9</x:f>
-        <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#9-phase-5--media-pipeline-and-content-model</x:v>
+        <x:v>HANDOFF.md</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -4017,11 +4404,11 @@
       </x:c>
       <x:c r="B24" s="111" t="str">
         <x:f>'Phase Roadmap'!B10</x:f>
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="C24" s="111" t="str">
         <x:f>'Phase Roadmap'!C10</x:f>
-        <x:v>Not Started</x:v>
+        <x:v>Partially Complete</x:v>
       </x:c>
       <x:c r="D24" s="111" t="str">
         <x:f>'Phase Roadmap'!D10</x:f>
@@ -4033,7 +4420,7 @@
       </x:c>
       <x:c r="F24" s="111" t="n">
         <x:f>'Phase Roadmap'!F10</x:f>
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G24" s="119" t="n">
         <x:f>'Phase Roadmap'!G10</x:f>
@@ -4041,7 +4428,7 @@
       </x:c>
       <x:c r="H24" s="111" t="n">
         <x:f>'Phase Roadmap'!H10</x:f>
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I24" s="111" t="n">
         <x:f>'Phase Roadmap'!I10</x:f>
@@ -4053,19 +4440,19 @@
       </x:c>
       <x:c r="K24" s="111" t="n">
         <x:f>'Phase Roadmap'!K10</x:f>
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L24" s="111" t="str">
         <x:f>'Phase Roadmap'!L10</x:f>
-        <x:v>Veso direction and UI prototypes exist; processor, ledger, webhooks, and entitlements are not implemented.</x:v>
+        <x:v>Provider/site preparation is in progress: CCBill Sales replied, safe-content/R2 milestone is verified and policy drafting is commissioned. Payment backend, webhooks and paid entitlements have not started.</x:v>
       </x:c>
       <x:c r="M24" s="111" t="str">
         <x:f>'Phase Roadmap'!M10</x:f>
-        <x:v>Founder/provider/counsel decisions on processor economics, refunds, payouts, and Veso terms.</x:v>
+        <x:v>Continue functioning-site slices; password protection is permitted for later review. Founder reviews the current local flow. Return to CCBill when review-ready; define the supported payment method before integration.</x:v>
       </x:c>
       <x:c r="N24" s="111" t="str">
         <x:f>'Phase Roadmap'!O10</x:f>
-        <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#10-phase-6--veso-payments-subscriptions-tipping-and-ppv</x:v>
+        <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -4115,11 +4502,11 @@
       </x:c>
       <x:c r="L25" s="111" t="str">
         <x:f>'Phase Roadmap'!L11</x:f>
-        <x:v>Waiting on creator approval, media, payments, entitlement, and operations dependencies.</x:v>
+        <x:v>Core journey still needs creator, content/access and operations controls. Apply payment dependencies to the chosen beta method.</x:v>
       </x:c>
       <x:c r="M25" s="111" t="str">
         <x:f>'Phase Roadmap'!M11</x:f>
-        <x:v>Develop one complete journey incrementally with synthetic data. Real use requires creator, media, payment, entitlement and operating controls.</x:v>
+        <x:v>Continue safe test flows. Define the beta payment model with its slice; any paid flow requires processor confirmation, entitlements, auditable earnings and reconciliation.</x:v>
       </x:c>
       <x:c r="N25" s="111" t="str">
         <x:f>'Phase Roadmap'!O11</x:f>
@@ -4177,7 +4564,7 @@
       </x:c>
       <x:c r="M26" s="111" t="str">
         <x:f>'Phase Roadmap'!M12</x:f>
-        <x:v>Integrate only after content, entitlement, and Veso foundations exist.</x:v>
+        <x:v>Integrate content and access controls. Define service/order and beta payment rules with the relevant slice.</x:v>
       </x:c>
       <x:c r="N26" s="111" t="str">
         <x:f>'Phase Roadmap'!O12</x:f>
@@ -4323,7 +4710,7 @@
       </x:c>
       <x:c r="F29" s="111" t="n">
         <x:f>'Phase Roadmap'!F15</x:f>
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="119" t="n">
         <x:f>'Phase Roadmap'!G15</x:f>
@@ -4343,11 +4730,11 @@
       </x:c>
       <x:c r="K29" s="111" t="n">
         <x:f>'Phase Roadmap'!K15</x:f>
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L29" s="111" t="str">
         <x:f>'Phase Roadmap'!L15</x:f>
-        <x:v>Dormant operations foundation has published source. Further operations work stays parked while Maryland approval and CCBill sales response are pending.</x:v>
+        <x:v>Dormant operations source remains parked. The next planned P05 test-content flow pairs storage decisions with implementation. No deployment, live payment or identity activation is implied.</x:v>
       </x:c>
       <x:c r="M29" s="111" t="str">
         <x:f>'Phase Roadmap'!M15</x:f>
@@ -4525,7 +4912,7 @@
       </x:c>
       <x:c r="M32" s="111" t="str">
         <x:f>'Phase Roadmap'!M18</x:f>
-        <x:v>Keep expanding domain tests; do not schedule beta until legal, payments, identity, recovery, and support gates exist.</x:v>
+        <x:v>Verify applicable creator, content, security, recovery and support controls for beta. Paid flows also need processor and payment controls.</x:v>
       </x:c>
       <x:c r="N32" s="111" t="str">
         <x:f>'Phase Roadmap'!O18</x:f>
@@ -4556,7 +4943,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B35" s="109" t="str">
-        <x:v>LLC filed and CCBill inquiry sent, per founder report. Wait for Maryland approval and CCBill sales response. Review the response when received, then choose one next action.</x:v>
+        <x:v>One functional slice at a time. R2 setup and safe-media integration are verified. Next: founder reviews the working local upload/publish flow to close this slice. CCBill follow-up stays cancelled; live sensitive use remains unavailable.</x:v>
       </x:c>
       <x:c r="C35" s="109" t="str">
         <x:v>2</x:v>
@@ -4684,7 +5071,7 @@
         <x:v>Next founder task</x:v>
       </x:c>
       <x:c r="J38" s="111" t="str">
-        <x:v>Share and review Maryland/CCBill responses when received.</x:v>
+        <x:v>Founder reviews the working local R2 upload, draft, publish and removal flow.</x:v>
       </x:c>
       <x:c r="K38" s="111" t="str"/>
       <x:c r="L38" s="111" t="str"/>
@@ -5679,6 +6066,9 @@
     <x:mergeCell ref="A16:N16"/>
     <x:mergeCell ref="A34:N34"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="C18:C32">
+    <x:cfRule type="containsText" dxfId="68" priority="1" operator="containsText" text="Deferred"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -5779,32 +6169,30 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C4" s="109" t="str">
-        <x:v>Wallet, payments and payouts</x:v>
+        <x:v>Payments and payouts</x:v>
       </x:c>
       <x:c r="D4" s="109" t="str">
-        <x:v>Await processor response</x:v>
+        <x:v>Cancelled clarification follow-up only</x:v>
       </x:c>
       <x:c r="E4" s="109" t="str">
-        <x:v>Review CCBill response when received</x:v>
+        <x:v>Do not send this cancelled follow-up</x:v>
       </x:c>
       <x:c r="F4" s="109" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Deferred</x:v>
       </x:c>
       <x:c r="G4" s="109" t="str">
         <x:v>Founder</x:v>
       </x:c>
-      <x:c r="H4" s="109" t="str">
-        <x:v>Awaiting CCBill sales response</x:v>
-      </x:c>
+      <x:c r="H4" s="109"/>
       <x:c r="I4" s="109" t="str">
-        <x:v>Founder reports CCBill sales inquiry sent and Maryland LLC filed. Wait for sales response and state approval; share/review what arrives before the next founder action. No reply or approval evidenced.</x:v>
+        <x:v>Deferred applies only to this cancelled clarification. CCBill Sales/site preparation is in progress; the current founder task remains local content-flow review. Account-specific approval and payment integration remain unresolved.</x:v>
       </x:c>
       <x:c r="J4" s="110"/>
       <x:c r="K4" s="109" t="str">
         <x:v>docs/product/initial-ccbill-inquiry.md</x:v>
       </x:c>
       <x:c r="L4" s="110" t="n">
-        <x:v>46273.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
@@ -5900,32 +6288,54 @@
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="H7" s="111" t="str">
-        <x:v>Phase 4–6 dependencies</x:v>
+        <x:v>Applicable beta flow dependencies</x:v>
       </x:c>
       <x:c r="I7" s="111" t="str">
-        <x:v>Build incrementally with synthetic data after the founder definition. Real use requires applicable creator/media/payment/operations controls.</x:v>
+        <x:v>Continue safe test slices. Beta payment method is unresolved. Paid flows still need processor, entitlement, earnings, refund and reconciliation controls.</x:v>
       </x:c>
       <x:c r="J7" s="112"/>
       <x:c r="K7" s="111" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#11-phase-7--core-end-to-end-vertical-slice</x:v>
       </x:c>
       <x:c r="L7" s="112" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="111"/>
-      <x:c r="B8" s="111"/>
-      <x:c r="C8" s="111"/>
-      <x:c r="D8" s="111"/>
-      <x:c r="E8" s="111"/>
-      <x:c r="F8" s="111"/>
-      <x:c r="G8" s="111"/>
-      <x:c r="H8" s="111"/>
-      <x:c r="I8" s="111"/>
+      <x:c r="A8" s="111" t="str">
+        <x:v>LEG-MT-087</x:v>
+      </x:c>
+      <x:c r="B8" s="111" t="str">
+        <x:v>P05</x:v>
+      </x:c>
+      <x:c r="C8" s="111" t="str">
+        <x:v>Media pipeline and content model</x:v>
+      </x:c>
+      <x:c r="D8" s="111" t="str">
+        <x:v>Content and access design</x:v>
+      </x:c>
+      <x:c r="E8" s="111" t="str">
+        <x:v>Review P05 Slice 1 local design</x:v>
+      </x:c>
+      <x:c r="F8" s="111" t="str">
+        <x:v>In Review</x:v>
+      </x:c>
+      <x:c r="G8" s="111" t="str">
+        <x:v>Engineering</x:v>
+      </x:c>
+      <x:c r="H8" s="111" t="str">
+        <x:v>Targeted review during relevant slice</x:v>
+      </x:c>
+      <x:c r="I8" s="111" t="str">
+        <x:v>Broader design remains In Review. The local safe-content slice is implemented and under verification. Targeted review is still required before live sensitive use. No P05 exit, deployment or provider approval is claimed.</x:v>
+      </x:c>
       <x:c r="J8" s="112"/>
-      <x:c r="K8" s="111"/>
-      <x:c r="L8" s="112"/>
+      <x:c r="K8" s="111" t="str">
+        <x:v>docs/architecture/phase5-slice1-content-model-and-access-design.md</x:v>
+      </x:c>
+      <x:c r="L8" s="112" t="n">
+        <x:v>46274.666666666664</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="111"/>
@@ -5947,17 +6357,17 @@
     <x:mergeCell ref="A2:L2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="F4:F9">
-    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Done"/>
-    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="In Progress"/>
-    <x:cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="In Review"/>
-    <x:cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="Blocked"/>
-    <x:cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="Not Started"/>
-    <x:cfRule type="containsText" dxfId="21" priority="6" operator="containsText" text="Ready"/>
-    <x:cfRule type="containsText" dxfId="25" priority="7" operator="containsText" text="Deferred"/>
+    <x:cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="Done"/>
+    <x:cfRule type="containsText" dxfId="48" priority="2" operator="containsText" text="In Progress"/>
+    <x:cfRule type="containsText" dxfId="49" priority="3" operator="containsText" text="In Review"/>
+    <x:cfRule type="containsText" dxfId="50" priority="4" operator="containsText" text="Blocked"/>
+    <x:cfRule type="containsText" dxfId="51" priority="5" operator="containsText" text="Not Started"/>
+    <x:cfRule type="containsText" dxfId="52" priority="6" operator="containsText" text="Ready"/>
+    <x:cfRule type="containsText" dxfId="53" priority="7" operator="containsText" text="Deferred"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9807d8f6f37d41c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46f208786e734731"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6070,7 +6480,7 @@
         <x:v>Later asynchronous product work can use a reviewed durable base instead of ad-hoc request-time delivery.</x:v>
       </x:c>
       <x:c r="G4" s="109" t="str">
-        <x:v>No product flow, provider, deployment, Redis, live credentials, email/token migration, payment, Veso, identity, or creator-review activation.</x:v>
+        <x:v>No product flow, provider, deployment, Redis, live credentials, email/token migration, payment, identity or creator-review activation.</x:v>
       </x:c>
       <x:c r="H4" s="109" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/pull/13 — baseline exact-head CI run 32442777168 passed before this tracker update; fresh CI is required.</x:v>
@@ -6254,7 +6664,7 @@
         <x:v>Record founder launch corrections and funding limits.</x:v>
       </x:c>
       <x:c r="E9" s="111" t="str">
-        <x:v>Retained Veso, Connect discovery, real-time chat and tipping; cancelled the old Oasis game; recorded post-launch streak concept, provisional founding/Plus offers and staged cash budget.</x:v>
+        <x:v>Retained Connect discovery, real-time chat and tipping; cancelled the old Oasis game; recorded post-launch streak concept, provisional founding/Plus offers and staged cash budget.</x:v>
       </x:c>
       <x:c r="F9" s="111" t="str">
         <x:v>The next founder task is the initial business definition, with no spending required.</x:v>
@@ -6279,21 +6689,45 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
-      <x:c r="A10" s="111"/>
-      <x:c r="B10" s="111"/>
-      <x:c r="C10" s="111"/>
-      <x:c r="D10" s="111"/>
-      <x:c r="E10" s="111"/>
-      <x:c r="F10" s="111"/>
-      <x:c r="G10" s="111"/>
-      <x:c r="H10" s="111"/>
-      <x:c r="I10" s="111"/>
-      <x:c r="J10" s="111"/>
-      <x:c r="K10" s="111"/>
-      <x:c r="L10" s="111"/>
+      <x:c r="A10" s="112" t="n">
+        <x:v>46273.666666666664</x:v>
+      </x:c>
+      <x:c r="B10" s="111" t="str">
+        <x:v>LEG-MT-087</x:v>
+      </x:c>
+      <x:c r="C10" s="111" t="str">
+        <x:v>P05</x:v>
+      </x:c>
+      <x:c r="D10" s="111" t="str">
+        <x:v>Draft P05 Slice 1 content model and access rules.</x:v>
+      </x:c>
+      <x:c r="E10" s="111" t="str">
+        <x:v>Prepared a local content/revision/media/offer model, lifecycle, access rules and synthetic acceptance cases. Definition tasks LEG-MT-087 and LEG-MT-089 are In Review.</x:v>
+      </x:c>
+      <x:c r="F10" s="111" t="str">
+        <x:v>Creates a concrete design for review before the first protected-media implementation.</x:v>
+      </x:c>
+      <x:c r="G10" s="111" t="str">
+        <x:v>No contracts, migrations, API routes, worker handlers or UI changed. P05 backend and phase exits remain unfinished; no upload, payment or live operations activated.</x:v>
+      </x:c>
+      <x:c r="H10" s="111" t="str">
+        <x:v>docs/architecture/phase5-slice1-content-model-and-access-design.md</x:v>
+      </x:c>
+      <x:c r="I10" s="111" t="str">
+        <x:v>In Review</x:v>
+      </x:c>
+      <x:c r="J10" s="111" t="str">
+        <x:v>Scoped human technical review remains pending.</x:v>
+      </x:c>
+      <x:c r="K10" s="111" t="str">
+        <x:v>Review the design. Founder still awaits the sent CCBill inquiry response and Maryland formation approval.</x:v>
+      </x:c>
+      <x:c r="L10" s="111" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11" s="111"/>
+      <x:c r="A11" s="112"/>
       <x:c r="B11" s="111"/>
       <x:c r="C11" s="111"/>
       <x:c r="D11" s="111"/>
@@ -7040,13 +7474,13 @@
     <x:mergeCell ref="A2:L2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="I4:I63">
-    <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Done"/>
-    <x:cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="In Progress"/>
-    <x:cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="In Review"/>
-    <x:cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="Blocked"/>
-    <x:cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Not Started"/>
-    <x:cfRule type="containsText" dxfId="22" priority="6" operator="containsText" text="Ready"/>
-    <x:cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="Deferred"/>
+    <x:cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="Done"/>
+    <x:cfRule type="containsText" dxfId="55" priority="2" operator="containsText" text="In Progress"/>
+    <x:cfRule type="containsText" dxfId="56" priority="3" operator="containsText" text="In Review"/>
+    <x:cfRule type="containsText" dxfId="57" priority="4" operator="containsText" text="Blocked"/>
+    <x:cfRule type="containsText" dxfId="58" priority="5" operator="containsText" text="Not Started"/>
+    <x:cfRule type="containsText" dxfId="59" priority="6" operator="containsText" text="Ready"/>
+    <x:cfRule type="containsText" dxfId="60" priority="7" operator="containsText" text="Deferred"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="I4:I63">
@@ -7055,7 +7489,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48a368095cad4ec5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe125cfc69b24b7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7312,16 +7746,16 @@
         <x:v>In Progress</x:v>
       </x:c>
       <x:c r="G9" s="111" t="str">
-        <x:v>Founder reports Kiban Digital Holdings LLC filed in Maryland through Northwest; state approval pending. Exact filing date, filing ID, EIN, bank account and actual cost have not been supplied.</x:v>
+        <x:v>Kiban Digital Holdings LLC is reported filed in Maryland through Northwest; state approval pending. Founder confirmed $196 total paid, recorded in Expense Tracker. Filing ID, EIN and bank readiness remain unverified.</x:v>
       </x:c>
       <x:c r="H9" s="111" t="str">
-        <x:v>Await Maryland approval and approved formation documents. Record invoice when available. Next founder action is to share and review the received Maryland or CCBill response.</x:v>
+        <x:v>Await Maryland approval and approved documents; record invoice when available. Continue the planned P05 test-content flow while handling only the founder/provider decisions that slice needs.</x:v>
       </x:c>
       <x:c r="I9" s="111" t="str">
-        <x:v>Founder report, September 8, 2026: LLC filed and CCBill sales inquiry sent. Exact event times, state approval and processor response not supplied.</x:v>
+        <x:v>Founder reports: filing/inquiry sent September 8; CCBill Sales reply supplied September 9; $196 formation total confirmed September 10. State approval and exact correspondence times remain unverified.</x:v>
       </x:c>
       <x:c r="J9" s="112" t="n">
-        <x:v>46273.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="55" customHeight="1">
@@ -7342,16 +7776,16 @@
         <x:v>In Progress</x:v>
       </x:c>
       <x:c r="G10" s="111" t="str">
-        <x:v>Founder reports the preliminary inquiry was sent to CCBill sales. No reply, quote, formal merchant approval or activation is evidenced. Epoch remains a possible later provider.</x:v>
+        <x:v>CCBill Sales replied: fully functioning online site required; password protection allowed. Site work is underway, including verified safe-content/R2 flow and commissioned policies. Model fit, fees/reserves, payouts and approval remain open.</x:v>
       </x:c>
       <x:c r="H10" s="111" t="str">
-        <x:v>Await and review the sales response for model eligibility, countries, Veso, creator payouts, complete fees/reserves and required documents. Do not send a duplicate inquiry or assume approval.</x:v>
+        <x:v>Keep the current founder step: review the working local content flow. Continue site slices and return to Sales when review-ready. The clarification follow-up remains cancelled; payment backend is not implemented.</x:v>
       </x:c>
       <x:c r="I10" s="111" t="str">
-        <x:v>Founder report, September 8, 2026: LLC filed and CCBill sales inquiry sent. Exact event times, state approval and processor response not supplied.</x:v>
+        <x:v>User-pasted CCBill Sales reply supplied September 9, 2026; sender timestamp not verified. docs/product/initial-ccbill-inquiry.md</x:v>
       </x:c>
       <x:c r="J10" s="112" t="n">
-        <x:v>46273.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="55" customHeight="1">
@@ -7454,7 +7888,7 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C14" s="111" t="str">
-        <x:v>Commission, payout, refund, and Veso economics</x:v>
+        <x:v>Commission, payout and refund economics</x:v>
       </x:c>
       <x:c r="D14" s="111" t="str">
         <x:v>Founder</x:v>
@@ -7469,13 +7903,13 @@
         <x:v>Founder corrected the offer: Pumdoki should recover costs without profit on founding creator sales. Processing-fees-only is superseded. Duration, fee allocation and no-loss economics are unproven.</x:v>
       </x:c>
       <x:c r="H14" s="111" t="str">
-        <x:v>After counsel/processor fit, define attributable costs, refunds, chargebacks, reserves and payout allocation before quoting founder fees. No loss-free promise is supported yet.</x:v>
+        <x:v>Validate processor costs, refunds, chargebacks, reserves and payout allocation before quoting fees. No-loss economics remain unproven.</x:v>
       </x:c>
       <x:c r="I14" s="111" t="str">
         <x:v>docs/product/initial-business-definition.md — founder answers reviewed September 6, 2026</x:v>
       </x:c>
       <x:c r="J14" s="112" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="55" customHeight="1">
@@ -7531,7 +7965,7 @@
         <x:v>Slice 3 merged in PR #15. Provider-neutral dormant foundation exists; no operational provider/session/hosting activation. G1–G12 remain NOT EVALUATED.</x:v>
       </x:c>
       <x:c r="H16" s="111" t="str">
-        <x:v>Operations work stays parked while awaiting CCBill response. Slice 4 is published; final CI/main evidence is in HANDOFF.md. Deployment and activation remain separate.</x:v>
+        <x:v>Operations work remains parked. Next is the planned P05 test-content flow, pairing storage decisions with code. Actual spending, deployment and live sensitive-use controls remain.</x:v>
       </x:c>
       <x:c r="I16" s="111" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/pull/15</x:v>
@@ -7620,16 +8054,16 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="G19" s="173" t="str">
-        <x:v>Business definition answered/reviewed and operating location confirmed as Maryland, USA. Work remains sequential, one founder assignment at a time.</x:v>
+        <x:v>Business definition reviewed; founder works one functional slice at a time. Necessary founder/provider decisions accompany that slice rather than preceding all code as a paperwork phase.</x:v>
       </x:c>
       <x:c r="H19" s="173" t="str">
-        <x:v>Current: await Maryland approval and CCBill sales response. Founder reports filing and inquiry completed. Share/review the response when received, then choose one next action.</x:v>
+        <x:v>R2 setup and safe-media integration verified. Next: founder reviews the working local upload/publish flow. No new provider signup, paperwork or payment task. Adult-content provider acceptance and hosted deployment remain unconfirmed.</x:v>
       </x:c>
       <x:c r="I19" s="173" t="str">
-        <x:v>Founder report, September 8, 2026: LLC filed and CCBill sales inquiry sent. Exact event times, state approval and processor response not supplied.</x:v>
+        <x:v>September 9, 2026: credential preflight, real R2 API/browser photo/video tests, Cloudflare Public Access Disabled, restart and cleanup checks passed. Evidence: HANDOFF.md. Token expiry and budget alert are not verified.</x:v>
       </x:c>
       <x:c r="J19" s="174" t="n">
-        <x:v>46273.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="95" customHeight="1">
@@ -7640,7 +8074,7 @@
         <x:v>P00</x:v>
       </x:c>
       <x:c r="C20" s="173" t="str">
-        <x:v>Veso, discovery, real-time chat and tipping remain launch scope</x:v>
+        <x:v>Discovery, real-time chat and tipping remain launch scope</x:v>
       </x:c>
       <x:c r="D20" s="173" t="str">
         <x:v>Founder</x:v>
@@ -7650,16 +8084,16 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="G20" s="173" t="str">
-        <x:v>Veso stays. Connect is creator discovery filtered by online status, price and language. Real-time chat and tipping remain required.</x:v>
+        <x:v>Connect is creator discovery filtered by online status, price and language. Real-time chat and tipping remain required.</x:v>
       </x:c>
       <x:c r="H20" s="173" t="str">
-        <x:v>Implement within funded launch scope. Do not assume a full automated booking/scheduling system from the Connect page.</x:v>
+        <x:v>Other confirmed launch scope remains. No automated booking expansion is implied.</x:v>
       </x:c>
       <x:c r="I20" s="173" t="str">
         <x:v>Founder decision, September 6, 2026</x:v>
       </x:c>
       <x:c r="J20" s="174" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="95" customHeight="1">
@@ -7803,13 +8237,13 @@
         <x:v>Founder now reports a $1,800 monthly ceiling and proposed recruiter/helper $300–$400/month. Inclusion in that ceiling and overlap with budget backup allowance are unconfirmed. Earlier cash assumptions remain.</x:v>
       </x:c>
       <x:c r="H25" s="173" t="str">
-        <x:v>Keep cost allowances until actual quotes/invoices support changes. LLC filing is reported but amount/payment details were not supplied; actual cost remains blank. Monthly funding and helper overlap remain unresolved.</x:v>
+        <x:v>Founder confirmed $196 Northwest formation and $1,100 policy drafting purchased on September 10. Actuals recorded in Expense Tracker; allowances unchanged. Monthly funding/helper overlap remains unresolved.</x:v>
       </x:c>
       <x:c r="I25" s="173" t="str">
-        <x:v>Founder funding statements September 6 and filed-LLC/sent-inquiry report September 8, 2026</x:v>
+        <x:v>Founder funding statements September 6 and purchase confirmations September 10, 2026</x:v>
       </x:c>
       <x:c r="J25" s="174" t="n">
-        <x:v>46273.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="95" customHeight="1">
@@ -7833,10 +8267,10 @@
         <x:v>Use DIY work, suitable Fiverr specialists and drafts to control cost. Necessary legal work uses a qualified lawyer reviewing the actual model. Record the reviewed version, corrections and remaining limitations.</x:v>
       </x:c>
       <x:c r="H26" s="173" t="str">
-        <x:v>Buy targeted legal advice only for unresolved requirements or necessary document/workflow review. Technical design review precedes fixed money/media designs; independent integrated assessment and retest precede real launch.</x:v>
+        <x:v>Use targeted reviews alongside relevant implementation and before live sensitive use. Controlled test implementation does not wait for blanket paid pre-code review. Independent integrated assessment and retest remain before real launch.</x:v>
       </x:c>
       <x:c r="I26" s="173" t="str">
-        <x:v>Founder instruction, September 8, 2026</x:v>
+        <x:v>Founder correction, September 9, 2026: cancel proposed CCBill follow-up; develop functioning slices with relevant founder/provider work alongside code. PLAN.md §9 and §20</x:v>
       </x:c>
       <x:c r="J26" s="174" t="n">
         <x:v>46273.666666666664</x:v>
@@ -7871,6 +8305,18 @@
       <x:c r="J27" s="174" t="n">
         <x:v>46271.666666666664</x:v>
       </x:c>
+    </x:row>
+    <x:row r="28" ht="95" customHeight="1">
+      <x:c r="A28" s="173"/>
+      <x:c r="B28" s="173"/>
+      <x:c r="C28" s="173"/>
+      <x:c r="D28" s="173"/>
+      <x:c r="E28" s="173"/>
+      <x:c r="F28" s="173"/>
+      <x:c r="G28" s="173"/>
+      <x:c r="H28" s="173"/>
+      <x:c r="I28" s="173"/>
+      <x:c r="J28" s="174"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7878,13 +8324,15 @@
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="F4:F18">
-    <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Done"/>
-    <x:cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="In Progress"/>
-    <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="In Review"/>
-    <x:cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="Blocked"/>
-    <x:cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="Not Started"/>
-    <x:cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="Ready"/>
-    <x:cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="Deferred"/>
+    <x:cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="Done"/>
+    <x:cfRule type="containsText" dxfId="62" priority="2" operator="containsText" text="In Progress"/>
+    <x:cfRule type="containsText" dxfId="63" priority="3" operator="containsText" text="In Review"/>
+    <x:cfRule type="containsText" dxfId="64" priority="4" operator="containsText" text="Blocked"/>
+    <x:cfRule type="containsText" dxfId="65" priority="5" operator="containsText" text="Not Started"/>
+    <x:cfRule type="containsText" dxfId="66" priority="6" operator="containsText" text="Ready"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F4:F28">
+    <x:cfRule type="containsText" dxfId="67" priority="7" operator="containsText" text="Deferred"/>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="F4:F18">
@@ -7896,7 +8344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45740b3e98174502"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf4d4d30ca3e45c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7921,7 +8369,7 @@
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
       <x:c r="A2" s="177" t="str">
-        <x:v>September 8, 2026</x:v>
+        <x:v>September 10, 2026</x:v>
       </x:c>
       <x:c r="B2" s="179"/>
       <x:c r="C2" s="179"/>
@@ -8125,12 +8573,12 @@
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="177" t="str">
-        <x:v>Current: await CCBill response</x:v>
+        <x:v>Next: review the working local R2 flow</x:v>
       </x:c>
       <x:c r="B17" s="179"/>
       <x:c r="C17" s="179"/>
       <x:c r="D17" s="177" t="str">
-        <x:v>Founder reports Kiban Digital Holdings LLC filed in Maryland and preliminary inquiry sent to CCBill sales. Await state approval and sales response; review what arrives before another founder task.</x:v>
+        <x:v>R2 connection verified. $0 was due at activation only; subsequent usage is metered. Proposed $5/month budget is not a hard cap. Budget-alert setup is unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
@@ -8174,7 +8622,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="D21" s="177" t="str">
-        <x:v>Optional scoped advice for unresolved material issues. DIY/Fiverr drafts first where suitable; use a qualified lawyer when needed. Unquoted allowance unchanged; no legal engagement.</x:v>
+        <x:v>Optional scoped advice for unresolved material issues. This allowance is separate from the purchased policy-document drafting bundle. Amount unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -8218,7 +8666,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="D24" s="177" t="str">
-        <x:v>Founder reports Maryland LLC filed through Northwest; state approval pending. Actual invoice and recurring charges not supplied; this allowance is not amount paid.</x:v>
+        <x:v>Founder confirmed $196 total paid to Northwest for Kiban Digital Holdings LLC. Maryland approval pending. Actual is in Expense Tracker; this planning allowance is unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
@@ -8232,7 +8680,7 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="D25" s="177" t="str">
-        <x:v>Prepare suitable drafts yourself or with Fiverr specialists; qualified adult-platform counsel reviews and corrects necessary final documents/workflows. Unquoted allowance unchanged.</x:v>
+        <x:v>Suzanne Lawyer on Fiverr hired for the $1,100 policy-document bundle. Delivery and substantive approval pending. Actual is in Expense Tracker; planning allowance unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -8246,7 +8694,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="D26" s="177" t="str">
-        <x:v>Before payments/ledger/entitlement and media designs lock. Experienced backend/security reviewer; findings and remediation guidance.</x:v>
+        <x:v>Targeted backend/security review accompanies relevant code and precedes live sensitive use. No blanket paid pre-code review gate for controlled test implementation. Unquoted allowance unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -8736,7 +9184,7 @@
       <x:c r="B67" s="179"/>
       <x:c r="C67" s="179"/>
       <x:c r="D67" s="177" t="str">
-        <x:v>Expense Tracker: 1,980 + 170 + 18 × 12 = 2,366. Old displayed total 1,713 preserved; those historical assumptions are not the current budget.</x:v>
+        <x:v>Expense Tracker historical estimates exclude the removed optional trademark line. Original displayed total 1,713 is retained. Confirmed purchases total $1,296; current planning remains separate.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="64" customHeight="1">
@@ -8746,7 +9194,7 @@
       <x:c r="B68" s="179"/>
       <x:c r="C68" s="179"/>
       <x:c r="D68" s="177" t="str">
-        <x:v>Current: wait for Maryland approval and CCBill sales response, then review the response. DIY/Fiverr and targeted qualified review remain the approach. Costs/formulas unchanged; actual filing expense unknown.</x:v>
+        <x:v>Fund and build one functional slice at a time. Pair necessary founder/provider decisions with code; next is test-content upload/publish/feed and storage. Spending/deployment/live-use controls remain. Financial assumptions unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="32" customHeight="1">
@@ -9060,13 +9508,11 @@
       <x:c r="B20" s="21" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C20" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D20" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CCBill/Epoch applications have not started. Assemble the compliance package in parallel with product development.</x:t>
-        </x:is>
+      <x:c r="C20" s="217" t="str">
+        <x:v>🔄 In Progress</x:v>
+      </x:c>
+      <x:c r="D20" s="22" t="str">
+        <x:v>CCBill replied: functioning online site needed; password protection allowed. Site/policy preparation underway.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
@@ -9101,36 +9547,36 @@
       <x:c r="A23" s="16" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B23" s="17" t="s">
-        <x:v>61</x:v>
+      <x:c r="B23" s="17" t="str">
+        <x:v>Decide classes (IC 009, 035, 042), timing and filing sequence for 'Pumdoki'.</x:v>
       </x:c>
       <x:c r="C23" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D23" s="19" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
       <x:c r="A24" s="20" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B24" s="21" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="B24" s="21" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="C24" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D24" s="22" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1">
       <x:c r="A25" s="16" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B25" s="17" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B25" s="17" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="23" t="s">
         <x:v>26</x:v>
@@ -9143,133 +9589,133 @@
     </x:row>
     <x:row r="26" ht="15.75" customHeight="1">
       <x:c r="A26" s="20" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B26" s="21" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B26" s="21" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="C26" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D26" s="22" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
       <x:c r="A27" s="16" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B27" s="17" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B27" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C27" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D27" s="19" t="s">
-        <x:v>73</x:v>
+      <x:c r="C27" s="217" t="str">
+        <x:v>🔄 In Progress</x:v>
+      </x:c>
+      <x:c r="D27" s="19" t="str">
+        <x:v>Included in Suzanne Lawyer’s purchased $1,100 bundle. Draft delivery, review and approval pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15.75" customHeight="1">
       <x:c r="A28" s="20" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B28" s="21" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C28" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D28" s="22" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
       <x:c r="A29" s="16" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B29" s="17" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C29" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D29" s="19" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15.75" customHeight="1">
       <x:c r="A30" s="20" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B30" s="21" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C30" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D30" s="22" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15.75" customHeight="1">
       <x:c r="A31" s="16" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="17" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C31" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D31" s="19" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15.75" customHeight="1">
       <x:c r="A32" s="20" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B32" s="21" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C32" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D32" s="22" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1">
       <x:c r="A33" s="16" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B33" s="17" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C33" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="19" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1">
       <x:c r="A34" s="20" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B34" s="21" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D34" s="22" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="27.75" customHeight="1">
       <x:c r="A35" s="15" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B35" s="2"/>
       <x:c r="C35" s="2"/>
@@ -9277,80 +9723,80 @@
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
       <x:c r="A36" s="16" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B36" s="17" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C36" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D36" s="19" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15.75" customHeight="1">
       <x:c r="A37" s="20" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B37" s="21" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C37" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D37" s="22" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15.75" customHeight="1">
       <x:c r="A38" s="16" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B38" s="17" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C38" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="19" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15.75" customHeight="1">
       <x:c r="A39" s="20" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B39" s="21" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C39" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D39" s="22" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15.75" customHeight="1">
       <x:c r="A40" s="16" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B40" s="17" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C40" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D40" s="19" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="24" hidden="0" customHeight="1">
       <x:c r="A41" s="20" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B41" s="21" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C41" s="23" t="s">
         <x:v>26</x:v>
@@ -9360,36 +9806,36 @@
       </x:c>
     </x:row>
     <x:row r="42" ht="15.75" customHeight="1">
-      <x:c r="A42" s="16" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="B42" s="17" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C42" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D42" s="19" t="s">
-        <x:v>115</x:v>
+      <x:c r="A42" s="16" t="str">
+        <x:v>Implement Midnight City theme</x:v>
+      </x:c>
+      <x:c r="B42" s="17" t="str">
+        <x:v>Second free theme alongside Sakura Kiss. Blue city rooftops with static desktop/mobile JPG backgrounds. Settings Appearance chooser stores the preference in this browser.</x:v>
+      </x:c>
+      <x:c r="C42" s="215" t="str">
+        <x:v>✅ Done</x:v>
+      </x:c>
+      <x:c r="D42" s="19" t="str">
+        <x:v>Published in 0f01961 (#19). Theme switch/restore and static assets are tested. Account sync remains separate future work.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15.75" customHeight="1">
       <x:c r="A43" s="20" t="s">
-        <x:v>116</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B43" s="21" t="s">
-        <x:v>117</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C43" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D43" s="22" t="s">
-        <x:v>118</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="27.75" customHeight="1">
       <x:c r="A44" s="15" t="s">
-        <x:v>119</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B44" s="2"/>
       <x:c r="C44" s="2"/>
@@ -9397,38 +9843,38 @@
     </x:row>
     <x:row r="45" ht="15.75" customHeight="1">
       <x:c r="A45" s="16" t="s">
-        <x:v>120</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B45" s="17" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C45" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D45" s="19" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15.75" customHeight="1">
       <x:c r="A46" s="20" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B46" s="21" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C46" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D46" s="22" t="s">
-        <x:v>125</x:v>
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B46" s="21" t="str">
+        <x:v>Private safe-sample R2 bucket and API integration verified. Signed delivery, CDN caching and production storage lifecycle/recovery remain pending.</x:v>
+      </x:c>
+      <x:c r="C46" s="216" t="str">
+        <x:v>🔄 In Progress</x:v>
+      </x:c>
+      <x:c r="D46" s="22" t="str">
+        <x:v>Safe PNG/MP4 uploads, private reads, restart/removal and browser checks passed. Adult-business acceptance unconfirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="24" hidden="0" customHeight="1">
       <x:c r="A47" s="16" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="B47" s="17" t="s">
-        <x:v>127</x:v>
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B47" s="17" t="str">
+        <x:v>Model users, creators, posts, subscriptions, plans, transactions and moderation.</x:v>
       </x:c>
       <x:c r="C47" s="24" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -9439,10 +9885,10 @@
     </x:row>
     <x:row r="48" ht="24" hidden="0" customHeight="1">
       <x:c r="A48" s="20" t="s">
-        <x:v>128</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B48" s="21" t="s">
-        <x:v>129</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C48" s="24" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -9453,10 +9899,10 @@
     </x:row>
     <x:row r="49" ht="24" hidden="0" customHeight="1">
       <x:c r="A49" s="16" t="s">
-        <x:v>130</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B49" s="17" t="s">
-        <x:v>131</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C49" s="23" t="inlineStr">
         <x:is>
@@ -9469,10 +9915,10 @@
     </x:row>
     <x:row r="50" ht="24" hidden="0" customHeight="1">
       <x:c r="A50" s="20" t="s">
-        <x:v>132</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B50" s="21" t="s">
-        <x:v>133</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C50" s="24" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -9483,24 +9929,24 @@
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="16" t="s">
-        <x:v>134</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B51" s="17" t="s">
-        <x:v>135</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C51" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D51" s="19" t="s">
-        <x:v>136</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="20" t="s">
-        <x:v>137</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B52" s="21" t="s">
-        <x:v>138</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C52" s="24" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -9511,10 +9957,10 @@
     </x:row>
     <x:row r="53" ht="24" hidden="0" customHeight="1">
       <x:c r="A53" s="16" t="s">
-        <x:v>139</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B53" s="17" t="s">
-        <x:v>140</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C53" s="23" t="inlineStr">
         <x:is>
@@ -9527,21 +9973,21 @@
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="20" t="s">
-        <x:v>141</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B54" s="21" t="s">
-        <x:v>142</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C54" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D54" s="22" t="s">
-        <x:v>143</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="27.75" customHeight="1">
       <x:c r="A55" s="15" t="s">
-        <x:v>144</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B55" s="2"/>
       <x:c r="C55" s="2"/>
@@ -9549,10 +9995,10 @@
     </x:row>
     <x:row r="56" ht="24" hidden="0" customHeight="1">
       <x:c r="A56" s="16" t="s">
-        <x:v>145</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B56" s="17" t="s">
-        <x:v>146</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C56" s="24" t="str">
         <x:v>✅ Done</x:v>
@@ -9563,10 +10009,10 @@
     </x:row>
     <x:row r="57" ht="24" hidden="0" customHeight="1">
       <x:c r="A57" s="20" t="s">
-        <x:v>147</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B57" s="21" t="s">
-        <x:v>148</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C57" s="24" t="str">
         <x:v>✅ Done</x:v>
@@ -9577,10 +10023,10 @@
     </x:row>
     <x:row r="58" ht="24" hidden="0" customHeight="1">
       <x:c r="A58" s="16" t="s">
-        <x:v>149</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B58" s="17" t="s">
-        <x:v>150</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C58" s="24" t="str">
         <x:v>✅ Done</x:v>
@@ -9591,10 +10037,10 @@
     </x:row>
     <x:row r="59" ht="24" hidden="0" customHeight="1">
       <x:c r="A59" s="20" t="s">
-        <x:v>151</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B59" s="21" t="s">
-        <x:v>152</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C59" s="23" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -9605,10 +10051,10 @@
     </x:row>
     <x:row r="60" ht="24" hidden="0" customHeight="1">
       <x:c r="A60" s="16" t="s">
-        <x:v>153</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B60" s="17" t="s">
-        <x:v>154</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C60" s="24" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -9619,10 +10065,10 @@
     </x:row>
     <x:row r="61" ht="24" hidden="0" customHeight="1">
       <x:c r="A61" s="20" t="s">
-        <x:v>155</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B61" s="21" t="s">
-        <x:v>156</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C61" s="24" t="s">
         <x:v>9</x:v>
@@ -9633,10 +10079,10 @@
     </x:row>
     <x:row r="62" ht="24" hidden="0" customHeight="1">
       <x:c r="A62" s="16" t="s">
-        <x:v>157</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B62" s="17" t="s">
-        <x:v>158</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C62" s="24" t="s">
         <x:v>9</x:v>
@@ -9647,7 +10093,7 @@
     </x:row>
     <x:row r="63" ht="27.75" customHeight="1">
       <x:c r="A63" s="15" t="s">
-        <x:v>159</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B63" s="2"/>
       <x:c r="C63" s="2"/>
@@ -9655,80 +10101,80 @@
     </x:row>
     <x:row r="64" ht="15.75" customHeight="1">
       <x:c r="A64" s="16" t="s">
-        <x:v>160</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B64" s="17" t="s">
-        <x:v>161</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C64" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D64" s="19" t="s">
-        <x:v>162</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15.75" customHeight="1">
       <x:c r="A65" s="20" t="s">
-        <x:v>163</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B65" s="21" t="s">
-        <x:v>164</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C65" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D65" s="22" t="s">
-        <x:v>165</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15.75" customHeight="1">
       <x:c r="A66" s="16" t="s">
-        <x:v>166</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B66" s="17" t="s">
-        <x:v>167</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C66" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D66" s="19" t="s">
-        <x:v>168</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15.75" customHeight="1">
       <x:c r="A67" s="20" t="s">
-        <x:v>169</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B67" s="21" t="s">
-        <x:v>170</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C67" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D67" s="22" t="s">
-        <x:v>171</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15.75" customHeight="1">
       <x:c r="A68" s="16" t="s">
-        <x:v>172</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B68" s="17" t="s">
-        <x:v>173</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C68" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D68" s="19" t="s">
-        <x:v>174</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="24" hidden="0" customHeight="1">
       <x:c r="A69" s="20" t="s">
-        <x:v>175</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B69" s="21" t="s">
-        <x:v>176</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C69" s="23" t="str">
         <x:v>✅ Done</x:v>
@@ -9739,10 +10185,10 @@
     </x:row>
     <x:row r="70" ht="15.75" customHeight="1">
       <x:c r="A70" s="16" t="s">
-        <x:v>177</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B70" s="17" t="s">
-        <x:v>178</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C70" s="18" t="str">
         <x:v>✅ Done</x:v>
@@ -9753,10 +10199,10 @@
     </x:row>
     <x:row r="71" ht="15.75" customHeight="1">
       <x:c r="A71" s="20" t="s">
-        <x:v>179</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B71" s="21" t="s">
-        <x:v>180</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C71" s="23" t="inlineStr">
         <x:is>
@@ -9771,10 +10217,10 @@
     </x:row>
     <x:row r="72" ht="15.75" customHeight="1">
       <x:c r="A72" s="16" t="s">
-        <x:v>181</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B72" s="17" t="s">
-        <x:v>182</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C72" s="23" t="inlineStr">
         <x:is>
@@ -9789,10 +10235,10 @@
     </x:row>
     <x:row r="73" ht="15.75" customHeight="1">
       <x:c r="A73" s="20" t="s">
-        <x:v>183</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B73" s="21" t="s">
-        <x:v>184</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C73" s="23" t="s">
         <x:v>26</x:v>
@@ -9805,23 +10251,21 @@
     </x:row>
     <x:row r="74" ht="15.75" customHeight="1">
       <x:c r="A74" s="16" t="s">
-        <x:v>185</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B74" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C74" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D74" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Launch-critical. UI prototype exists. Requires service configuration, availability, Veso booking, cancellation, reviews, and disputes.</x:t>
-        </x:is>
+      <x:c r="D74" s="22" t="str">
+        <x:v>Launch-critical. UI prototype exists. Requires service configuration, availability, payment rules, cancellation, reviews and disputes.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15.75" customHeight="1">
       <x:c r="A75" s="20" t="s">
-        <x:v>187</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B75" s="17" t="inlineStr">
         <x:is>
@@ -9840,26 +10284,14 @@
       </x:c>
     </x:row>
     <x:row r="76" ht="15.75" customHeight="1">
-      <x:c r="A76" s="16" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="B76" s="17" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="C76" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">🔄 In Progress</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D76" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wallet UI prototype exists. Add/recharge Veso needs an E-Pal Buff-inspired design plus real ledger/payment integration.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A76" s="16"/>
+      <x:c r="B76" s="17"/>
+      <x:c r="C76" s="23"/>
+      <x:c r="D76" s="22"/>
     </x:row>
     <x:row r="77" ht="24" hidden="0" customHeight="1">
       <x:c r="A77" s="20" t="s">
-        <x:v>190</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B77" s="17" t="inlineStr">
         <x:is>
@@ -9875,94 +10307,94 @@
     </x:row>
     <x:row r="78" ht="24" hidden="0" customHeight="1">
       <x:c r="A78" s="16" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="B78" s="17" t="s">
-        <x:v>192</x:v>
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B78" s="17" t="str">
+        <x:v>Account info, password change, notification preferences, theme toggle (Sakura Kiss / Midnight City), NSFW content toggle, payment/billing section.</x:v>
       </x:c>
       <x:c r="C78" s="24" t="str">
         <x:v>🔄 In Progress</x:v>
       </x:c>
       <x:c r="D78" s="19" t="str">
-        <x:v>Protected Settings is implemented for display name, email/reverification, password, active sessions, and explicit-content preference. Notifications, theme, billing, export, and deletion remain deferred to dependency phases.</x:v>
+        <x:v>Protected Settings implements display name, email/reverification, password, active sessions and explicit-content preference. Theme selection is implemented browser-locally. Account theme sync, real notifications/billing, export and deletion remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15.75" customHeight="1">
       <x:c r="A79" s="20" t="s">
-        <x:v>193</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B79" s="21" t="s">
-        <x:v>194</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C79" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D79" s="22" t="s">
-        <x:v>195</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15.75" customHeight="1">
       <x:c r="A80" s="16" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="B80" s="17" t="s">
-        <x:v>197</x:v>
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B80" s="17" t="str">
+        <x:v>Member activity history: posts liked, content purchased, subscriptions and payment history. Lower priority.</x:v>
       </x:c>
       <x:c r="C80" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D80" s="19" t="s">
-        <x:v>198</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15.75" customHeight="1">
       <x:c r="A81" s="20" t="s">
-        <x:v>199</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B81" s="21" t="s">
-        <x:v>200</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C81" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D81" s="22" t="s">
-        <x:v>201</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15.75" customHeight="1">
       <x:c r="A82" s="16" t="s">
-        <x:v>202</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B82" s="17" t="s">
-        <x:v>203</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C82" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D82" s="19" t="s">
-        <x:v>204</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15.75" customHeight="1">
       <x:c r="A83" s="20" t="s">
-        <x:v>205</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B83" s="21" t="s">
-        <x:v>206</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C83" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D83" s="22" t="s">
-        <x:v>207</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="30.75" customHeight="1">
       <x:c r="A84" s="16" t="s">
-        <x:v>208</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B84" s="17" t="s">
-        <x:v>209</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C84" s="23" t="inlineStr">
         <x:is>
@@ -9977,21 +10409,21 @@
     </x:row>
     <x:row r="85" ht="18.75" customHeight="1">
       <x:c r="A85" s="25" t="s">
-        <x:v>210</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B85" s="26" t="s">
-        <x:v>211</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C85" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D85" s="27" t="s">
-        <x:v>212</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15.75" customHeight="1">
       <x:c r="A86" s="15" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B86" s="2"/>
       <x:c r="C86" s="2"/>
@@ -9999,91 +10431,91 @@
     </x:row>
     <x:row r="87" ht="15.75" customHeight="1">
       <x:c r="A87" s="16" t="s">
-        <x:v>214</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B87" s="17" t="s">
-        <x:v>215</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C87" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D87" s="19" t="s">
-        <x:v>216</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15.75" customHeight="1">
       <x:c r="A88" s="20" t="s">
-        <x:v>217</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B88" s="21" t="s">
-        <x:v>218</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C88" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D88" s="22" t="s">
-        <x:v>219</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15.75" customHeight="1">
       <x:c r="A89" s="16" t="s">
-        <x:v>220</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B89" s="17" t="s">
-        <x:v>221</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C89" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D89" s="19" t="s">
-        <x:v>222</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15.75" customHeight="1">
       <x:c r="A90" s="20" t="s">
-        <x:v>223</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B90" s="21" t="s">
-        <x:v>224</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C90" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D90" s="22" t="s">
-        <x:v>225</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15.75" customHeight="1">
       <x:c r="A91" s="16" t="s">
-        <x:v>226</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B91" s="17" t="s">
-        <x:v>227</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C91" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D91" s="19" t="s">
-        <x:v>228</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="27.75" customHeight="1">
       <x:c r="A92" s="28" t="s">
-        <x:v>229</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B92" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C92" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D92" s="31" t="s">
-        <x:v>231</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15.75" customHeight="1">
       <x:c r="A93" s="15" t="s">
-        <x:v>232</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B93" s="2"/>
       <x:c r="C93" s="2"/>
@@ -10091,136 +10523,116 @@
     </x:row>
     <x:row r="94" ht="15.75" customHeight="1">
       <x:c r="A94" s="32" t="s">
-        <x:v>233</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B94" s="33" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C94" s="24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">📋 Not Started</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D94" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Processor selected, but merchant application and API/webhook integration have not started.</x:t>
-        </x:is>
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="C94" s="217" t="str">
+        <x:v>🔄 In Progress</x:v>
+      </x:c>
+      <x:c r="D94" s="22" t="str">
+        <x:v>Sales replied; review site is being built. Merchant approval, API/webhooks and billing remain unimplemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15.75" customHeight="1">
       <x:c r="A95" s="20" t="s">
-        <x:v>235</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B95" s="21" t="s">
-        <x:v>236</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C95" s="24" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">📋 Not Started</x:t>
         </x:is>
       </x:c>
-      <x:c r="D95" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fallback provider selected, but application and technical integration have not started.</x:t>
-        </x:is>
+      <x:c r="D95" s="19" t="str">
+        <x:v>CCBill site prep underway. Epoch outreach, account approval and integration remain unstarted.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15.75" customHeight="1">
       <x:c r="A96" s="16" t="s">
-        <x:v>237</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B96" s="17" t="s">
-        <x:v>238</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C96" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D96" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Do not implement until CCBill and Epoch confirm the account-specific cascade design in writing.</x:t>
-        </x:is>
+      <x:c r="D96" s="22" t="str">
+        <x:v>CCBill site prep underway. Cascade needs written account-specific confirmation from both processors.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15.75" customHeight="1">
       <x:c r="A97" s="20" t="s">
-        <x:v>239</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B97" s="21" t="s">
-        <x:v>240</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C97" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D97" s="22" t="s">
-        <x:v>241</x:v>
+      <x:c r="D97" s="22" t="str">
+        <x:v>CCBill site prep underway. Billing awaits agreed payment flow, processor approval and trusted payment events.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15.75" customHeight="1">
       <x:c r="A98" s="16" t="s">
-        <x:v>242</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B98" s="17" t="s">
-        <x:v>243</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C98" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D98" s="19" t="s">
-        <x:v>244</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15.75" customHeight="1">
       <x:c r="A99" s="20" t="s">
-        <x:v>245</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B99" s="21" t="s">
-        <x:v>246</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C99" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D99" s="22" t="s">
-        <x:v>247</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15.75" customHeight="1">
       <x:c r="A100" s="16" t="s">
-        <x:v>248</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B100" s="17" t="s">
-        <x:v>249</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C100" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D100" s="19" t="s">
-        <x:v>250</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15.75" customHeight="1">
-      <x:c r="A101" s="20" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="B101" s="21" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="C101" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">🔄 In Progress</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D101" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Direction locked: prepaid credits, 1 Veso = 1 USD. Refund, transfer, expiration, promotional credit, and ledger policies remain.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A101" s="20"/>
+      <x:c r="B101" s="21"/>
+      <x:c r="C101" s="23"/>
+      <x:c r="D101" s="19"/>
     </x:row>
     <x:row r="102" ht="15.75" customHeight="1">
       <x:c r="A102" s="16" t="s">
-        <x:v>253</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B102" s="17" t="s">
-        <x:v>254</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C102" s="24" t="s">
         <x:v>21</x:v>
@@ -10233,35 +10645,35 @@
     </x:row>
     <x:row r="103" ht="15.75" customHeight="1">
       <x:c r="A103" s="20" t="s">
-        <x:v>255</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B103" s="21" t="s">
-        <x:v>256</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C103" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D103" s="22" t="s">
-        <x:v>257</x:v>
+      <x:c r="D103" s="22" t="str">
+        <x:v>CCBill site prep underway. Dispute workflow awaits processor rules/events and authorized operations.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="27.75" customHeight="1">
       <x:c r="A104" s="36" t="s">
-        <x:v>258</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B104" s="37" t="s">
-        <x:v>259</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C104" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D104" s="38" t="s">
-        <x:v>260</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15.75" customHeight="1">
       <x:c r="A105" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B105" s="2"/>
       <x:c r="C105" s="2"/>
@@ -10283,38 +10695,38 @@
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="20" t="s">
-        <x:v>262</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B107" s="21" t="s">
-        <x:v>263</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C107" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D107" s="22" t="s">
-        <x:v>264</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
       <x:c r="A108" s="16" t="s">
-        <x:v>265</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B108" s="17" t="s">
-        <x:v>266</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C108" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D108" s="19" t="s">
-        <x:v>267</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="24" hidden="0" customHeight="1">
       <x:c r="A109" s="20" t="s">
-        <x:v>268</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B109" s="21" t="s">
-        <x:v>269</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C109" s="24" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -10325,122 +10737,114 @@
     </x:row>
     <x:row r="110" ht="15.75" customHeight="1">
       <x:c r="A110" s="16" t="s">
-        <x:v>270</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B110" s="17" t="s">
-        <x:v>271</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C110" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D110" s="19" t="s">
-        <x:v>272</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15.75" customHeight="1">
       <x:c r="A111" s="20" t="s">
-        <x:v>273</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B111" s="21" t="s">
-        <x:v>274</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D111" s="22" t="s">
-        <x:v>275</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15.75" customHeight="1">
       <x:c r="A112" s="16" t="s">
-        <x:v>276</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B112" s="17" t="s">
-        <x:v>277</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D112" s="19" t="s">
-        <x:v>278</x:v>
+      <x:c r="D112" s="19" t="str">
+        <x:v>CCBill site prep underway. Admin view awaits payment/payout data and private-operations controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15.75" customHeight="1">
       <x:c r="A113" s="20" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="B113" s="21" t="s">
-        <x:v>280</x:v>
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B113" s="21" t="str">
+        <x:v>View verified processor chargeback events, calculate rates, apply confirmed account-specific alert thresholds and log authorized dispute responses.</x:v>
       </x:c>
       <x:c r="C113" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D113" s="22" t="s">
-        <x:v>281</x:v>
+      <x:c r="D113" s="22" t="str">
+        <x:v>CCBill site prep underway. Dashboard awaits verified dispute events and account-specific alert thresholds.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15.75" customHeight="1">
-      <x:c r="A114" s="16" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="B114" s="17" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="C114" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D114" s="19" t="s">
-        <x:v>284</x:v>
-      </x:c>
+      <x:c r="A114" s="16"/>
+      <x:c r="B114" s="17"/>
+      <x:c r="C114" s="24"/>
+      <x:c r="D114" s="19"/>
     </x:row>
     <x:row r="115" ht="15.75" customHeight="1">
       <x:c r="A115" s="20" t="s">
-        <x:v>285</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B115" s="21" t="s">
-        <x:v>286</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C115" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D115" s="22" t="s">
-        <x:v>287</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15.75" customHeight="1">
       <x:c r="A116" s="16" t="s">
-        <x:v>288</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B116" s="17" t="s">
-        <x:v>289</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C116" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D116" s="19" t="s">
-        <x:v>290</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15.75" customHeight="1">
       <x:c r="A117" s="20" t="s">
-        <x:v>291</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B117" s="21" t="s">
-        <x:v>292</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C117" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D117" s="22" t="s">
-        <x:v>293</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="24" hidden="0" customHeight="1">
       <x:c r="A118" s="36" t="s">
-        <x:v>294</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B118" s="37" t="s">
-        <x:v>295</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C118" s="30" t="s">
         <x:v>21</x:v>
@@ -10451,7 +10855,7 @@
     </x:row>
     <x:row r="119" ht="15.75" customHeight="1">
       <x:c r="A119" s="15" t="s">
-        <x:v>296</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B119" s="2"/>
       <x:c r="C119" s="2"/>
@@ -10459,10 +10863,10 @@
     </x:row>
     <x:row r="120" ht="15.75" customHeight="1">
       <x:c r="A120" s="32" t="s">
-        <x:v>297</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B120" s="33" t="s">
-        <x:v>298</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C120" s="39" t="s">
         <x:v>21</x:v>
@@ -10473,52 +10877,52 @@
     </x:row>
     <x:row r="121" ht="15.75" customHeight="1">
       <x:c r="A121" s="20" t="s">
-        <x:v>299</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B121" s="21" t="s">
-        <x:v>300</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C121" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D121" s="22" t="s">
-        <x:v>301</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15.75" customHeight="1">
       <x:c r="A122" s="16" t="s">
-        <x:v>302</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B122" s="17" t="s">
-        <x:v>303</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C122" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D122" s="19" t="s">
-        <x:v>304</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15.75" customHeight="1">
       <x:c r="A123" s="20" t="s">
-        <x:v>305</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B123" s="21" t="s">
-        <x:v>306</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C123" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D123" s="22" t="s">
-        <x:v>307</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="24" hidden="0" customHeight="1">
       <x:c r="A124" s="36" t="s">
-        <x:v>308</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B124" s="37" t="s">
-        <x:v>309</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C124" s="30" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -10529,7 +10933,7 @@
     </x:row>
     <x:row r="125" ht="15.75" customHeight="1">
       <x:c r="A125" s="15" t="s">
-        <x:v>310</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B125" s="2"/>
       <x:c r="C125" s="2"/>
@@ -10537,105 +10941,105 @@
     </x:row>
     <x:row r="126" ht="15.75" customHeight="1">
       <x:c r="A126" s="32" t="s">
-        <x:v>311</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B126" s="33" t="s">
-        <x:v>312</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C126" s="39" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D126" s="35" t="s">
-        <x:v>313</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15.75" customHeight="1">
       <x:c r="A127" s="20" t="s">
-        <x:v>314</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B127" s="21" t="s">
-        <x:v>315</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C127" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D127" s="22" t="s">
-        <x:v>316</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15.75" customHeight="1">
       <x:c r="A128" s="16" t="s">
-        <x:v>317</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B128" s="17" t="s">
-        <x:v>318</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C128" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D128" s="19" t="s">
-        <x:v>319</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15.75" customHeight="1">
       <x:c r="A129" s="20" t="s">
-        <x:v>320</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B129" s="21" t="s">
-        <x:v>321</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C129" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D129" s="22" t="s">
-        <x:v>322</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15.75" customHeight="1">
       <x:c r="A130" s="16" t="s">
-        <x:v>323</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B130" s="17" t="s">
-        <x:v>324</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C130" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D130" s="19" t="s">
-        <x:v>325</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" customHeight="1">
       <x:c r="A131" s="20" t="s">
-        <x:v>326</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B131" s="21" t="s">
-        <x:v>327</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C131" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D131" s="22" t="s">
-        <x:v>328</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15.75" customHeight="1">
       <x:c r="A132" s="40" t="s">
-        <x:v>329</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B132" s="41" t="s">
-        <x:v>330</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C132" s="42" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D132" s="43" t="s">
-        <x:v>325</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15.75" customHeight="1">
       <x:c r="A133" s="15" t="s">
-        <x:v>331</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B133" s="2"/>
       <x:c r="C133" s="2"/>
@@ -10643,10 +11047,10 @@
     </x:row>
     <x:row r="134" ht="24" hidden="0" customHeight="1">
       <x:c r="A134" s="32" t="s">
-        <x:v>332</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B134" s="33" t="s">
-        <x:v>333</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C134" s="44" t="s">
         <x:v>26</x:v>
@@ -10657,100 +11061,100 @@
     </x:row>
     <x:row r="135" ht="15.75" customHeight="1">
       <x:c r="A135" s="20" t="s">
-        <x:v>334</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B135" s="21" t="s">
-        <x:v>335</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C135" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D135" s="22" t="s">
-        <x:v>336</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15.75" customHeight="1">
       <x:c r="A136" s="16" t="s">
-        <x:v>337</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B136" s="17" t="s">
-        <x:v>338</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C136" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D136" s="19" t="s">
-        <x:v>339</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15.75" customHeight="1">
       <x:c r="A137" s="20" t="s">
-        <x:v>340</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B137" s="21" t="s">
-        <x:v>341</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C137" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D137" s="22" t="s">
-        <x:v>325</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15.75" customHeight="1">
       <x:c r="A138" s="16" t="s">
-        <x:v>342</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B138" s="17" t="s">
-        <x:v>343</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C138" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D138" s="19" t="s">
-        <x:v>344</x:v>
+      <x:c r="D138" s="19" t="str">
+        <x:v>CCBill site prep underway. Testing awaits implemented processor flows; cascade only if confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15.75" customHeight="1">
       <x:c r="A139" s="20" t="s">
-        <x:v>345</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B139" s="21" t="s">
-        <x:v>346</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C139" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D139" s="22" t="s">
-        <x:v>347</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15.75" customHeight="1">
       <x:c r="A140" s="16" t="s">
-        <x:v>348</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B140" s="17" t="s">
-        <x:v>349</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C140" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D140" s="19" t="s">
-        <x:v>350</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15.75" customHeight="1">
       <x:c r="A141" s="20" t="s">
-        <x:v>351</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B141" s="21" t="s">
-        <x:v>352</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C141" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D141" s="22" t="s">
-        <x:v>353</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="27.75" customHeight="1">
@@ -10764,48 +11168,16 @@
       <x:c r="D142" s="3"/>
     </x:row>
     <x:row r="143" ht="31.5" customHeight="1">
-      <x:c r="A143" s="16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build Veso recharge UI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B143" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Design and implement Add/Recharge Vesos with presets, payment summary, receipt, and transaction history. Visual reference: E-Pal Buff recharge.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C143" s="24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">📋 Not Started</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D143" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Launch-critical. 1 Veso = 1 USD.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A143" s="16"/>
+      <x:c r="B143" s="17"/>
+      <x:c r="C143" s="24"/>
+      <x:c r="D143" s="19"/>
     </x:row>
     <x:row r="144" ht="31.5" customHeight="1">
-      <x:c r="A144" s="20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Define Veso terms and ledger policies</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B144" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Define purchased vs promotional Veso, refunds, expiration, transfer, account closure, chargebacks, and creator earnings conversion.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C144" s="23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">🔄 In Progress</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D144" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use E-Pal as product research only; draft independent policies for Pumdoki with processor/legal review.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A144" s="20"/>
+      <x:c r="B144" s="21"/>
+      <x:c r="C144" s="23"/>
+      <x:c r="D144" s="22"/>
     </x:row>
     <x:row r="145" ht="31.5" customHeight="1">
       <x:c r="A145" s="16" t="inlineStr">
@@ -10813,10 +11185,8 @@
           <x:t xml:space="preserve">Implement tipping / Send Love</x:t>
         </x:is>
       </x:c>
-      <x:c r="B145" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Allow members to tip creators using Veso with idempotent ledger transfers and creator pending earnings.</x:t>
-        </x:is>
+      <x:c r="B145" s="17" t="str">
+        <x:v>Allow members to tip creators with idempotent payment evidence and creator pending earnings. Payment method remains unresolved.</x:v>
       </x:c>
       <x:c r="C145" s="24" t="inlineStr">
         <x:is>
@@ -10835,10 +11205,8 @@
           <x:t xml:space="preserve">Implement PPV purchases</x:t>
         </x:is>
       </x:c>
-      <x:c r="B146" s="21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Allow members to unlock individual creator content with Veso and durable entitlement records.</x:t>
-        </x:is>
+      <x:c r="B146" s="21" t="str">
+        <x:v>Allow members to unlock individual creator content with durable entitlement records. Payment method remains unresolved.</x:v>
       </x:c>
       <x:c r="C146" s="24" t="inlineStr">
         <x:is>
@@ -10901,10 +11269,8 @@
           <x:t xml:space="preserve">Complete Connect for launch</x:t>
         </x:is>
       </x:c>
-      <x:c r="B149" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implement service setup, schedules, time zones, Veso booking, confirmations, cancellations, disputes, and reviews.</x:t>
-        </x:is>
+      <x:c r="B149" s="17" t="str">
+        <x:v>Implement service setup, schedules, time zones, payment rules, confirmations, cancellations, disputes and reviews.</x:v>
       </x:c>
       <x:c r="C149" s="23" t="inlineStr">
         <x:is>
@@ -11225,10 +11591,8 @@
           <x:t xml:space="preserve">📋 Not Started</x:t>
         </x:is>
       </x:c>
-      <x:c r="D164" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Merchant applications have not started.</x:t>
-        </x:is>
+      <x:c r="D164" s="22" t="str">
+        <x:v>CCBill Sales replied; site prep underway. Written cascade confirmation and Epoch outreach remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15.75" customHeight="1"/>
@@ -12104,50 +12468,50 @@
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
       <x:c r="A1" s="14" t="s">
-        <x:v>354</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B1" s="14" t="s">
-        <x:v>355</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C1" s="14" t="s">
-        <x:v>356</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="D1" s="14" t="s">
-        <x:v>357</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E1" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="14" t="s">
-        <x:v>358</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20" t="s">
-        <x:v>359</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B2" s="21" t="s">
-        <x:v>360</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C2" s="21" t="s">
-        <x:v>361</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="D2" s="21" t="s">
-        <x:v>362</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E2" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F2" s="21" t="s">
-        <x:v>363</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="16" t="s">
-        <x:v>364</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B3" s="17" t="s">
-        <x:v>360</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C3" s="21" t="inlineStr">
         <x:is>
@@ -12155,7 +12519,7 @@
         </x:is>
       </x:c>
       <x:c r="D3" s="17" t="s">
-        <x:v>362</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E3" s="24" t="s">
         <x:v>21</x:v>
@@ -12168,10 +12532,10 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="20" t="s">
-        <x:v>365</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B4" s="21" t="s">
-        <x:v>366</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C4" s="21" t="inlineStr">
         <x:is>
@@ -12196,10 +12560,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="16" t="s">
-        <x:v>367</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
-        <x:v>366</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C5" s="17" t="inlineStr">
         <x:is>
@@ -12224,70 +12588,70 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="s">
-        <x:v>368</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>369</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="C6" s="21" t="s">
-        <x:v>370</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D6" s="21" t="s">
-        <x:v>362</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E6" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="21" t="s">
-        <x:v>363</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="16" t="s">
-        <x:v>371</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B7" s="17" t="s">
-        <x:v>372</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C7" s="17" t="s">
-        <x:v>373</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="D7" s="17" t="s">
-        <x:v>374</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E7" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="17" t="s">
-        <x:v>363</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="20" t="s">
-        <x:v>375</x:v>
+      <x:c r="A8" s="20" t="str">
+        <x:v>Multiple themes (beyond Sakura Kiss &amp; Midnight City)</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
-        <x:v>376</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C8" s="21" t="s">
-        <x:v>377</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="D8" s="21" t="s">
-        <x:v>374</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E8" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="21" t="s">
-        <x:v>378</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="16" t="s">
-        <x:v>379</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B9" s="17" t="s">
-        <x:v>360</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C9" s="17" t="inlineStr">
         <x:is>
@@ -12312,162 +12676,162 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="20" t="s">
-        <x:v>380</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B10" s="21" t="s">
-        <x:v>366</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C10" s="21" t="s">
-        <x:v>381</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="D10" s="21" t="s">
-        <x:v>362</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E10" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="21" t="s">
-        <x:v>382</x:v>
+        <x:v>358</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="16" t="s">
-        <x:v>383</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B11" s="17" t="s">
-        <x:v>366</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
-        <x:v>384</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="D11" s="17" t="s">
-        <x:v>362</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E11" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F11" s="17" t="s">
-        <x:v>385</x:v>
+        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="20" t="s">
-        <x:v>386</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B12" s="21" t="s">
-        <x:v>387</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C12" s="21" t="s">
-        <x:v>388</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D12" s="21" t="s">
-        <x:v>362</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E12" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F12" s="21" t="s">
-        <x:v>389</x:v>
+        <x:v>365</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="16" t="s">
-        <x:v>390</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B13" s="17" t="s">
-        <x:v>391</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C13" s="17" t="s">
-        <x:v>392</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="D13" s="17" t="s">
-        <x:v>393</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E13" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F13" s="17" t="s">
-        <x:v>394</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="20" t="s">
-        <x:v>395</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B14" s="21" t="s">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s">
-        <x:v>397</x:v>
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="str">
+        <x:v>Activity history for members: posts liked, content purchased and payment history.</x:v>
       </x:c>
       <x:c r="D14" s="21" t="s">
-        <x:v>374</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E14" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F14" s="21" t="s">
-        <x:v>398</x:v>
+        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="45" t="s">
-        <x:v>399</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B15" s="46" t="s">
-        <x:v>400</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C15" s="47" t="s">
-        <x:v>401</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D15" s="46" t="s">
-        <x:v>362</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E15" s="48" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F15" s="47" t="s">
-        <x:v>402</x:v>
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="49" t="s">
-        <x:v>403</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B16" s="50" t="s">
-        <x:v>404</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C16" s="51" t="s">
-        <x:v>405</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="D16" s="50" t="s">
-        <x:v>374</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E16" s="48" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F16" s="51" t="s">
-        <x:v>406</x:v>
+        <x:v>381</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="52" t="s">
-        <x:v>407</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B17" s="53" t="s">
-        <x:v>376</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C17" s="54" t="s">
-        <x:v>408</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="D17" s="53" t="s">
-        <x:v>374</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E17" s="48" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F17" s="54" t="s">
-        <x:v>409</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -13466,21 +13830,21 @@
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B3" s="14" t="s">
-        <x:v>412</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="55" t="s">
-        <x:v>413</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B4" s="58" t="str">
         <x:v>This workbook is reconciled with the repository, founder decisions, and merged PR #1–#3 baseline through August 16, 2026.</x:v>
@@ -13488,204 +13852,200 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="57" t="s">
-        <x:v>414</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B5" s="58" t="s">
-        <x:v>415</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="55" t="s">
-        <x:v>416</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B6" s="56" t="s">
-        <x:v>417</x:v>
+        <x:v>392</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="57" t="s">
-        <x:v>418</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B7" s="58" t="s">
-        <x:v>419</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="55" t="s">
-        <x:v>420</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B8" s="56" t="s">
-        <x:v>421</x:v>
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="57" t="s">
-        <x:v>422</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B9" s="58" t="s">
-        <x:v>423</x:v>
+        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="55" t="s">
-        <x:v>424</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B10" s="56" t="s">
-        <x:v>425</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="57" t="s">
-        <x:v>426</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B11" s="58" t="s">
-        <x:v>427</x:v>
+        <x:v>402</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="55" t="s">
-        <x:v>428</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B12" s="56" t="s">
-        <x:v>429</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="57" t="s">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="B13" s="58" t="s">
-        <x:v>431</x:v>
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B13" s="58" t="str">
+        <x:v>Phase 6 expanded — added: NSFW toggle, Settings, Help/Support, Activity, modal/drawer/chat fixes, creator dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="55" t="s">
-        <x:v>432</x:v>
-      </x:c>
-      <x:c r="B14" s="56" t="s">
-        <x:v>433</x:v>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B14" s="56" t="str">
+        <x:v>Midnight City is implemented as the second free default theme alongside Sakura Kiss, with browser-local selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="57" t="s">
-        <x:v>434</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B15" s="58" t="s">
-        <x:v>435</x:v>
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="s">
-        <x:v>436</x:v>
+        <x:v>409</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B18" s="60" t="s">
-        <x:v>438</x:v>
+        <x:v>411</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B19" s="60" t="s">
-        <x:v>439</x:v>
+        <x:v>412</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B20" s="60" t="s">
-        <x:v>440</x:v>
+        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
       <x:c r="A21" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B21" s="60" t="s">
-        <x:v>441</x:v>
+        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15.75" customHeight="1">
       <x:c r="A22" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B22" s="60" t="s">
-        <x:v>442</x:v>
+        <x:v>415</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">
-      <x:c r="A23" s="59" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="B23" s="60" t="s">
-        <x:v>443</x:v>
-      </x:c>
+      <x:c r="A23" s="59"/>
+      <x:c r="B23" s="60"/>
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
       <x:c r="A24" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B24" s="60" t="s">
-        <x:v>444</x:v>
+        <x:v>416</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1">
       <x:c r="A25" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B25" s="60" t="s">
-        <x:v>445</x:v>
+        <x:v>417</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15.75" customHeight="1">
       <x:c r="A26" s="59" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="B26" s="60" t="s">
-        <x:v>446</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B26" s="60" t="str">
+        <x:v>CCBill is the intended primary processor. Sales has replied; merchant/model approval and technical integration remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
       <x:c r="A27" s="59" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="B27" s="60" t="s">
-        <x:v>447</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B27" s="60" t="str">
+        <x:v>Epoch is the intended fallback. Outreach and account-specific cascade confirmation remain pending; no routing is implemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15.75" customHeight="1">
       <x:c r="A28" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B28" s="60" t="s">
-        <x:v>448</x:v>
+        <x:v>418</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
       <x:c r="A29" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B29" s="60" t="s">
-        <x:v>449</x:v>
+        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15.75" customHeight="1">
       <x:c r="A30" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B30" s="60" t="s">
-        <x:v>450</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A31" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B31" s="60" t="str">
         <x:v>Admin operations: separate apps/admin shell; no public /admin. Public ADMIN sessions are insufficient for operations access. The dormant review router stays unmounted until signed operations identity, exact provisioning, phishing-resistant hardware-backed assurance, private-origin/CSRF, trusted-proxy, restricted DB-role, audit, and recovery gates pass.</x:v>
@@ -13693,79 +14053,79 @@
     </x:row>
     <x:row r="32" ht="15.75" customHeight="1">
       <x:c r="A32" s="59" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="B32" s="60" t="s">
-        <x:v>451</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B32" s="60" t="str">
+        <x:v>Midnight City: blue city rooftops, static desktop/mobile JPGs. Browser-local Settings selection implemented; account sync pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1">
       <x:c r="A33" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B33" s="60" t="s">
-        <x:v>452</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1">
       <x:c r="A34" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B34" s="60" t="s">
-        <x:v>453</x:v>
+        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15.75" customHeight="1">
       <x:c r="A35" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B35" s="60" t="s">
-        <x:v>454</x:v>
+        <x:v>423</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
       <x:c r="A36" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B36" s="60" t="s">
-        <x:v>455</x:v>
+        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15.75" customHeight="1">
       <x:c r="A37" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B37" s="60" t="s">
-        <x:v>456</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15.75" customHeight="1">
       <x:c r="A38" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B38" s="60" t="s">
-        <x:v>457</x:v>
+        <x:v>426</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15.75" customHeight="1">
       <x:c r="A39" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B39" s="60" t="s">
-        <x:v>458</x:v>
+        <x:v>427</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15.75" customHeight="1">
       <x:c r="A40" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B40" s="60" t="s">
-        <x:v>459</x:v>
+        <x:v>428</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15.75" customHeight="1">
       <x:c r="A41" s="59" t="s">
-        <x:v>437</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B41" s="60" t="inlineStr">
         <x:is>
@@ -14014,10 +14374,8 @@
           <x:t xml:space="preserve">•</x:t>
         </x:is>
       </x:c>
-      <x:c r="B71" s="66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CCBill and Epoch merchant applications have not started and will proceed in parallel.</x:t>
-        </x:is>
+      <x:c r="B71" s="66" t="str">
+        <x:v>CCBill Sales replied and functioning-site preparation is underway. Password protection is permitted. Epoch outreach remains pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="28.5" customHeight="1">
@@ -14033,28 +14391,12 @@
       </x:c>
     </x:row>
     <x:row r="73" ht="28.5" customHeight="1">
-      <x:c r="A73" s="65" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">•</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B73" s="66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Veso is prepaid platform credit: 1 Veso = 1 USD.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A73" s="65"/>
+      <x:c r="B73" s="66"/>
     </x:row>
     <x:row r="74" ht="28.5" customHeight="1">
-      <x:c r="A74" s="65" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">•</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B74" s="66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">E-Pal Buff is a product reference for recharge and behavior; Pumdoki needs independently drafted terms.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A74" s="65"/>
+      <x:c r="B74" s="66"/>
     </x:row>
     <x:row r="75" ht="28.5" customHeight="1">
       <x:c r="A75" s="65" t="inlineStr">
@@ -14192,10 +14534,8 @@
           <x:t xml:space="preserve">•</x:t>
         </x:is>
       </x:c>
-      <x:c r="B86" s="66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Store purchases use Veso.</x:t>
-        </x:is>
+      <x:c r="B86" s="66" t="str">
+        <x:v>Store purchases remain launch scope. Payment method is unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="28.5" customHeight="1">
@@ -14204,10 +14544,8 @@
           <x:t xml:space="preserve">•</x:t>
         </x:is>
       </x:c>
-      <x:c r="B87" s="66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Connect bookings use Veso.</x:t>
-        </x:is>
+      <x:c r="B87" s="66" t="str">
+        <x:v>Connect remains launch scope. Payment and service rules need definition.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="28.5" customHeight="1">
@@ -14320,7 +14658,7 @@
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
       <x:c r="A97" s="161" t="str">
-        <x:v>Historical/current boundary: rows 1–96 preserve the August 16 baseline; current operating notes begin below.</x:v>
+        <x:v>Rows 1–96 retain historical context except scope removed by founder instruction; current operating notes begin below.</x:v>
       </x:c>
       <x:c r="B97" s="161"/>
     </x:row>
@@ -15326,7 +15664,7 @@
   <x:sheetData>
     <x:row r="1" ht="39.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -15336,36 +15674,36 @@
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="3"/>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="13" t="str">
-        <x:v>Historical estimates; use Launch Budget for current planning. Maryland LLC filing reported September 8, 2026; exact filing date and actual invoice amount unverified.</x:v>
-      </x:c>
-      <x:c r="B2" s="2"/>
-      <x:c r="C2" s="2"/>
-      <x:c r="D2" s="2"/>
-      <x:c r="E2" s="2"/>
-      <x:c r="F2" s="2"/>
-      <x:c r="G2" s="2"/>
-      <x:c r="H2" s="3"/>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="205" t="str">
+        <x:v>USD. Estimated costs are historical; see Launch Budget for planning. Actual purchases below were confirmed by the founder September 10, 2026. Transaction dates were not supplied.</x:v>
+      </x:c>
+      <x:c r="B2" s="206"/>
+      <x:c r="C2" s="206"/>
+      <x:c r="D2" s="206"/>
+      <x:c r="E2" s="206"/>
+      <x:c r="F2" s="206"/>
+      <x:c r="G2" s="206"/>
+      <x:c r="H2" s="206"/>
     </x:row>
     <x:row r="3" ht="25.5" customHeight="1">
       <x:c r="A3" s="68" t="s">
-        <x:v>461</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B3" s="68" t="s">
-        <x:v>355</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C3" s="68" t="s">
-        <x:v>462</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="D3" s="68" t="s">
-        <x:v>463</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E3" s="68" t="s">
-        <x:v>464</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F3" s="68" t="s">
-        <x:v>465</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="G3" s="68" t="s">
         <x:v>4</x:v>
@@ -15376,7 +15714,7 @@
     </x:row>
     <x:row r="4" ht="25.5" customHeight="1">
       <x:c r="A4" s="15" t="s">
-        <x:v>466</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -15388,247 +15726,237 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="16" t="s">
-        <x:v>467</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C5" s="17" t="s">
-        <x:v>469</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D5" s="17">
         <x:v>500.0</x:v>
       </x:c>
       <x:c r="E5" s="17"/>
       <x:c r="F5" s="17" t="s">
-        <x:v>470</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="G5" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H5" s="17" t="s">
-        <x:v>472</x:v>
+        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="s">
-        <x:v>473</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C6" s="21" t="s">
-        <x:v>469</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D6" s="21">
         <x:v>500.0</x:v>
       </x:c>
       <x:c r="E6" s="21"/>
       <x:c r="F6" s="21" t="s">
-        <x:v>470</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="G6" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H6" s="21" t="s">
-        <x:v>474</x:v>
+        <x:v>443</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="16" t="s">
-        <x:v>475</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B7" s="17" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C7" s="17" t="s">
-        <x:v>469</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D7" s="17">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E7" s="17"/>
       <x:c r="F7" s="17" t="s">
-        <x:v>470</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="G7" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H7" s="17" t="s">
-        <x:v>476</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="20" t="s">
-        <x:v>477</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C8" s="21" t="s">
-        <x:v>469</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="D8" s="21">
         <x:v>350.0</x:v>
       </x:c>
       <x:c r="E8" s="21"/>
       <x:c r="F8" s="21" t="s">
-        <x:v>470</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="G8" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H8" s="21" t="s">
-        <x:v>479</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="16" t="s">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="B9" s="17" t="s">
-        <x:v>478</x:v>
-      </x:c>
-      <x:c r="C9" s="17" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="D9" s="17">
-        <x:v>350.0</x:v>
-      </x:c>
+      <x:c r="A9" s="16"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
       <x:c r="E9" s="17"/>
-      <x:c r="F9" s="17" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="G9" s="24" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="H9" s="17" t="s">
-        <x:v>481</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="41" t="str">
-        <x:v>LLC formation — Maryland / Northwest</x:v>
-      </x:c>
-      <x:c r="B10" s="21" t="s">
-        <x:v>478</x:v>
-      </x:c>
-      <x:c r="C10" s="21" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="D10" s="21">
+      <x:c r="F9" s="17"/>
+      <x:c r="G9" s="24"/>
+      <x:c r="H9" s="17"/>
+    </x:row>
+    <x:row r="10" ht="65" customHeight="1">
+      <x:c r="A10" s="207" t="str">
+        <x:v>Kiban Digital Holdings LLC — Northwest formation</x:v>
+      </x:c>
+      <x:c r="B10" s="208" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="C10" s="208" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="D10" s="208">
         <x:v>155.0</x:v>
       </x:c>
-      <x:c r="E10" s="21"/>
-      <x:c r="F10" s="21" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="G10" s="24" t="str">
-        <x:v>Filed</x:v>
-      </x:c>
-      <x:c r="H10" s="43" t="str">
-        <x:v>Founder reports Kiban Digital Holdings LLC filed, awaiting Maryland approval. September 8 is the report date; filing date and payment amount unverified. D10 is historical, not the Northwest price.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="25" t="s">
-        <x:v>482</x:v>
-      </x:c>
-      <x:c r="B11" s="21" t="s">
-        <x:v>478</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="D11" s="26">
+      <x:c r="E10" s="212" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F10" s="208" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="G10" s="213" t="str">
+        <x:v>Paid / filed</x:v>
+      </x:c>
+      <x:c r="H10" s="210" t="str">
+        <x:v>Founder confirmed $196 total on September 10. Filed through Northwest; Maryland approval pending. Exact purchase date not supplied. Estimated Cost is the old allowance, not the amount paid.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="120" customHeight="1">
+      <x:c r="A11" s="211" t="str">
+        <x:v>Policy documents — Suzanne Lawyer (Fiverr)</x:v>
+      </x:c>
+      <x:c r="B11" s="208" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="C11" s="208" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="D11" s="208">
         <x:v>125.0</x:v>
       </x:c>
-      <x:c r="E11" s="21"/>
-      <x:c r="F11" s="21" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="G11" s="24" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="H11" s="26" t="s">
-        <x:v>483</x:v>
+      <x:c r="E11" s="212" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="F11" s="208" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="G11" s="214" t="str">
+        <x:v>Paid / drafting</x:v>
+      </x:c>
+      <x:c r="H11" s="208" t="str">
+        <x:v>Founder confirmed purchase September 10. $1,100 bundle: ToS $150; Privacy/Cookies $150; AUP $100; community rules $100; DMCA $100; NCII/TAKE IT DOWN $100; anti-trafficking $100; complaints/appeals $150; creator/payout terms $150. Offer: 5 revisions, 7 days. Delivery and approval pending. Transaction date and added fees not supplied. No other Fiverr purchases reported.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="16" t="s">
-        <x:v>484</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B12" s="17" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C12" s="17" t="s">
-        <x:v>485</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D12" s="17">
         <x:v>125.0</x:v>
       </x:c>
       <x:c r="E12" s="17"/>
       <x:c r="F12" s="17" t="s">
-        <x:v>486</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="G12" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H12" s="17" t="s">
-        <x:v>487</x:v>
+        <x:v>452</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="20" t="s">
-        <x:v>488</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B13" s="21" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C13" s="21" t="s">
-        <x:v>485</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D13" s="21">
         <x:v>15.0</x:v>
       </x:c>
       <x:c r="E13" s="21"/>
       <x:c r="F13" s="21" t="s">
-        <x:v>486</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="G13" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H13" s="21" t="s">
-        <x:v>490</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="16.5" customHeight="1">
       <x:c r="A14" s="16" t="s">
-        <x:v>491</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B14" s="17" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s">
-        <x:v>485</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="D14" s="17">
         <x:v>30.0</x:v>
       </x:c>
       <x:c r="E14" s="17"/>
       <x:c r="F14" s="17" t="s">
-        <x:v>486</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="G14" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H14" s="17" t="s">
-        <x:v>492</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="15" t="s">
-        <x:v>493</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B15" s="2"/>
       <x:c r="C15" s="2"/>
@@ -15640,175 +15968,175 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="32" t="s">
-        <x:v>494</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B16" s="33" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C16" s="33" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D16" s="33">
         <x:v>18.0</x:v>
       </x:c>
       <x:c r="E16" s="33"/>
       <x:c r="F16" s="33" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G16" s="39" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H16" s="33" t="s">
-        <x:v>496</x:v>
+        <x:v>461</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="20" t="s">
-        <x:v>497</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B17" s="21" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C17" s="21" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D17" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E17" s="21"/>
       <x:c r="F17" s="21" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G17" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H17" s="21" t="s">
-        <x:v>498</x:v>
+        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="16" t="s">
-        <x:v>499</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B18" s="17" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C18" s="17" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D18" s="17">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E18" s="17"/>
       <x:c r="F18" s="17" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G18" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H18" s="17" t="s">
-        <x:v>500</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="20" t="s">
-        <x:v>501</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B19" s="21" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C19" s="21" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D19" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E19" s="21"/>
       <x:c r="F19" s="21" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G19" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H19" s="21" t="s">
-        <x:v>502</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="16" t="s">
-        <x:v>503</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B20" s="17" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D20" s="17">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E20" s="17"/>
       <x:c r="F20" s="17" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G20" s="24" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H20" s="17" t="s">
-        <x:v>504</x:v>
+        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
       <x:c r="A21" s="20" t="s">
-        <x:v>505</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B21" s="21" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C21" s="21" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D21" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E21" s="21"/>
       <x:c r="F21" s="21" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G21" s="24" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="H21" s="21" t="s">
         <x:v>471</x:v>
-      </x:c>
-      <x:c r="H21" s="21" t="s">
-        <x:v>506</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="25.5" customHeight="1">
       <x:c r="A22" s="36" t="s">
-        <x:v>507</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B22" s="37" t="s">
-        <x:v>489</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C22" s="37" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D22" s="37">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E22" s="37"/>
       <x:c r="F22" s="37" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>471</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="H22" s="37" t="s">
-        <x:v>508</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">
       <x:c r="A23" s="15" t="s">
-        <x:v>509</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B23" s="2"/>
       <x:c r="C23" s="2"/>
@@ -15820,79 +16148,79 @@
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
       <x:c r="A24" s="32" t="s">
-        <x:v>510</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B24" s="33" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C24" s="33" t="s">
-        <x:v>511</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D24" s="33">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E24" s="33"/>
       <x:c r="F24" s="33" t="s">
-        <x:v>512</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="G24" s="39" t="s">
-        <x:v>513</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="H24" s="33" t="s">
-        <x:v>514</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1">
       <x:c r="A25" s="20" t="s">
-        <x:v>515</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B25" s="21" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C25" s="21" t="s">
-        <x:v>511</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D25" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E25" s="21"/>
       <x:c r="F25" s="21" t="s">
-        <x:v>512</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="G25" s="24" t="s">
-        <x:v>513</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="H25" s="21" t="s">
-        <x:v>516</x:v>
+        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="25.5" customHeight="1">
       <x:c r="A26" s="36" t="s">
-        <x:v>517</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B26" s="37" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C26" s="37" t="s">
-        <x:v>511</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D26" s="37">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E26" s="37"/>
       <x:c r="F26" s="37" t="s">
-        <x:v>518</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>513</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="H26" s="37" t="s">
-        <x:v>519</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
       <x:c r="A27" s="15" t="s">
-        <x:v>520</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B27" s="2"/>
       <x:c r="C27" s="2"/>
@@ -15904,80 +16232,80 @@
     </x:row>
     <x:row r="28" ht="15.75" customHeight="1">
       <x:c r="A28" s="32" t="s">
-        <x:v>521</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B28" s="33" t="s">
-        <x:v>468</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C28" s="33" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D28" s="33">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E28" s="33"/>
       <x:c r="F28" s="33" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G28" s="39" t="s">
-        <x:v>522</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="H28" s="33" t="s">
-        <x:v>523</x:v>
+        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
       <x:c r="A29" s="20" t="s">
-        <x:v>524</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B29" s="21" t="s">
-        <x:v>525</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C29" s="21" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D29" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E29" s="21"/>
       <x:c r="F29" s="21" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G29" s="24" t="s">
-        <x:v>522</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="H29" s="21" t="s">
-        <x:v>526</x:v>
+        <x:v>491</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15.75" customHeight="1">
       <x:c r="A30" s="16" t="s">
-        <x:v>527</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B30" s="17" t="s">
-        <x:v>478</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C30" s="17" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D30" s="17">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E30" s="17"/>
       <x:c r="F30" s="17" t="s">
-        <x:v>495</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G30" s="24" t="s">
-        <x:v>522</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="H30" s="17" t="s">
-        <x:v>528</x:v>
+        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="25.5" customHeight="1"/>
     <x:row r="32" ht="15.75" customHeight="1">
       <x:c r="A32" s="15" t="s">
-        <x:v>529</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B32" s="2"/>
       <x:c r="C32" s="2"/>
@@ -15989,16 +16317,16 @@
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1">
       <x:c r="A33" s="6" t="s">
-        <x:v>530</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B33" s="69" t="n">
         <x:f>SUM(D5:D11)</x:f>
-        <x:v>1980</x:v>
+        <x:v>1630</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1">
       <x:c r="A34" s="7" t="s">
-        <x:v>531</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B34" s="70" t="n">
         <x:f>SUM(D12:D14)</x:f>
@@ -16007,7 +16335,7 @@
     </x:row>
     <x:row r="35" ht="15.75" customHeight="1">
       <x:c r="A35" s="6" t="s">
-        <x:v>532</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B35" s="69" t="n">
         <x:f>SUM(D16:D22)</x:f>
@@ -16016,14 +16344,22 @@
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
       <x:c r="A36" s="7" t="s">
-        <x:v>533</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B36" s="70" t="n">
         <x:f>B33+B34+B35*12</x:f>
-        <x:v>2366</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="15.75" customHeight="1"/>
+        <x:v>2016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="203" t="str">
+        <x:v>Actual paid to date</x:v>
+      </x:c>
+      <x:c r="B37" s="204" t="n">
+        <x:f>SUM(E5:E30)</x:f>
+        <x:v>1296</x:v>
+      </x:c>
+    </x:row>
     <x:row r="38" ht="15.75" customHeight="1">
       <x:c r="A38" t="str">
         <x:v>Original displayed Year 1 total</x:v>
@@ -16034,11 +16370,11 @@
     </x:row>
     <x:row r="39" ht="15.75" customHeight="1">
       <x:c r="A39" t="str">
-        <x:v>Arithmetic correction</x:v>
+        <x:v>Remaining estimate vs original total</x:v>
       </x:c>
       <x:c r="B39" s="172" t="n">
         <x:f>B36-B38</x:f>
-        <x:v>653</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="38" customHeight="1">
@@ -17026,6 +17362,9 @@
     <x:mergeCell ref="A32:H32"/>
     <x:mergeCell ref="B40:H40"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="G5:G30">
+    <x:cfRule type="containsText" dxfId="69" priority="1" operator="containsText" text="Deferred"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -17036,7 +17375,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
-        <x:v>534</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B1"/>
       <x:c r="C1"/>
@@ -17047,7 +17386,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
-        <x:v>535</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -17067,12 +17406,12 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>536</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B4"/>
       <x:c r="C4"/>
       <x:c r="D4" t="s">
-        <x:v>537</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="E4"/>
       <x:c r="F4"/>
@@ -17080,15 +17419,15 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>538</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B5" t="n">
         <x:f>COUNTIF('Master Tracker'!C4:C164,"✅ Done")+COUNTIF('Master Tracker'!C4:C164,"🔄 In Progress")+COUNTIF('Master Tracker'!C4:C164,"📋 Not Started")</x:f>
-        <x:v>148</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C5"/>
       <x:c r="D5" t="s">
-        <x:v>539</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="E5" t="n">
         <x:f>COUNTA(Backlog!A2:A30)</x:f>
@@ -17103,7 +17442,7 @@
       </x:c>
       <x:c r="B6" t="n">
         <x:f>COUNTIF('Master Tracker'!C4:C164,"✅ Done")</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6"/>
       <x:c r="D6" t="s">
@@ -17122,7 +17461,7 @@
       </x:c>
       <x:c r="B7" t="n">
         <x:f>COUNTIF('Master Tracker'!C4:C164,"🔄 In Progress")</x:f>
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C7"/>
       <x:c r="D7"/>
@@ -17136,7 +17475,7 @@
       </x:c>
       <x:c r="B8" t="n">
         <x:f>COUNTIF('Master Tracker'!C4:C164,"📋 Not Started")</x:f>
-        <x:v>78</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C8"/>
       <x:c r="D8"/>
@@ -17146,11 +17485,11 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
-        <x:v>540</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B9" t="n">
         <x:f>IF(B5=0,0,B6/B5)</x:f>
-        <x:v>0.13513513513513514</x:v>
+        <x:v>0.14685314685314685</x:v>
       </x:c>
       <x:c r="C9"/>
       <x:c r="D9"/>
@@ -17178,11 +17517,11 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="s">
-        <x:v>541</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B12"/>
       <x:c r="C12" t="s">
-        <x:v>542</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D12"/>
       <x:c r="E12"/>
@@ -17208,7 +17547,7 @@
       </x:c>
       <x:c r="B14"/>
       <x:c r="C14" t="s">
-        <x:v>543</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="D14"/>
       <x:c r="E14"/>
@@ -17221,7 +17560,7 @@
       </x:c>
       <x:c r="B15"/>
       <x:c r="C15" t="s">
-        <x:v>544</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="D15"/>
       <x:c r="E15"/>
@@ -17232,7 +17571,7 @@
       <x:c r="A16"/>
       <x:c r="B16"/>
       <x:c r="C16" t="s">
-        <x:v>545</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="D16"/>
       <x:c r="E16"/>
@@ -17243,7 +17582,7 @@
       <x:c r="A17"/>
       <x:c r="B17"/>
       <x:c r="C17" t="s">
-        <x:v>546</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -17254,7 +17593,7 @@
       <x:c r="A18"/>
       <x:c r="B18"/>
       <x:c r="C18" t="s">
-        <x:v>547</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D18"/>
       <x:c r="E18"/>
@@ -17265,7 +17604,7 @@
       <x:c r="A19"/>
       <x:c r="B19"/>
       <x:c r="C19" t="s">
-        <x:v>548</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D19"/>
       <x:c r="E19"/>
@@ -17559,7 +17898,7 @@
       <x:c r="G10" s="111" t="str">
         <x:v>Decision</x:v>
       </x:c>
-      <x:c r="H10" s="111" t="str">
+      <x:c r="H10" s="219" t="str">
         <x:v>Deferred</x:v>
       </x:c>
     </x:row>
@@ -17568,9 +17907,9 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="B11" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
-      </x:c>
-      <x:c r="C11" s="111" t="str">
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
+      </x:c>
+      <x:c r="C11" s="219" t="str">
         <x:v>Deferred</x:v>
       </x:c>
       <x:c r="D11" s="111" t="str"/>
@@ -17892,7 +18231,7 @@
       </x:c>
     </x:row>
     <x:row r="32" ht="44" customHeight="1">
-      <x:c r="A32" s="111" t="str">
+      <x:c r="A32" s="219" t="str">
         <x:v>Deferred</x:v>
       </x:c>
       <x:c r="B32" s="111" t="str">
@@ -18099,7 +18438,7 @@
       </x:c>
       <x:c r="E5" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A5,'Delivery Tracker'!$H$4:$H$400,"Done")</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="111" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$B$4:$B$400,$A5)</x:f>
@@ -18107,7 +18446,7 @@
       </x:c>
       <x:c r="G5" s="119" t="n">
         <x:f>IF(F5=0,0,E5/F5)</x:f>
-        <x:v>0.375</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="H5" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A5,'Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
@@ -18123,7 +18462,7 @@
       </x:c>
       <x:c r="K5" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A5,'Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L5" s="111" t="str">
         <x:v>Maintain routing, shared shell, fixtures, CI, error states, and code splitting.</x:v>
@@ -18282,7 +18621,7 @@
       </x:c>
       <x:c r="H8" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I8" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"In Review")</x:f>
@@ -18294,10 +18633,10 @@
       </x:c>
       <x:c r="K8" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L8" s="111" t="str">
-        <x:v>Slices 1–4 have published source; operations remain dormant. Founder reports Maryland LLC filed and CCBill inquiry sent. Await approval/response; review what arrives before another founder task.</x:v>
+        <x:v>Slices 1–4 published; operations dormant. Maryland approval pending. Initial CCBill reply retained; proposed follow-up cancelled. Founder/provider work now accompanies each functional code slice.</x:v>
       </x:c>
       <x:c r="M8" s="111" t="str">
         <x:v>Resolve business/legal/provider prerequisites in sequence. G1–G12 apply to operations activation, not all synthetic local product work.</x:v>
@@ -18320,10 +18659,10 @@
         <x:v>Media pipeline and content model</x:v>
       </x:c>
       <x:c r="C9" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partially Complete</x:v>
       </x:c>
       <x:c r="D9" s="111" t="str">
-        <x:v>UI Prototype</x:v>
+        <x:v>Backend Implemented</x:v>
       </x:c>
       <x:c r="E9" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A9,'Delivery Tracker'!$H$4:$H$400,"Done")</x:f>
@@ -18339,11 +18678,11 @@
       </x:c>
       <x:c r="H9" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A9,'Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I9" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A9,'Delivery Tracker'!$H$4:$H$400,"In Review")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J9" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A9,'Delivery Tracker'!$H$4:$H$400,"Blocked")</x:f>
@@ -18351,22 +18690,22 @@
       </x:c>
       <x:c r="K9" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A9,'Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L9" s="111" t="str">
-        <x:v>UI seams exist; secure R2 upload, quarantine, moderation, entitlement, and signed delivery are absent.</x:v>
+        <x:v>Safe photo/video flow now uses private R2 storage. Cloud upload/read, private drafts, publish/feed, ranges, restart persistence and removal are verified. Test accounts only. Hosted review deployment and production media controls remain open.</x:v>
       </x:c>
       <x:c r="M9" s="111" t="str">
-        <x:v>After the business definition, authorize a bounded synthetic content/media slice. Real identity/content exposure requires applicable safeguards.</x:v>
+        <x:v>Founder reviews the working local R2 upload/publish flow for this slice. No new signup, paperwork or payment task. Real identity, adult uploads and payments remain disabled. Full P05 exit, deployment and processor approval remain open.</x:v>
       </x:c>
       <x:c r="N9" s="111" t="str">
         <x:v>Approved creators publish; unauthorized users cannot access originals; takedowns invalidate delivery.</x:v>
       </x:c>
       <x:c r="O9" s="111" t="str">
-        <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#9-phase-5--media-pipeline-and-content-model</x:v>
+        <x:v>HANDOFF.md</x:v>
       </x:c>
       <x:c r="P9" s="112" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
@@ -18374,10 +18713,10 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="B10" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="C10" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Partially Complete</x:v>
       </x:c>
       <x:c r="D10" s="111" t="str">
         <x:v>UI Prototype</x:v>
@@ -18388,7 +18727,7 @@
       </x:c>
       <x:c r="F10" s="111" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$B$4:$B$400,$A10)</x:f>
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G10" s="119" t="n">
         <x:f>IF(F10=0,0,E10/F10)</x:f>
@@ -18396,7 +18735,7 @@
       </x:c>
       <x:c r="H10" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A10,'Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I10" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A10,'Delivery Tracker'!$H$4:$H$400,"In Review")</x:f>
@@ -18408,22 +18747,22 @@
       </x:c>
       <x:c r="K10" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A10,'Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L10" s="111" t="str">
-        <x:v>Veso direction and UI prototypes exist; processor, ledger, webhooks, and entitlements are not implemented.</x:v>
+        <x:v>Provider/site preparation is in progress: CCBill Sales replied, safe-content/R2 milestone is verified and policy drafting is commissioned. Payment backend, webhooks and paid entitlements have not started.</x:v>
       </x:c>
       <x:c r="M10" s="111" t="str">
-        <x:v>Founder/provider/counsel decisions on processor economics, refunds, payouts, and Veso terms.</x:v>
+        <x:v>Continue functioning-site slices; password protection is permitted for later review. Founder reviews the current local flow. Return to CCBill when review-ready; define the supported payment method before integration.</x:v>
       </x:c>
       <x:c r="N10" s="111" t="str">
-        <x:v>Recharge and ledger work; Store/Connect/tips/PPV consume Veso; webhooks drive subscriptions and reconciliation.</x:v>
+        <x:v>For paid beta flows: trusted payment events, entitlements, earnings, refunds and chargebacks reconcile.</x:v>
       </x:c>
       <x:c r="O10" s="111" t="str">
-        <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#10-phase-6--veso-payments-subscriptions-tipping-and-ppv</x:v>
+        <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md</x:v>
       </x:c>
       <x:c r="P10" s="112" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
@@ -18468,19 +18807,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L11" s="111" t="str">
-        <x:v>Waiting on creator approval, media, payments, entitlement, and operations dependencies.</x:v>
+        <x:v>Core journey still needs creator, content/access and operations controls. Apply payment dependencies to the chosen beta method.</x:v>
       </x:c>
       <x:c r="M11" s="111" t="str">
-        <x:v>Develop one complete journey incrementally with synthetic data. Real use requires creator, media, payment, entitlement and operating controls.</x:v>
+        <x:v>Continue safe test flows. Define the beta payment model with its slice; any paid flow requires processor confirmation, entitlements, auditable earnings and reconciliation.</x:v>
       </x:c>
       <x:c r="N11" s="111" t="str">
-        <x:v>Complete automated member/creator/payment/content/audit flow with no manual DB edits.</x:v>
+        <x:v>Agreed beta journey passes automated tests without manual DB edits. Paid flows satisfy payment, access and audit controls.</x:v>
       </x:c>
       <x:c r="O11" s="111" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#11-phase-7--core-end-to-end-vertical-slice</x:v>
       </x:c>
       <x:c r="P11" s="112" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
@@ -18528,7 +18867,7 @@
         <x:v>Connect discovery, Store and feed remain launch scope. Connect means online, price and language filters.</x:v>
       </x:c>
       <x:c r="M12" s="111" t="str">
-        <x:v>Integrate only after content, entitlement, and Veso foundations exist.</x:v>
+        <x:v>Integrate content and access controls. Define service/order and beta payment rules with the relevant slice.</x:v>
       </x:c>
       <x:c r="N12" s="111" t="str">
         <x:v>Feed actions persist; Store uses real data; creator discovery filters work. Separately define service order/payment rules.</x:v>
@@ -18537,7 +18876,7 @@
         <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#12-phase-8--feed-social-actions-store-and-connect</x:v>
       </x:c>
       <x:c r="P12" s="112" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -18673,7 +19012,7 @@
       </x:c>
       <x:c r="F15" s="111" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$B$4:$B$400,$A15)</x:f>
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G15" s="119" t="n">
         <x:f>IF(F15=0,0,E15/F15)</x:f>
@@ -18693,10 +19032,10 @@
       </x:c>
       <x:c r="K15" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A15,'Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L15" s="111" t="str">
-        <x:v>Dormant operations foundation has published source. Further operations work stays parked while Maryland approval and CCBill sales response are pending.</x:v>
+        <x:v>Dormant operations source remains parked. The next planned P05 test-content flow pairs storage decisions with implementation. No deployment, live payment or identity activation is implied.</x:v>
       </x:c>
       <x:c r="M15" s="111" t="str">
         <x:v>Evaluate provider, restricted hosting, MFA/recovery, session, permission, audit and deployment controls when activating real operations.</x:v>
@@ -18870,7 +19209,7 @@
         <x:v>CI/E2E foundations and the deterministic promotion clock fix are published; product E2E, security drills, beta, and launch gates remain open.</x:v>
       </x:c>
       <x:c r="M18" s="111" t="str">
-        <x:v>Keep expanding domain tests; do not schedule beta until legal, payments, identity, recovery, and support gates exist.</x:v>
+        <x:v>Verify applicable creator, content, security, recovery and support controls for beta. Paid flows also need processor and payment controls.</x:v>
       </x:c>
       <x:c r="N18" s="111" t="str">
         <x:v>Restore/security/processor/content/support drills pass; launch gates are satisfied; no critical findings.</x:v>
@@ -18879,7 +19218,7 @@
         <x:v>https://github.com/QK-Connoisseur/PDoki/actions/runs/32535922437</x:v>
       </x:c>
       <x:c r="P18" s="112" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
@@ -18945,12 +19284,12 @@
     <x:mergeCell ref="A2:P2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="C4:C19">
-    <x:cfRule type="containsText" dxfId="28" priority="1" operator="containsText" text="Complete"/>
-    <x:cfRule type="containsText" dxfId="29" priority="2" operator="containsText" text="Partially Complete"/>
-    <x:cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="Foundation Complete"/>
-    <x:cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="Blocked"/>
-    <x:cfRule type="containsText" dxfId="32" priority="5" operator="containsText" text="Not Started"/>
-    <x:cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="Deferred"/>
+    <x:cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="Complete"/>
+    <x:cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="Partially Complete"/>
+    <x:cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="Foundation Complete"/>
+    <x:cfRule type="containsText" dxfId="37" priority="4" operator="containsText" text="Blocked"/>
+    <x:cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="Not Started"/>
+    <x:cfRule type="containsText" dxfId="39" priority="6" operator="containsText" text="Deferred"/>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="C4:C19">
@@ -18962,7 +19301,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f70c7d9d6084912"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68c94d1baaac45d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19401,7 +19740,7 @@
         <x:v>Prepare terms governing platform use, NSFW content rules, user responsibilities, dispute resolution.</x:v>
       </x:c>
       <x:c r="R9" s="111" t="str">
-        <x:v>Must exist before launch.</x:v>
+        <x:v>Suzanne Lawyer hired on Fiverr for the $1,100 policy-document bundle. Draft delivery and review pending.</x:v>
       </x:c>
       <x:c r="S9" s="111" t="str">
         <x:v>Preserved Master Tracker row 11; legacy status: 🔄 In Progress</x:v>
@@ -19842,7 +20181,7 @@
         <x:v>Prepare Payment Provider Compliance Package</x:v>
       </x:c>
       <x:c r="H18" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I18" s="111" t="str">
         <x:v>N/A</x:v>
@@ -19857,21 +20196,23 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M18" s="111" t="str">
-        <x:v>Review the CCBill sales response for account-specific compliance requirements when received; assemble requested evidence in sequence afterward.</x:v>
+        <x:v>Continue functioning-site and policy preparation alongside the current product slice. Assemble account-specific evidence for later CCBill review.</x:v>
       </x:c>
       <x:c r="N18" s="112"/>
-      <x:c r="O18" s="111" t="str"/>
+      <x:c r="O18" s="111" t="str">
+        <x:v>docs/product/initial-ccbill-inquiry.md</x:v>
+      </x:c>
       <x:c r="P18" s="112" t="n">
-        <x:v>46273.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q18" s="111" t="str">
         <x:v>Document policies/controls required by CCBill and Epoch for merchant onboarding.</x:v>
       </x:c>
       <x:c r="R18" s="111" t="str">
-        <x:v>Founder reports preliminary inquiry sent to CCBill sales. No response, formal merchant application or approval evidenced. Epoch may follow later. Await response before choosing another founder task.</x:v>
+        <x:v>CCBill Sales replied: a functioning online site is required; password protection is allowed. Site preparation is underway, safe-content/R2 milestone is verified and policy drafting is commissioned. Merchant approval, model eligibility, fees and payouts remain unresolved.</x:v>
       </x:c>
       <x:c r="S18" s="111" t="str">
-        <x:v>Preserved Master Tracker row 20; legacy status: 📋 Not Started</x:v>
+        <x:v>Master Tracker row 20; provider preparation reconciled September 10, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="46" customHeight="1">
@@ -20022,7 +20363,7 @@
         <x:v>46250.666666666664</x:v>
       </x:c>
       <x:c r="Q21" s="111" t="str">
-        <x:v>Decide classes (IC 009, 035, 042), timing, filing sequence for 'Pumdoki' and 'Veso'.</x:v>
+        <x:v>Decide classes (IC 009, 035, 042), timing and filing sequence for 'Pumdoki'.</x:v>
       </x:c>
       <x:c r="R21" s="111" t="str">
         <x:v>Trademark timing/classes already considered.</x:v>
@@ -20211,7 +20552,7 @@
         <x:v>Draft Anti-Human Trafficking Policy</x:v>
       </x:c>
       <x:c r="H25" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I25" s="111" t="str">
         <x:v>N/A</x:v>
@@ -20226,21 +20567,23 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M25" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Await the commissioned draft, then review and approve it before publication or operational reliance.</x:v>
       </x:c>
       <x:c r="N25" s="112"/>
-      <x:c r="O25" s="111" t="str"/>
+      <x:c r="O25" s="111" t="str">
+        <x:v>Expense Tracker row 11; founder-confirmed Suzanne Lawyer $1,100 document bundle, including anti-trafficking policy.</x:v>
+      </x:c>
       <x:c r="P25" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q25" s="111" t="str">
         <x:v>Prohibit trafficking, exploitation, coercive content. Include reporting mechanisms and creator guidance.</x:v>
       </x:c>
       <x:c r="R25" s="111" t="str">
-        <x:v>Required by CCBill/Epoch for merchant onboarding.</x:v>
+        <x:v>Drafting commissioned within the purchased policy bundle. Delivery and substantive approval remain pending.</x:v>
       </x:c>
       <x:c r="S25" s="111" t="str">
-        <x:v>Preserved Master Tracker row 27; legacy status: 📋 Not Started</x:v>
+        <x:v>Master Tracker row 27; purchased drafting recorded September 10, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="46" customHeight="1">
@@ -20930,13 +21273,13 @@
         <x:v>Repository and frontend foundation</x:v>
       </x:c>
       <x:c r="G39" s="111" t="str">
-        <x:v>Implement Dark Knight theme</x:v>
+        <x:v>Implement Midnight City theme</x:v>
       </x:c>
       <x:c r="H39" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I39" s="111" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Integrated</x:v>
       </x:c>
       <x:c r="J39" s="111" t="str">
         <x:v>Medium</x:v>
@@ -20946,21 +21289,23 @@
       </x:c>
       <x:c r="L39" s="111" t="str"/>
       <x:c r="M39" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Browser-local static theme scope is complete. Account-synced preferences remain separate future work.</x:v>
       </x:c>
       <x:c r="N39" s="112"/>
-      <x:c r="O39" s="111" t="str"/>
+      <x:c r="O39" s="111" t="str">
+        <x:v>0f01961 (#19); apps/web/src/appearance/memberThemeContext.js; MemberThemeProvider.test.jsx; staticBackgroundAssets.test.js; README.md</x:v>
+      </x:c>
       <x:c r="P39" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q39" s="111" t="str">
-        <x:v>Second default theme (dark/charcoal). Near-black backgrounds, deep tones, pink accent. Toggle in Settings. All users get this free alongside Sakura Pink.</x:v>
+        <x:v>Second free theme alongside Sakura Kiss. Blue city rooftops with static desktop/mobile JPG backgrounds. Settings Appearance chooser stores the preference in this browser.</x:v>
       </x:c>
       <x:c r="R39" s="111" t="str">
-        <x:v>Committed as a default theme — not premium. CSS variable overrides over existing system. Do not skip.</x:v>
+        <x:v>Published implementation; switching and saved preference restoration are tested. Static asset tests cover desktop/mobile JPGs and absence of background video. Internal DARK_KNIGHT key is retained for stored-preference compatibility.</x:v>
       </x:c>
       <x:c r="S39" s="111" t="str">
-        <x:v>Preserved Master Tracker row 42; legacy status: 📋 Not Started</x:v>
+        <x:v>Master Tracker row 42; theme completion reconciled September 10, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="46" customHeight="1">
@@ -20971,7 +21316,7 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C40" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D40" s="111" t="str">
         <x:v>P10, P11</x:v>
@@ -20980,7 +21325,7 @@
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F40" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G40" s="111" t="str">
         <x:v>Design Founding Creator / Member badge program</x:v>
@@ -21088,10 +21433,10 @@
         <x:v>Set up Cloudflare R2 media storage</x:v>
       </x:c>
       <x:c r="H42" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I42" s="111" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Integrated</x:v>
       </x:c>
       <x:c r="J42" s="111" t="str">
         <x:v>Medium</x:v>
@@ -21101,21 +21446,23 @@
       </x:c>
       <x:c r="L42" s="111" t="str"/>
       <x:c r="M42" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Broader storage scope remains: signed delivery, CDN caching, retention/garbage collection and recovery/production hardening.</x:v>
       </x:c>
       <x:c r="N42" s="112"/>
-      <x:c r="O42" s="111" t="str"/>
+      <x:c r="O42" s="111" t="str">
+        <x:v>HANDOFF.md lines 120–151; docs/architecture/phase5-local-content-flow.md; apps/api/src/content/r2.ts; 86 targeted tests and both R2 browser checks passed.</x:v>
+      </x:c>
       <x:c r="P42" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q42" s="111" t="str">
-        <x:v>Configure R2 buckets, access policies, signed URLs for private media, CDN caching.</x:v>
+        <x:v>Private safe-sample R2 bucket and API integration verified. Signed delivery, CDN caching and production storage lifecycle/recovery remain pending.</x:v>
       </x:c>
       <x:c r="R42" s="111" t="str">
-        <x:v>R2 chosen for NSFW-safe media delivery.</x:v>
+        <x:v>R2 activated ($0 due), private review bucket created, Public Access Disabled. Safe PNG/MP4 uploads, authenticated API reads, restart persistence, removal and browser checks passed. Adult-business acceptance unconfirmed; not production-ready.</x:v>
       </x:c>
       <x:c r="S42" s="111" t="str">
-        <x:v>Preserved Master Tracker row 46; legacy status: 📋 Not Started</x:v>
+        <x:v>Master Tracker row 46; safe-sample R2 milestone reconciled September 10, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="46" customHeight="1">
@@ -21157,10 +21504,10 @@
       <x:c r="N43" s="112"/>
       <x:c r="O43" s="111" t="str"/>
       <x:c r="P43" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
       <x:c r="Q43" s="111" t="str">
-        <x:v>Model users, creators, posts, subscriptions, plans, transactions, Veso wallets, moderation.</x:v>
+        <x:v>Model users, creators, posts, subscriptions, plans, transactions and moderation as needed.</x:v>
       </x:c>
       <x:c r="R43" s="111" t="str">
         <x:v>Local PostgreSQL/Prisma includes User, Session, append-only AcceptanceRecord, VerificationToken, UserPreference, CreatorApplication, creator-policy acceptance, and constrained successful-transition review evidence. Remaining product domains and production RDS deployment are pending.</x:v>
@@ -22107,14 +22454,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C62" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D62" s="111" t="str"/>
       <x:c r="E62" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F62" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G62" s="111" t="str">
         <x:v>Build subscription / pricing page</x:v>
@@ -22311,14 +22658,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C66" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D66" s="111" t="str"/>
       <x:c r="E66" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F66" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G66" s="111" t="str">
         <x:v>Implement membership tier modules</x:v>
@@ -22508,55 +22855,25 @@
       </x:c>
     </x:row>
     <x:row r="70" ht="46" customHeight="1">
-      <x:c r="A70" s="111" t="str">
-        <x:v>LEG-MT-076</x:v>
-      </x:c>
-      <x:c r="B70" s="111" t="str">
-        <x:v>P06</x:v>
-      </x:c>
-      <x:c r="C70" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
-      </x:c>
+      <x:c r="A70" s="111"/>
+      <x:c r="B70" s="111"/>
+      <x:c r="C70" s="111"/>
       <x:c r="D70" s="111" t="str"/>
-      <x:c r="E70" s="111" t="str">
-        <x:v>Legacy-mapped task</x:v>
-      </x:c>
-      <x:c r="F70" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
-      </x:c>
-      <x:c r="G70" s="111" t="str">
-        <x:v>Build Veso wallet page</x:v>
-      </x:c>
-      <x:c r="H70" s="111" t="str">
-        <x:v>In Progress</x:v>
-      </x:c>
-      <x:c r="I70" s="111" t="str">
-        <x:v>UI Prototype</x:v>
-      </x:c>
-      <x:c r="J70" s="111" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="K70" s="111" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
+      <x:c r="E70" s="111"/>
+      <x:c r="F70" s="111"/>
+      <x:c r="G70" s="111"/>
+      <x:c r="H70" s="111"/>
+      <x:c r="I70" s="111"/>
+      <x:c r="J70" s="111"/>
+      <x:c r="K70" s="111"/>
       <x:c r="L70" s="111" t="str"/>
-      <x:c r="M70" s="111" t="str">
-        <x:v>Close the remaining gap: Wallet UI prototype exists.</x:v>
-      </x:c>
+      <x:c r="M70" s="111"/>
       <x:c r="N70" s="112"/>
-      <x:c r="O70" s="111" t="str"/>
-      <x:c r="P70" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
-      </x:c>
-      <x:c r="Q70" s="111" t="str">
-        <x:v>Member-facing wallet: Veso balance display, add funds flow, transaction history. 1 Veso = 1 USD. Keep it simple for MVP.</x:v>
-      </x:c>
-      <x:c r="R70" s="111" t="str">
-        <x:v>Wallet UI prototype exists. Add/recharge Veso needs an E-Pal Buff-inspired design plus real ledger/payment integration.</x:v>
-      </x:c>
-      <x:c r="S70" s="111" t="str">
-        <x:v>Preserved Master Tracker row 76; legacy status: 🔄 In Progress</x:v>
-      </x:c>
+      <x:c r="O70" s="111"/>
+      <x:c r="P70" s="112"/>
+      <x:c r="Q70" s="111"/>
+      <x:c r="R70" s="111"/>
+      <x:c r="S70" s="111"/>
     </x:row>
     <x:row r="71" ht="46" customHeight="1">
       <x:c r="A71" s="111" t="str">
@@ -22655,10 +22972,10 @@
         <x:v>46250.666666666664</x:v>
       </x:c>
       <x:c r="Q72" s="111" t="str">
-        <x:v>Account info, password change, notification preferences, theme toggle (Sakura Pink / Dark Knight), NSFW content toggle, payment/billing section.</x:v>
+        <x:v>Account info, password change, notification preferences, theme toggle (Sakura Kiss / Midnight City), NSFW content toggle, payment/billing section.</x:v>
       </x:c>
       <x:c r="R72" s="111" t="str">
-        <x:v>Protected Settings is implemented for display name, email/reverification, password, active sessions, and explicit-content preference. Notifications, theme, billing, export, and deletion remain deferred to dependency phases.</x:v>
+        <x:v>Protected Settings implements display name, email/reverification, password, active sessions and explicit-content preference. Theme selection is implemented browser-locally. Account theme sync, real notifications/billing, export and deletion remain pending.</x:v>
       </x:c>
       <x:c r="S72" s="111" t="str">
         <x:v>Preserved Master Tracker row 78; legacy status: 🔄 In Progress</x:v>
@@ -22757,7 +23074,7 @@
         <x:v>46250.666666666664</x:v>
       </x:c>
       <x:c r="Q74" s="111" t="str">
-        <x:v>Member activity history: posts liked, content purchased, subscriptions, Veso spent. Lower priority.</x:v>
+        <x:v>Member activity history: posts liked, content purchased, subscriptions and payment history. Lower priority.</x:v>
       </x:c>
       <x:c r="R74" s="111" t="str">
         <x:v>Nice-to-have post-launch. Defer if time is tight.</x:v>
@@ -23042,7 +23359,7 @@
         <x:v>Define post / content model</x:v>
       </x:c>
       <x:c r="H80" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Review</x:v>
       </x:c>
       <x:c r="I80" s="111" t="str">
         <x:v>N/A</x:v>
@@ -23053,20 +23370,24 @@
       <x:c r="K80" s="111" t="str">
         <x:v>Engineering</x:v>
       </x:c>
-      <x:c r="L80" s="111" t="str"/>
+      <x:c r="L80" s="111" t="str">
+        <x:v>Targeted review during relevant slice</x:v>
+      </x:c>
       <x:c r="M80" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Local ContentPost/MediaAsset model implemented. Broader content/access design remains In Review. Review revisions, paid audiences and production eligibility before live sensitive use.</x:v>
       </x:c>
       <x:c r="N80" s="112"/>
-      <x:c r="O80" s="111" t="str"/>
+      <x:c r="O80" s="111" t="str">
+        <x:v>docs/architecture/phase5-slice1-content-model-and-access-design.md</x:v>
+      </x:c>
       <x:c r="P80" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
       <x:c r="Q80" s="111" t="str">
         <x:v>Creator posting, visibility flags (public/subscriber/tier-locked), member access rules.</x:v>
       </x:c>
       <x:c r="R80" s="111" t="str">
-        <x:v>Core content object needs build.</x:v>
+        <x:v>Safe test posts persist locally with sealed bodies/media identities. No paid offers or real creator eligibility. Full content/access design and human review remain open.</x:v>
       </x:c>
       <x:c r="S80" s="111" t="str">
         <x:v>Preserved Master Tracker row 87; legacy status: 📋 Not Started</x:v>
@@ -23093,10 +23414,10 @@
         <x:v>Build media upload pipeline</x:v>
       </x:c>
       <x:c r="H81" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I81" s="111" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Backend Implemented</x:v>
       </x:c>
       <x:c r="J81" s="111" t="str">
         <x:v>Critical</x:v>
@@ -23104,20 +23425,24 @@
       <x:c r="K81" s="111" t="str">
         <x:v>Engineering</x:v>
       </x:c>
-      <x:c r="L81" s="111" t="str"/>
+      <x:c r="L81" s="111" t="str">
+        <x:v>Founder review of working local R2 flow</x:v>
+      </x:c>
       <x:c r="M81" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Review safe photo/video upload, draft reload, publish/member read and removal in the local preview. R2 account, credentials and private access are verified. No deployment or processor approval is implied.</x:v>
       </x:c>
       <x:c r="N81" s="112"/>
-      <x:c r="O81" s="111" t="str"/>
+      <x:c r="O81" s="111" t="str">
+        <x:v>HANDOFF.md</x:v>
+      </x:c>
       <x:c r="P81" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
       <x:c r="Q81" s="111" t="str">
         <x:v>Image/video upload → Cloudflare R2 storage → signed URL delivery.</x:v>
       </x:c>
       <x:c r="R81" s="111" t="str">
-        <x:v>Launch-critical capability.</x:v>
+        <x:v>R2 PNG/MP4 API and browser paths passed, including image display/video playback, private drafts, publish/ranges and removal. API restart preserved posts/session/identical bytes. Public access disabled. All 5 test objects deleted and absence checked. HANDOFF.md.</x:v>
       </x:c>
       <x:c r="S81" s="111" t="str">
         <x:v>Preserved Master Tracker row 88; legacy status: 📋 Not Started</x:v>
@@ -23144,7 +23469,7 @@
         <x:v>Define public vs private asset rules</x:v>
       </x:c>
       <x:c r="H82" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Review</x:v>
       </x:c>
       <x:c r="I82" s="111" t="str">
         <x:v>N/A</x:v>
@@ -23155,20 +23480,24 @@
       <x:c r="K82" s="111" t="str">
         <x:v>Engineering</x:v>
       </x:c>
-      <x:c r="L82" s="111" t="str"/>
+      <x:c r="L82" s="111" t="str">
+        <x:v>Targeted review during relevant slice</x:v>
+      </x:c>
       <x:c r="M82" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Local per-request authorization and draft privacy are tested. Review remaining paid entitlements, explicit content and live eligibility before enabling those flows.</x:v>
       </x:c>
       <x:c r="N82" s="112"/>
-      <x:c r="O82" s="111" t="str"/>
+      <x:c r="O82" s="111" t="str">
+        <x:v>docs/architecture/phase5-slice1-content-model-and-access-design.md</x:v>
+      </x:c>
       <x:c r="P82" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
       <x:c r="Q82" s="111" t="str">
         <x:v>Separate teaser, paid, and internal assets with signed URL gating.</x:v>
       </x:c>
       <x:c r="R82" s="111" t="str">
-        <x:v>Needed for secure access gating.</x:v>
+        <x:v>Local member reads require an active verified test session. Removal/suspension revoke media access. Disabled by default and rejected in production. Real identity, adult uploads and money remain unavailable.</x:v>
       </x:c>
       <x:c r="S82" s="111" t="str">
         <x:v>Preserved Master Tracker row 89; legacy status: 📋 Not Started</x:v>
@@ -23337,23 +23666,23 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C86" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D86" s="111" t="str"/>
       <x:c r="E86" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F86" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G86" s="111" t="str">
         <x:v>Integrate CCBill (primary processor)</x:v>
       </x:c>
       <x:c r="H86" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I86" s="111" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Decision Locked</x:v>
       </x:c>
       <x:c r="J86" s="111" t="str">
         <x:v>Medium</x:v>
@@ -23365,21 +23694,23 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M86" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Build the functioning review site through the current slices. Return to CCBill when review-ready; merchant approval and technical payment integration remain future work.</x:v>
       </x:c>
       <x:c r="N86" s="112"/>
-      <x:c r="O86" s="111" t="str"/>
+      <x:c r="O86" s="111" t="str">
+        <x:v>docs/product/initial-ccbill-inquiry.md; PLAN.md §21; HANDOFF.md safe-content/R2 verification.</x:v>
+      </x:c>
       <x:c r="P86" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q86" s="111" t="str">
-        <x:v>Set up merchant account, API integration, webhook handling, subscription billing.</x:v>
+        <x:v>CCBill is the intended primary processor. Sales/site preparation is underway. Formal merchant approval, API/webhooks and subscription billing remain unimplemented.</x:v>
       </x:c>
       <x:c r="R86" s="111" t="str">
-        <x:v>Processor selected, but merchant application and API/webhook integration have not started.</x:v>
+        <x:v>Inquiry sent and Sales reply received. CCBill requires a fully functioning online site, which may be password protected. The site is being built; no review-ready site, approved account or payment backend is claimed.</x:v>
       </x:c>
       <x:c r="S86" s="111" t="str">
-        <x:v>Preserved Master Tracker row 94; legacy status: 📋 Not Started</x:v>
+        <x:v>Master Tracker row 94; preparation stage reconciled September 10, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="46" customHeight="1">
@@ -23390,14 +23721,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C87" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D87" s="111" t="str"/>
       <x:c r="E87" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F87" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G87" s="111" t="str">
         <x:v>Integrate Epoch (cascade fallback)</x:v>
@@ -23418,18 +23749,18 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M87" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>After core policies/entity details are ready, discuss Epoch fit and any fallback design. Do not implement until the account-specific model is confirmed.</x:v>
       </x:c>
       <x:c r="N87" s="112"/>
       <x:c r="O87" s="111" t="str"/>
       <x:c r="P87" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q87" s="111" t="str">
         <x:v>Set up Epoch as secondary for transactions CCBill declines.</x:v>
       </x:c>
       <x:c r="R87" s="111" t="str">
-        <x:v>Fallback provider selected, but application and technical integration have not started.</x:v>
+        <x:v>CCBill review-site preparation is underway. Epoch is an intended fallback only; outreach, approval and integration have not started.</x:v>
       </x:c>
       <x:c r="S87" s="111" t="str">
         <x:v>Preserved Master Tracker row 95; legacy status: 📋 Not Started</x:v>
@@ -23443,14 +23774,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C88" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D88" s="111" t="str"/>
       <x:c r="E88" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F88" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G88" s="111" t="str">
         <x:v>Build payment cascading logic</x:v>
@@ -23471,18 +23802,18 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M88" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Obtain written technical/commercial confirmation from both processors before implementing cascade routing.</x:v>
       </x:c>
       <x:c r="N88" s="112"/>
       <x:c r="O88" s="111" t="str"/>
       <x:c r="P88" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q88" s="111" t="str">
         <x:v>Route failed CCBill transactions automatically to Epoch before returning decline.</x:v>
       </x:c>
       <x:c r="R88" s="111" t="str">
-        <x:v>Do not implement until CCBill and Epoch confirm the account-specific cascade design in writing.</x:v>
+        <x:v>CCBill review-site preparation is underway. No Epoch outreach or account-specific cascade approval is evidenced; routing is unimplemented.</x:v>
       </x:c>
       <x:c r="S88" s="111" t="str">
         <x:v>Preserved Master Tracker row 96; legacy status: 📋 Not Started</x:v>
@@ -23496,14 +23827,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C89" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D89" s="111" t="str"/>
       <x:c r="E89" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F89" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G89" s="111" t="str">
         <x:v>Implement recurring subscription billing</x:v>
@@ -23524,18 +23855,18 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M89" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Agree the processor-supported payment flow and obtain the required account setup before implementing billing and trusted payment events.</x:v>
       </x:c>
       <x:c r="N89" s="112"/>
       <x:c r="O89" s="111" t="str"/>
       <x:c r="P89" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q89" s="111" t="str">
         <x:v>Create the actual subscription/payment flow through CCBill/Epoch.</x:v>
       </x:c>
       <x:c r="R89" s="111" t="str">
-        <x:v>Implementation not confirmed.</x:v>
+        <x:v>CCBill review-site preparation is underway. Recurring billing and payment-webhook handling are not implemented.</x:v>
       </x:c>
       <x:c r="S89" s="111" t="str">
         <x:v>Preserved Master Tracker row 97; legacy status: 📋 Not Started</x:v>
@@ -23549,14 +23880,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C90" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D90" s="111" t="str"/>
       <x:c r="E90" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F90" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G90" s="111" t="str">
         <x:v>Build renewal / cancel logic</x:v>
@@ -23600,14 +23931,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C91" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D91" s="111" t="str"/>
       <x:c r="E91" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F91" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G91" s="111" t="str">
         <x:v>Tie access gating to subscription status</x:v>
@@ -23651,14 +23982,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C92" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D92" s="111" t="str"/>
       <x:c r="E92" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F92" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G92" s="111" t="str">
         <x:v>Define creator payouts flow</x:v>
@@ -23697,55 +24028,25 @@
       </x:c>
     </x:row>
     <x:row r="93" ht="46" customHeight="1">
-      <x:c r="A93" s="111" t="str">
-        <x:v>LEG-MT-101</x:v>
-      </x:c>
-      <x:c r="B93" s="111" t="str">
-        <x:v>P06</x:v>
-      </x:c>
-      <x:c r="C93" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
-      </x:c>
+      <x:c r="A93" s="111"/>
+      <x:c r="B93" s="111"/>
+      <x:c r="C93" s="111"/>
       <x:c r="D93" s="111" t="str"/>
-      <x:c r="E93" s="111" t="str">
-        <x:v>Legacy-mapped task</x:v>
-      </x:c>
-      <x:c r="F93" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
-      </x:c>
-      <x:c r="G93" s="111" t="str">
-        <x:v>Define Veso wallet / display logic</x:v>
-      </x:c>
-      <x:c r="H93" s="111" t="str">
-        <x:v>In Progress</x:v>
-      </x:c>
-      <x:c r="I93" s="111" t="str">
-        <x:v>Decision Locked</x:v>
-      </x:c>
-      <x:c r="J93" s="111" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="K93" s="111" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
+      <x:c r="E93" s="111"/>
+      <x:c r="F93" s="111"/>
+      <x:c r="G93" s="111"/>
+      <x:c r="H93" s="111"/>
+      <x:c r="I93" s="111"/>
+      <x:c r="J93" s="111"/>
+      <x:c r="K93" s="111"/>
       <x:c r="L93" s="111" t="str"/>
-      <x:c r="M93" s="111" t="str">
-        <x:v>Close the remaining gap: Direction locked: prepaid credits, 1 Veso = 1 USD.</x:v>
-      </x:c>
+      <x:c r="M93" s="111"/>
       <x:c r="N93" s="112"/>
-      <x:c r="O93" s="111" t="str"/>
-      <x:c r="P93" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
-      </x:c>
-      <x:c r="Q93" s="111" t="str">
-        <x:v>Where Veso (1 = $1 USD) appears: balance display, purchase flow, spend flow.</x:v>
-      </x:c>
-      <x:c r="R93" s="111" t="str">
-        <x:v>Direction locked: prepaid credits, 1 Veso = 1 USD. Refund, transfer, expiration, promotional credit, and ledger policies remain.</x:v>
-      </x:c>
-      <x:c r="S93" s="111" t="str">
-        <x:v>Preserved Master Tracker row 101; legacy status: 🔄 In Progress</x:v>
-      </x:c>
+      <x:c r="O93" s="111"/>
+      <x:c r="P93" s="112"/>
+      <x:c r="Q93" s="111"/>
+      <x:c r="R93" s="111"/>
+      <x:c r="S93" s="111"/>
     </x:row>
     <x:row r="94" ht="46" customHeight="1">
       <x:c r="A94" s="111" t="str">
@@ -23755,14 +24056,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C94" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D94" s="111" t="str"/>
       <x:c r="E94" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F94" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G94" s="111" t="str">
         <x:v>Define platform commission model</x:v>
@@ -23808,14 +24109,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C95" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D95" s="111" t="str"/>
       <x:c r="E95" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F95" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G95" s="111" t="str">
         <x:v>Implement chargeback &amp; dispute workflow</x:v>
@@ -23836,18 +24137,18 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M95" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Define account-specific dispute rules and trusted events, then implement the workflow with private-operations authorization and audit.</x:v>
       </x:c>
       <x:c r="N95" s="112"/>
       <x:c r="O95" s="111" t="str"/>
       <x:c r="P95" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q95" s="111" t="str">
         <x:v>Track chargebacks from CCBill/Epoch, alert admin, manage dispute responses.</x:v>
       </x:c>
       <x:c r="R95" s="111" t="str">
-        <x:v>Critical for high-risk adult processing.</x:v>
+        <x:v>CCBill review-site preparation is underway. Processor dispute integration and operational handling remain unimplemented.</x:v>
       </x:c>
       <x:c r="S95" s="111" t="str">
         <x:v>Preserved Master Tracker row 103; legacy status: 📋 Not Started</x:v>
@@ -24258,18 +24559,18 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M103" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Implement trusted transactions/earnings/payout records and private-operations controls before connecting the admin view.</x:v>
       </x:c>
       <x:c r="N103" s="112"/>
       <x:c r="O103" s="111" t="str"/>
       <x:c r="P103" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q103" s="111" t="str">
         <x:v>View all transactions, subscription events, payout queue. Manually trigger or block payouts. View CCBill/Epoch transaction IDs. Filter by date, creator, status.</x:v>
       </x:c>
       <x:c r="R103" s="111" t="str">
-        <x:v>Needed for business operations and dispute resolution.</x:v>
+        <x:v>CCBill review-site preparation is underway. Payment/payout backend and this operations view remain unimplemented.</x:v>
       </x:c>
       <x:c r="S103" s="111" t="str">
         <x:v>Preserved Master Tracker row 112; legacy status: 📋 Not Started</x:v>
@@ -24311,75 +24612,43 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M104" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Confirm processor dispute events and account-specific thresholds before implementing alerts and audited responses.</x:v>
       </x:c>
       <x:c r="N104" s="112"/>
       <x:c r="O104" s="111" t="str"/>
       <x:c r="P104" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q104" s="111" t="str">
-        <x:v>Real-time view of incoming chargebacks from CCBill/Epoch webhooks. Show chargeback rate %, alert when approaching 1% threshold. Log dispute responses.</x:v>
+        <x:v>View verified processor chargeback events, calculate rates, apply confirmed account-specific alert thresholds and log authorized dispute responses.</x:v>
       </x:c>
       <x:c r="R104" s="111" t="str">
-        <x:v>Adult platforms live and die by chargeback rate. Exceeding 1% risks losing your merchant account.</x:v>
+        <x:v>CCBill review-site preparation is underway. No chargeback webhook integration or operational dashboard is implemented.</x:v>
       </x:c>
       <x:c r="S104" s="111" t="str">
         <x:v>Preserved Master Tracker row 113; legacy status: 📋 Not Started</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="46" customHeight="1">
-      <x:c r="A105" s="111" t="str">
-        <x:v>LEG-MT-114</x:v>
-      </x:c>
-      <x:c r="B105" s="111" t="str">
-        <x:v>P11</x:v>
-      </x:c>
-      <x:c r="C105" s="111" t="str">
-        <x:v>Admin and moderation</x:v>
-      </x:c>
+      <x:c r="A105" s="111"/>
+      <x:c r="B105" s="111"/>
+      <x:c r="C105" s="111"/>
       <x:c r="D105" s="111" t="str"/>
-      <x:c r="E105" s="111" t="str">
-        <x:v>Legacy-mapped task</x:v>
-      </x:c>
-      <x:c r="F105" s="111" t="str">
-        <x:v>Private operations &amp; moderation</x:v>
-      </x:c>
-      <x:c r="G105" s="111" t="str">
-        <x:v>Build Veso / wallet admin view</x:v>
-      </x:c>
-      <x:c r="H105" s="111" t="str">
-        <x:v>Not Started</x:v>
-      </x:c>
-      <x:c r="I105" s="111" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="J105" s="111" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="K105" s="111" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
-      <x:c r="L105" s="111" t="str">
-        <x:v>Private-operations security gates</x:v>
-      </x:c>
-      <x:c r="M105" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
-      </x:c>
+      <x:c r="E105" s="111"/>
+      <x:c r="F105" s="111"/>
+      <x:c r="G105" s="111"/>
+      <x:c r="H105" s="111"/>
+      <x:c r="I105" s="111"/>
+      <x:c r="J105" s="111"/>
+      <x:c r="K105" s="111"/>
+      <x:c r="L105" s="111"/>
+      <x:c r="M105" s="111"/>
       <x:c r="N105" s="112"/>
-      <x:c r="O105" s="111" t="str"/>
-      <x:c r="P105" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
-      </x:c>
-      <x:c r="Q105" s="111" t="str">
-        <x:v>View all Veso balances across users. See top-up history, spend history, manual adjustments. Ability to issue Veso credits (e.g., for promotions or support resolutions).</x:v>
-      </x:c>
-      <x:c r="R105" s="111" t="str">
-        <x:v>Needed once Veso is live. Also useful for resolving billing disputes.</x:v>
-      </x:c>
-      <x:c r="S105" s="111" t="str">
-        <x:v>Preserved Master Tracker row 114; legacy status: 📋 Not Started</x:v>
-      </x:c>
+      <x:c r="O105" s="111"/>
+      <x:c r="P105" s="112"/>
+      <x:c r="Q105" s="111"/>
+      <x:c r="R105" s="111"/>
+      <x:c r="S105" s="111"/>
     </x:row>
     <x:row r="106" ht="46" customHeight="1">
       <x:c r="A106" s="111" t="str">
@@ -25298,18 +25567,18 @@
       </x:c>
       <x:c r="L123" s="111" t="str"/>
       <x:c r="M123" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Define beta testing and its payment method with the relevant functional slice. No payment implementation alternative is selected.</x:v>
       </x:c>
       <x:c r="N123" s="112"/>
       <x:c r="O123" s="111" t="str"/>
       <x:c r="P123" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
       <x:c r="Q123" s="111" t="str">
         <x:v>Define who tests, what gets tested, how feedback is captured.</x:v>
       </x:c>
       <x:c r="R123" s="111" t="str">
-        <x:v>Recommended before public launch.</x:v>
+        <x:v>Launch features and live-use controls remain applicable. Beta payment method is unresolved.</x:v>
       </x:c>
       <x:c r="S123" s="111" t="str">
         <x:v>Preserved Master Tracker row 135; legacy status: 📋 Not Started</x:v>
@@ -25459,18 +25728,18 @@
         <x:v>Founder + provider response</x:v>
       </x:c>
       <x:c r="M126" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Test the agreed implemented payment flow in the appropriate provider test environment. Include cascade only after written confirmation.</x:v>
       </x:c>
       <x:c r="N126" s="112"/>
       <x:c r="O126" s="111" t="str"/>
       <x:c r="P126" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q126" s="111" t="str">
         <x:v>CCBill → Epoch cascade, subscription lifecycle, renewal, cancel, chargebacks.</x:v>
       </x:c>
       <x:c r="R126" s="111" t="str">
-        <x:v>Critical for revenue reliability.</x:v>
+        <x:v>CCBill review-site preparation is underway. No payment integration exists to test yet; no passing payment tests are claimed.</x:v>
       </x:c>
       <x:c r="S126" s="111" t="str">
         <x:v>Preserved Master Tracker row 138; legacy status: 📋 Not Started</x:v>
@@ -25632,108 +25901,46 @@
       </x:c>
     </x:row>
     <x:row r="130" ht="46" customHeight="1">
-      <x:c r="A130" s="111" t="str">
-        <x:v>LEG-MT-143</x:v>
-      </x:c>
-      <x:c r="B130" s="111" t="str">
-        <x:v>P06</x:v>
-      </x:c>
-      <x:c r="C130" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
-      </x:c>
+      <x:c r="A130" s="111"/>
+      <x:c r="B130" s="111"/>
+      <x:c r="C130" s="111"/>
       <x:c r="D130" s="111" t="str"/>
-      <x:c r="E130" s="111" t="str">
-        <x:v>Legacy-mapped task</x:v>
-      </x:c>
-      <x:c r="F130" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
-      </x:c>
-      <x:c r="G130" s="111" t="str">
-        <x:v>Build Veso recharge UI</x:v>
-      </x:c>
-      <x:c r="H130" s="111" t="str">
-        <x:v>Not Started</x:v>
-      </x:c>
-      <x:c r="I130" s="111" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="J130" s="111" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="K130" s="111" t="str">
-        <x:v>Engineering</x:v>
-      </x:c>
+      <x:c r="E130" s="111"/>
+      <x:c r="F130" s="111"/>
+      <x:c r="G130" s="111"/>
+      <x:c r="H130" s="111"/>
+      <x:c r="I130" s="111"/>
+      <x:c r="J130" s="111"/>
+      <x:c r="K130" s="111"/>
       <x:c r="L130" s="111" t="str"/>
-      <x:c r="M130" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
-      </x:c>
+      <x:c r="M130" s="111"/>
       <x:c r="N130" s="112"/>
-      <x:c r="O130" s="111" t="str"/>
-      <x:c r="P130" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
-      </x:c>
-      <x:c r="Q130" s="111" t="str">
-        <x:v>Design and implement Add/Recharge Vesos with presets, payment summary, receipt, and transaction history. Visual reference: E-Pal Buff recharge.</x:v>
-      </x:c>
-      <x:c r="R130" s="111" t="str">
-        <x:v>Launch-critical. 1 Veso = 1 USD.</x:v>
-      </x:c>
-      <x:c r="S130" s="111" t="str">
-        <x:v>Preserved Master Tracker row 143; legacy status: 📋 Not Started</x:v>
-      </x:c>
+      <x:c r="O130" s="111"/>
+      <x:c r="P130" s="112"/>
+      <x:c r="Q130" s="111"/>
+      <x:c r="R130" s="111"/>
+      <x:c r="S130" s="111"/>
     </x:row>
     <x:row r="131" ht="46" customHeight="1">
-      <x:c r="A131" s="111" t="str">
-        <x:v>LEG-MT-144</x:v>
-      </x:c>
-      <x:c r="B131" s="111" t="str">
-        <x:v>P06</x:v>
-      </x:c>
-      <x:c r="C131" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
-      </x:c>
+      <x:c r="A131" s="111"/>
+      <x:c r="B131" s="111"/>
+      <x:c r="C131" s="111"/>
       <x:c r="D131" s="111" t="str"/>
-      <x:c r="E131" s="111" t="str">
-        <x:v>Legacy-mapped task</x:v>
-      </x:c>
-      <x:c r="F131" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
-      </x:c>
-      <x:c r="G131" s="111" t="str">
-        <x:v>Define Veso terms and ledger policies</x:v>
-      </x:c>
-      <x:c r="H131" s="111" t="str">
-        <x:v>In Progress</x:v>
-      </x:c>
-      <x:c r="I131" s="111" t="str">
-        <x:v>Decision Locked</x:v>
-      </x:c>
-      <x:c r="J131" s="111" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="K131" s="111" t="str">
-        <x:v>Founder</x:v>
-      </x:c>
-      <x:c r="L131" s="111" t="str">
-        <x:v>Counsel / founder decision</x:v>
-      </x:c>
-      <x:c r="M131" s="111" t="str">
-        <x:v>Close the remaining gap: Use E-Pal as product research only; draft independent policies for Pumdoki with processor/legal review.</x:v>
-      </x:c>
+      <x:c r="E131" s="111"/>
+      <x:c r="F131" s="111"/>
+      <x:c r="G131" s="111"/>
+      <x:c r="H131" s="111"/>
+      <x:c r="I131" s="111"/>
+      <x:c r="J131" s="111"/>
+      <x:c r="K131" s="111"/>
+      <x:c r="L131" s="111"/>
+      <x:c r="M131" s="111"/>
       <x:c r="N131" s="112"/>
-      <x:c r="O131" s="111" t="str"/>
-      <x:c r="P131" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
-      </x:c>
-      <x:c r="Q131" s="111" t="str">
-        <x:v>Define purchased vs promotional Veso, refunds, expiration, transfer, account closure, chargebacks, and creator earnings conversion.</x:v>
-      </x:c>
-      <x:c r="R131" s="111" t="str">
-        <x:v>Use E-Pal as product research only; draft independent policies for Pumdoki with processor/legal review.</x:v>
-      </x:c>
-      <x:c r="S131" s="111" t="str">
-        <x:v>Preserved Master Tracker row 144; legacy status: 🔄 In Progress</x:v>
-      </x:c>
+      <x:c r="O131" s="111"/>
+      <x:c r="P131" s="112"/>
+      <x:c r="Q131" s="111"/>
+      <x:c r="R131" s="111"/>
+      <x:c r="S131" s="111"/>
     </x:row>
     <x:row r="132" ht="46" customHeight="1">
       <x:c r="A132" s="111" t="str">
@@ -25743,14 +25950,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C132" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D132" s="111" t="str"/>
       <x:c r="E132" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F132" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G132" s="111" t="str">
         <x:v>Implement tipping / Send Love</x:v>
@@ -25769,18 +25976,18 @@
       </x:c>
       <x:c r="L132" s="111" t="str"/>
       <x:c r="M132" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Define tipping funding with the beta payment method and processor terms.</x:v>
       </x:c>
       <x:c r="N132" s="112"/>
       <x:c r="O132" s="111" t="str"/>
       <x:c r="P132" s="112" t="n">
-        <x:v>46271.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
       <x:c r="Q132" s="111" t="str">
-        <x:v>Allow members to tip creators using Veso with idempotent ledger transfers and creator pending earnings.</x:v>
+        <x:v>Tipping/Send Love remains launch scope. Paid flows need idempotent payment evidence, creator earnings and refund controls.</x:v>
       </x:c>
       <x:c r="R132" s="111" t="str">
-        <x:v>Moved from backlog into MVP launch scope.</x:v>
+        <x:v>Historically moved from backlog into launch scope. Beta payment method remains unresolved.</x:v>
       </x:c>
       <x:c r="S132" s="111" t="str">
         <x:v>Preserved Master Tracker row 145; legacy status: 📋 Not Started</x:v>
@@ -25794,14 +26001,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C133" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D133" s="111" t="str"/>
       <x:c r="E133" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F133" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G133" s="111" t="str">
         <x:v>Implement PPV purchases</x:v>
@@ -25820,18 +26027,18 @@
       </x:c>
       <x:c r="L133" s="111" t="str"/>
       <x:c r="M133" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Define PPV funding with the beta payment method and processor terms. Preserve durable entitlements and reconciliation.</x:v>
       </x:c>
       <x:c r="N133" s="112"/>
       <x:c r="O133" s="111" t="str"/>
       <x:c r="P133" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
       <x:c r="Q133" s="111" t="str">
-        <x:v>Allow members to unlock individual creator content with Veso and durable entitlement records.</x:v>
+        <x:v>Unlock individual photos/videos or bundles using the agreed beta payment method, with durable asset-level entitlements.</x:v>
       </x:c>
       <x:c r="R133" s="111" t="str">
-        <x:v>Moved from backlog into MVP launch scope.</x:v>
+        <x:v>Historically moved from backlog into launch scope. Payment method remains unresolved.</x:v>
       </x:c>
       <x:c r="S133" s="111" t="str">
         <x:v>Preserved Master Tracker row 146; legacy status: 📋 Not Started</x:v>
@@ -26469,14 +26676,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C146" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D146" s="111" t="str"/>
       <x:c r="E146" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F146" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G146" s="111" t="str">
         <x:v>Decide commission and payout model</x:v>
@@ -26738,14 +26945,14 @@
         <x:v>P06</x:v>
       </x:c>
       <x:c r="C151" s="111" t="str">
-        <x:v>Veso, payments, subscriptions, tipping, and PPV</x:v>
+        <x:v>Payments, subscriptions, tipping, and PPV</x:v>
       </x:c>
       <x:c r="D151" s="111" t="str"/>
       <x:c r="E151" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F151" s="111" t="str">
-        <x:v>Money, Veso &amp; entitlements</x:v>
+        <x:v>Payments &amp; entitlements</x:v>
       </x:c>
       <x:c r="G151" s="111" t="str">
         <x:v>Confirm CCBill → Epoch cascade</x:v>
@@ -26764,18 +26971,18 @@
       </x:c>
       <x:c r="L151" s="111" t="str"/>
       <x:c r="M151" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Obtain written account-specific technical and commercial confirmation from CCBill and Epoch before any fallback implementation.</x:v>
       </x:c>
       <x:c r="N151" s="112"/>
       <x:c r="O151" s="111" t="str"/>
       <x:c r="P151" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q151" s="111" t="str">
         <x:v>Obtain written technical and commercial confirmation before implementing fallback payment routing.</x:v>
       </x:c>
       <x:c r="R151" s="111" t="str">
-        <x:v>Merchant applications have not started.</x:v>
+        <x:v>CCBill Sales has replied and site preparation is underway. Epoch outreach and cascade confirmation remain pending.</x:v>
       </x:c>
       <x:c r="S151" s="111" t="str">
         <x:v>Preserved Master Tracker row 164; legacy status: 📋 Not Started</x:v>
@@ -27255,20 +27462,20 @@
         <x:v>Phase 4–6 dependencies</x:v>
       </x:c>
       <x:c r="M160" s="111" t="str">
-        <x:v>Do not begin the product slice until creator approval, media entitlement, and payment-ledger prerequisites are accepted.</x:v>
+        <x:v>Continue controlled test slices. Real beta needs applicable creator/content/access/operations controls. Paid flows also need processor evidence and reconciliation.</x:v>
       </x:c>
       <x:c r="N160" s="112"/>
       <x:c r="O160" s="111" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#11-phase-7--core-end-to-end-vertical-slice</x:v>
       </x:c>
       <x:c r="P160" s="112" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46274.666666666664</x:v>
       </x:c>
       <x:c r="Q160" s="111" t="str">
-        <x:v>Member discovers an approved creator, acquires Veso, purchases access, consumes authorized media, and produces auditable records without manual database edits.</x:v>
+        <x:v>Member discovers an eligible creator and accesses authorized content with auditable records. Purchases and tips follow the beta payment method, still unresolved.</x:v>
       </x:c>
       <x:c r="R160" s="111" t="str">
-        <x:v>Explicit dependency marker so Phase 7 is visible even though no legacy tracker row represented it.</x:v>
+        <x:v>Phase 7 remains incomplete. Payment, entitlement, earnings and refund controls remain necessary for paid beta flows.</x:v>
       </x:c>
       <x:c r="S160" s="111" t="str">
         <x:v>PLAN.md Phase 7 exit gate</x:v>
@@ -27500,13 +27707,13 @@
     <x:mergeCell ref="A2:S2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="H4:H164">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Done"/>
-    <x:cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="In Progress"/>
-    <x:cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="In Review"/>
-    <x:cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Blocked"/>
-    <x:cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="Not Started"/>
-    <x:cfRule type="containsText" dxfId="20" priority="6" operator="containsText" text="Ready"/>
-    <x:cfRule type="containsText" dxfId="24" priority="7" operator="containsText" text="Deferred"/>
+    <x:cfRule type="containsText" dxfId="40" priority="1" operator="containsText" text="Done"/>
+    <x:cfRule type="containsText" dxfId="41" priority="2" operator="containsText" text="In Progress"/>
+    <x:cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="In Review"/>
+    <x:cfRule type="containsText" dxfId="43" priority="4" operator="containsText" text="Blocked"/>
+    <x:cfRule type="containsText" dxfId="44" priority="5" operator="containsText" text="Not Started"/>
+    <x:cfRule type="containsText" dxfId="45" priority="6" operator="containsText" text="Ready"/>
+    <x:cfRule type="containsText" dxfId="46" priority="7" operator="containsText" text="Deferred"/>
   </x:conditionalFormatting>
   <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="H4:H164">
@@ -27527,7 +27734,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc07a6951aab4717"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38016ecd093840d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/product/Pumdoki_MasterTracker_V4.xlsx
+++ b/docs/product/Pumdoki_MasterTracker_V4.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Re81aaddfa62f47b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" r:id="Rb5047abd3826488d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" r:id="R005d9f5f39f94900"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Assumptions" sheetId="4" r:id="Recd0c28599924730"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💸 Expense Tracker" sheetId="5" r:id="R39c9842b214f462a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Overview 2026-08-16" sheetId="6" r:id="Refdec6ae1cc1424c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="7" r:id="R8a341beb143b467c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="8" r:id="R760da7d95eb34f00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Tracker" sheetId="9" r:id="R322ee4ad41984bca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Blocker Queue" sheetId="10" r:id="R7ce6841af0e74069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="11" r:id="R445718308a854512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Register" sheetId="12" r:id="R4e090ff29e2949a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Budget" sheetId="13" r:id="Rb6b02667adec4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R716f6b96a1924d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Tracker" sheetId="2" r:id="R93dcd7e29dec4b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" r:id="Rd0a8e2b0220d4ba5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Assumptions" sheetId="4" r:id="R3eac5e89d79e4665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💸 Expense Tracker" sheetId="5" r:id="Rba6512b08e9045d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Overview 2026-08-16" sheetId="6" r:id="Rd21724ac9677451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="7" r:id="Ra8f00a8c14254370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="8" r:id="R48e6850903f243f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Tracker" sheetId="9" r:id="R33358fc467cd41e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review &amp; Blocker Queue" sheetId="10" r:id="R3c9b8cfc375648e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="11" r:id="R508e271d11dd4542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Register" sheetId="12" r:id="Re0e57af217b94f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Budget" sheetId="13" r:id="R097f08b44fd9486a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -580,9 +580,6 @@
     <x:t xml:space="preserve">Build 'Your Activity' page</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Nice-to-have post-launch. Defer if time is tight.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Improve Create Post ('Moments') modal</x:t>
   </x:si>
   <x:si>
@@ -1133,15 +1130,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Web-first; mobile later.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">'Your Activity' page</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UX</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Nice-to-have. Build post-launch if time is tight during MVP push.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">TikTok paid creator promotions</x:t>
@@ -1742,7 +1730,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1852,6 +1840,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFC7CE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1990,7 +1983,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="220">
+  <x:cellXfs count="221">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -2641,6 +2634,9 @@
     <x:xf numFmtId="0" fontId="30" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -3026,7 +3022,7 @@
         <x:color rgb="FF246B3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -3037,7 +3033,7 @@
         <x:color rgb="FF805E00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1C9"/>
         </x:patternFill>
       </x:fill>
@@ -3048,7 +3044,7 @@
         <x:color rgb="FF245B84"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBFA"/>
         </x:patternFill>
       </x:fill>
@@ -3059,7 +3055,7 @@
         <x:color rgb="FF8A2432"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF9D7DC"/>
         </x:patternFill>
       </x:fill>
@@ -3070,7 +3066,7 @@
         <x:color rgb="FF5D535C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECE8EC"/>
         </x:patternFill>
       </x:fill>
@@ -3081,7 +3077,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -3092,7 +3088,7 @@
         <x:color rgb="FF246B3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -3103,7 +3099,7 @@
         <x:color rgb="FF805E00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1C9"/>
         </x:patternFill>
       </x:fill>
@@ -3114,7 +3110,7 @@
         <x:color rgb="FF245B84"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBFA"/>
         </x:patternFill>
       </x:fill>
@@ -3125,7 +3121,7 @@
         <x:color rgb="FF8A2432"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF9D7DC"/>
         </x:patternFill>
       </x:fill>
@@ -3136,7 +3132,7 @@
         <x:color rgb="FF5D535C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECE8EC"/>
         </x:patternFill>
       </x:fill>
@@ -3147,7 +3143,7 @@
         <x:color rgb="FF3D1A3E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFAE1EC"/>
         </x:patternFill>
       </x:fill>
@@ -3158,7 +3154,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -3169,7 +3165,7 @@
         <x:color rgb="FF246B3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -3180,7 +3176,7 @@
         <x:color rgb="FF805E00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1C9"/>
         </x:patternFill>
       </x:fill>
@@ -3191,7 +3187,7 @@
         <x:color rgb="FF245B84"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBFA"/>
         </x:patternFill>
       </x:fill>
@@ -3202,7 +3198,7 @@
         <x:color rgb="FF8A2432"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF9D7DC"/>
         </x:patternFill>
       </x:fill>
@@ -3213,7 +3209,7 @@
         <x:color rgb="FF5D535C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECE8EC"/>
         </x:patternFill>
       </x:fill>
@@ -3224,7 +3220,7 @@
         <x:color rgb="FF3D1A3E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFAE1EC"/>
         </x:patternFill>
       </x:fill>
@@ -3235,7 +3231,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -3246,7 +3242,7 @@
         <x:color rgb="FF246B3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -3257,7 +3253,7 @@
         <x:color rgb="FF805E00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1C9"/>
         </x:patternFill>
       </x:fill>
@@ -3268,7 +3264,7 @@
         <x:color rgb="FF245B84"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBFA"/>
         </x:patternFill>
       </x:fill>
@@ -3279,7 +3275,7 @@
         <x:color rgb="FF8A2432"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF9D7DC"/>
         </x:patternFill>
       </x:fill>
@@ -3290,7 +3286,7 @@
         <x:color rgb="FF5D535C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECE8EC"/>
         </x:patternFill>
       </x:fill>
@@ -3301,7 +3297,7 @@
         <x:color rgb="FF3D1A3E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFAE1EC"/>
         </x:patternFill>
       </x:fill>
@@ -3312,7 +3308,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -3323,7 +3319,7 @@
         <x:color rgb="FF246B3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -3334,7 +3330,7 @@
         <x:color rgb="FF805E00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1C9"/>
         </x:patternFill>
       </x:fill>
@@ -3345,7 +3341,7 @@
         <x:color rgb="FF245B84"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBFA"/>
         </x:patternFill>
       </x:fill>
@@ -3356,7 +3352,7 @@
         <x:color rgb="FF8A2432"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF9D7DC"/>
         </x:patternFill>
       </x:fill>
@@ -3367,7 +3363,7 @@
         <x:color rgb="FF5D535C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFECE8EC"/>
         </x:patternFill>
       </x:fill>
@@ -3378,7 +3374,7 @@
         <x:color rgb="FF3D1A3E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFAE1EC"/>
         </x:patternFill>
       </x:fill>
@@ -3389,7 +3385,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -3400,7 +3396,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -3411,7 +3407,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -3943,7 +3939,7 @@
       <x:c r="D13" s="151"/>
       <x:c r="E13" s="150" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F13" s="151"/>
       <x:c r="G13" s="150" t="n">
@@ -3958,7 +3954,7 @@
       <x:c r="J13" s="151"/>
       <x:c r="K13" s="150" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L13" s="151"/>
       <x:c r="M13" s="158" t="n">
@@ -4536,15 +4532,15 @@
       </x:c>
       <x:c r="F26" s="111" t="n">
         <x:f>'Phase Roadmap'!F12</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G26" s="119" t="n">
         <x:f>'Phase Roadmap'!G12</x:f>
-        <x:v>0.4444444444444444</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="H26" s="111" t="n">
         <x:f>'Phase Roadmap'!H12</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I26" s="111" t="n">
         <x:f>'Phase Roadmap'!I12</x:f>
@@ -4560,11 +4556,11 @@
       </x:c>
       <x:c r="L26" s="111" t="str">
         <x:f>'Phase Roadmap'!L12</x:f>
-        <x:v>Connect discovery, Store and feed remain launch scope. Connect means online, price and language filters.</x:v>
+        <x:v>Feed, Store and Connect remain launch scope (online/price/language discovery). Your Activity /activity UI is an explicit example-data preview; real member history remains pending.</x:v>
       </x:c>
       <x:c r="M26" s="111" t="str">
         <x:f>'Phase Roadmap'!M12</x:f>
-        <x:v>Integrate content and access controls. Define service/order and beta payment rules with the relevant slice.</x:v>
+        <x:v>Integrate content/access, service/order and beta payment rules. Connect Your Activity to authenticated P05/P06/P07 data.</x:v>
       </x:c>
       <x:c r="N26" s="111" t="str">
         <x:f>'Phase Roadmap'!O12</x:f>
@@ -6367,7 +6363,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46f208786e734731"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb3347981fce4ac2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7489,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe125cfc69b24b7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3a41e2639444792"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8344,7 +8340,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf4d4d30ca3e45c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a6f89c65da04024"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10338,63 +10334,63 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B80" s="17" t="str">
-        <x:v>Member activity history: posts liked, content purchased, subscriptions and payment history. Lower priority.</x:v>
-      </x:c>
-      <x:c r="C80" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D80" s="19" t="s">
-        <x:v>186</x:v>
+        <x:v>P08 member history: liked posts, purchases, subscriptions and payment history. UI preview first; account-backed events follow.</x:v>
+      </x:c>
+      <x:c r="C80" s="220" t="str">
+        <x:v>🔄 In Progress</x:v>
+      </x:c>
+      <x:c r="D80" s="19" t="str">
+        <x:v>Example-data /activity UI with search/filters and sidebar/header links. Real account API and persistence pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15.75" customHeight="1">
       <x:c r="A81" s="20" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B81" s="21" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="B81" s="21" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="C81" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D81" s="22" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15.75" customHeight="1">
       <x:c r="A82" s="16" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B82" s="17" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="B82" s="17" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="C82" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D82" s="19" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15.75" customHeight="1">
       <x:c r="A83" s="20" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B83" s="21" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="B83" s="21" t="s">
-        <x:v>194</x:v>
       </x:c>
       <x:c r="C83" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D83" s="22" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="30.75" customHeight="1">
       <x:c r="A84" s="16" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B84" s="17" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="B84" s="17" t="s">
-        <x:v>197</x:v>
       </x:c>
       <x:c r="C84" s="23" t="inlineStr">
         <x:is>
@@ -10409,21 +10405,21 @@
     </x:row>
     <x:row r="85" ht="18.75" customHeight="1">
       <x:c r="A85" s="25" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B85" s="26" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="B85" s="26" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="C85" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D85" s="27" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15.75" customHeight="1">
       <x:c r="A86" s="15" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B86" s="2"/>
       <x:c r="C86" s="2"/>
@@ -10431,91 +10427,91 @@
     </x:row>
     <x:row r="87" ht="15.75" customHeight="1">
       <x:c r="A87" s="16" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B87" s="17" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="B87" s="17" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="C87" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D87" s="19" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15.75" customHeight="1">
       <x:c r="A88" s="20" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B88" s="21" t="s">
         <x:v>205</x:v>
-      </x:c>
-      <x:c r="B88" s="21" t="s">
-        <x:v>206</x:v>
       </x:c>
       <x:c r="C88" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D88" s="22" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15.75" customHeight="1">
       <x:c r="A89" s="16" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B89" s="17" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="B89" s="17" t="s">
-        <x:v>209</x:v>
       </x:c>
       <x:c r="C89" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D89" s="19" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15.75" customHeight="1">
       <x:c r="A90" s="20" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B90" s="21" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="B90" s="21" t="s">
-        <x:v>212</x:v>
       </x:c>
       <x:c r="C90" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D90" s="22" t="s">
-        <x:v>213</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15.75" customHeight="1">
       <x:c r="A91" s="16" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B91" s="17" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="B91" s="17" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="C91" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D91" s="19" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="27.75" customHeight="1">
       <x:c r="A92" s="28" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B92" s="29" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="B92" s="29" t="s">
-        <x:v>218</x:v>
       </x:c>
       <x:c r="C92" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D92" s="31" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15.75" customHeight="1">
       <x:c r="A93" s="15" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B93" s="2"/>
       <x:c r="C93" s="2"/>
@@ -10523,10 +10519,10 @@
     </x:row>
     <x:row r="94" ht="15.75" customHeight="1">
       <x:c r="A94" s="32" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B94" s="33" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="B94" s="33" t="s">
-        <x:v>222</x:v>
       </x:c>
       <x:c r="C94" s="217" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -10537,10 +10533,10 @@
     </x:row>
     <x:row r="95" ht="15.75" customHeight="1">
       <x:c r="A95" s="20" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B95" s="21" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="B95" s="21" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="C95" s="24" t="inlineStr">
         <x:is>
@@ -10553,10 +10549,10 @@
     </x:row>
     <x:row r="96" ht="15.75" customHeight="1">
       <x:c r="A96" s="16" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B96" s="17" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="B96" s="17" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="C96" s="24" t="s">
         <x:v>21</x:v>
@@ -10567,10 +10563,10 @@
     </x:row>
     <x:row r="97" ht="15.75" customHeight="1">
       <x:c r="A97" s="20" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B97" s="21" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="B97" s="21" t="s">
-        <x:v>228</x:v>
       </x:c>
       <x:c r="C97" s="24" t="s">
         <x:v>21</x:v>
@@ -10581,44 +10577,44 @@
     </x:row>
     <x:row r="98" ht="15.75" customHeight="1">
       <x:c r="A98" s="16" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B98" s="17" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="B98" s="17" t="s">
-        <x:v>230</x:v>
       </x:c>
       <x:c r="C98" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D98" s="19" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15.75" customHeight="1">
       <x:c r="A99" s="20" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B99" s="21" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="B99" s="21" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="C99" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D99" s="22" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15.75" customHeight="1">
       <x:c r="A100" s="16" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B100" s="17" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="B100" s="17" t="s">
-        <x:v>236</x:v>
       </x:c>
       <x:c r="C100" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D100" s="19" t="s">
-        <x:v>237</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15.75" customHeight="1">
@@ -10629,10 +10625,10 @@
     </x:row>
     <x:row r="102" ht="15.75" customHeight="1">
       <x:c r="A102" s="16" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B102" s="17" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="B102" s="17" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="C102" s="24" t="s">
         <x:v>21</x:v>
@@ -10645,10 +10641,10 @@
     </x:row>
     <x:row r="103" ht="15.75" customHeight="1">
       <x:c r="A103" s="20" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B103" s="21" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="B103" s="21" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="C103" s="24" t="s">
         <x:v>21</x:v>
@@ -10659,21 +10655,21 @@
     </x:row>
     <x:row r="104" ht="27.75" customHeight="1">
       <x:c r="A104" s="36" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B104" s="37" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="B104" s="37" t="s">
-        <x:v>243</x:v>
       </x:c>
       <x:c r="C104" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D104" s="38" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15.75" customHeight="1">
       <x:c r="A105" s="15" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B105" s="2"/>
       <x:c r="C105" s="2"/>
@@ -10695,38 +10691,38 @@
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="20" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B107" s="21" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="B107" s="21" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="C107" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D107" s="22" t="s">
-        <x:v>248</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
       <x:c r="A108" s="16" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B108" s="17" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="B108" s="17" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="C108" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D108" s="19" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="24" hidden="0" customHeight="1">
       <x:c r="A109" s="20" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B109" s="21" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="B109" s="21" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="C109" s="24" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -10737,38 +10733,38 @@
     </x:row>
     <x:row r="110" ht="15.75" customHeight="1">
       <x:c r="A110" s="16" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B110" s="17" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="B110" s="17" t="s">
-        <x:v>255</x:v>
       </x:c>
       <x:c r="C110" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D110" s="19" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15.75" customHeight="1">
       <x:c r="A111" s="20" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B111" s="21" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="B111" s="21" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D111" s="22" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15.75" customHeight="1">
       <x:c r="A112" s="16" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B112" s="17" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="B112" s="17" t="s">
-        <x:v>261</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s">
         <x:v>21</x:v>
@@ -10779,7 +10775,7 @@
     </x:row>
     <x:row r="113" ht="15.75" customHeight="1">
       <x:c r="A113" s="20" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B113" s="21" t="str">
         <x:v>View verified processor chargeback events, calculate rates, apply confirmed account-specific alert thresholds and log authorized dispute responses.</x:v>
@@ -10799,52 +10795,52 @@
     </x:row>
     <x:row r="115" ht="15.75" customHeight="1">
       <x:c r="A115" s="20" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B115" s="21" t="s">
         <x:v>263</x:v>
-      </x:c>
-      <x:c r="B115" s="21" t="s">
-        <x:v>264</x:v>
       </x:c>
       <x:c r="C115" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D115" s="22" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15.75" customHeight="1">
       <x:c r="A116" s="16" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B116" s="17" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="B116" s="17" t="s">
-        <x:v>267</x:v>
       </x:c>
       <x:c r="C116" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D116" s="19" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15.75" customHeight="1">
       <x:c r="A117" s="20" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B117" s="21" t="s">
         <x:v>269</x:v>
-      </x:c>
-      <x:c r="B117" s="21" t="s">
-        <x:v>270</x:v>
       </x:c>
       <x:c r="C117" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D117" s="22" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="24" hidden="0" customHeight="1">
       <x:c r="A118" s="36" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B118" s="37" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="B118" s="37" t="s">
-        <x:v>273</x:v>
       </x:c>
       <x:c r="C118" s="30" t="s">
         <x:v>21</x:v>
@@ -10855,7 +10851,7 @@
     </x:row>
     <x:row r="119" ht="15.75" customHeight="1">
       <x:c r="A119" s="15" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B119" s="2"/>
       <x:c r="C119" s="2"/>
@@ -10863,10 +10859,10 @@
     </x:row>
     <x:row r="120" ht="15.75" customHeight="1">
       <x:c r="A120" s="32" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B120" s="33" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="B120" s="33" t="s">
-        <x:v>276</x:v>
       </x:c>
       <x:c r="C120" s="39" t="s">
         <x:v>21</x:v>
@@ -10877,52 +10873,52 @@
     </x:row>
     <x:row r="121" ht="15.75" customHeight="1">
       <x:c r="A121" s="20" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B121" s="21" t="s">
         <x:v>277</x:v>
-      </x:c>
-      <x:c r="B121" s="21" t="s">
-        <x:v>278</x:v>
       </x:c>
       <x:c r="C121" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D121" s="22" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15.75" customHeight="1">
       <x:c r="A122" s="16" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B122" s="17" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="B122" s="17" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="C122" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D122" s="19" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15.75" customHeight="1">
       <x:c r="A123" s="20" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B123" s="21" t="s">
         <x:v>283</x:v>
-      </x:c>
-      <x:c r="B123" s="21" t="s">
-        <x:v>284</x:v>
       </x:c>
       <x:c r="C123" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D123" s="22" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="24" hidden="0" customHeight="1">
       <x:c r="A124" s="36" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B124" s="37" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="B124" s="37" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="C124" s="30" t="str">
         <x:v>🔄 In Progress</x:v>
@@ -10933,7 +10929,7 @@
     </x:row>
     <x:row r="125" ht="15.75" customHeight="1">
       <x:c r="A125" s="15" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B125" s="2"/>
       <x:c r="C125" s="2"/>
@@ -10941,105 +10937,105 @@
     </x:row>
     <x:row r="126" ht="15.75" customHeight="1">
       <x:c r="A126" s="32" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B126" s="33" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="B126" s="33" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="C126" s="39" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D126" s="35" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15.75" customHeight="1">
       <x:c r="A127" s="20" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B127" s="21" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="B127" s="21" t="s">
-        <x:v>293</x:v>
       </x:c>
       <x:c r="C127" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D127" s="22" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15.75" customHeight="1">
       <x:c r="A128" s="16" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B128" s="17" t="s">
         <x:v>295</x:v>
-      </x:c>
-      <x:c r="B128" s="17" t="s">
-        <x:v>296</x:v>
       </x:c>
       <x:c r="C128" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D128" s="19" t="s">
-        <x:v>297</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15.75" customHeight="1">
       <x:c r="A129" s="20" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B129" s="21" t="s">
         <x:v>298</x:v>
-      </x:c>
-      <x:c r="B129" s="21" t="s">
-        <x:v>299</x:v>
       </x:c>
       <x:c r="C129" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D129" s="22" t="s">
-        <x:v>300</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15.75" customHeight="1">
       <x:c r="A130" s="16" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B130" s="17" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B130" s="17" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C130" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D130" s="19" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" customHeight="1">
       <x:c r="A131" s="20" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B131" s="21" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B131" s="21" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C131" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D131" s="22" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15.75" customHeight="1">
       <x:c r="A132" s="40" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B132" s="41" t="s">
         <x:v>307</x:v>
-      </x:c>
-      <x:c r="B132" s="41" t="s">
-        <x:v>308</x:v>
       </x:c>
       <x:c r="C132" s="42" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D132" s="43" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15.75" customHeight="1">
       <x:c r="A133" s="15" t="s">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B133" s="2"/>
       <x:c r="C133" s="2"/>
@@ -11047,10 +11043,10 @@
     </x:row>
     <x:row r="134" ht="24" hidden="0" customHeight="1">
       <x:c r="A134" s="32" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B134" s="33" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B134" s="33" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C134" s="44" t="s">
         <x:v>26</x:v>
@@ -11061,52 +11057,52 @@
     </x:row>
     <x:row r="135" ht="15.75" customHeight="1">
       <x:c r="A135" s="20" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B135" s="21" t="s">
         <x:v>312</x:v>
-      </x:c>
-      <x:c r="B135" s="21" t="s">
-        <x:v>313</x:v>
       </x:c>
       <x:c r="C135" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D135" s="22" t="s">
-        <x:v>314</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15.75" customHeight="1">
       <x:c r="A136" s="16" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B136" s="17" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="B136" s="17" t="s">
-        <x:v>316</x:v>
       </x:c>
       <x:c r="C136" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D136" s="19" t="s">
-        <x:v>317</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15.75" customHeight="1">
       <x:c r="A137" s="20" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B137" s="21" t="s">
         <x:v>318</x:v>
-      </x:c>
-      <x:c r="B137" s="21" t="s">
-        <x:v>319</x:v>
       </x:c>
       <x:c r="C137" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D137" s="22" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15.75" customHeight="1">
       <x:c r="A138" s="16" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B138" s="17" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="B138" s="17" t="s">
-        <x:v>321</x:v>
       </x:c>
       <x:c r="C138" s="24" t="s">
         <x:v>21</x:v>
@@ -11117,44 +11113,44 @@
     </x:row>
     <x:row r="139" ht="15.75" customHeight="1">
       <x:c r="A139" s="20" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B139" s="21" t="s">
         <x:v>322</x:v>
-      </x:c>
-      <x:c r="B139" s="21" t="s">
-        <x:v>323</x:v>
       </x:c>
       <x:c r="C139" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D139" s="22" t="s">
-        <x:v>324</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15.75" customHeight="1">
       <x:c r="A140" s="16" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B140" s="17" t="s">
         <x:v>325</x:v>
-      </x:c>
-      <x:c r="B140" s="17" t="s">
-        <x:v>326</x:v>
       </x:c>
       <x:c r="C140" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D140" s="19" t="s">
-        <x:v>327</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15.75" customHeight="1">
       <x:c r="A141" s="20" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B141" s="21" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B141" s="21" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C141" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D141" s="22" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="27.75" customHeight="1">
@@ -12468,50 +12464,50 @@
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
       <x:c r="A1" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="s">
+      <x:c r="C1" s="14" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="s">
+      <x:c r="D1" s="14" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="D1" s="14" t="s">
-        <x:v>334</x:v>
       </x:c>
       <x:c r="E1" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F1" s="14" t="s">
-        <x:v>335</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="B2" s="21" t="s">
+      <x:c r="C2" s="21" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="C2" s="21" t="s">
+      <x:c r="D2" s="21" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="D2" s="21" t="s">
-        <x:v>339</x:v>
       </x:c>
       <x:c r="E2" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F2" s="21" t="s">
-        <x:v>340</x:v>
+        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="16" t="s">
-        <x:v>341</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B3" s="17" t="s">
-        <x:v>337</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C3" s="21" t="inlineStr">
         <x:is>
@@ -12519,7 +12515,7 @@
         </x:is>
       </x:c>
       <x:c r="D3" s="17" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E3" s="24" t="s">
         <x:v>21</x:v>
@@ -12532,10 +12528,10 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="20" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B4" s="21" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="B4" s="21" t="s">
-        <x:v>343</x:v>
       </x:c>
       <x:c r="C4" s="21" t="inlineStr">
         <x:is>
@@ -12560,10 +12556,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="16" t="s">
-        <x:v>344</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
-        <x:v>343</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C5" s="17" t="inlineStr">
         <x:is>
@@ -12588,42 +12584,42 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="B6" s="21" t="s">
+      <x:c r="C6" s="21" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="C6" s="21" t="s">
-        <x:v>347</x:v>
-      </x:c>
       <x:c r="D6" s="21" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E6" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="21" t="s">
-        <x:v>340</x:v>
+        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="16" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="C7" s="17" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="D7" s="17" t="s">
         <x:v>350</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
-        <x:v>351</x:v>
       </x:c>
       <x:c r="E7" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="17" t="s">
-        <x:v>340</x:v>
+        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -12631,27 +12627,27 @@
         <x:v>Multiple themes (beyond Sakura Kiss &amp; Midnight City)</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>353</x:v>
-      </x:c>
       <x:c r="D8" s="21" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E8" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="21" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="16" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B9" s="17" t="s">
-        <x:v>337</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C9" s="17" t="inlineStr">
         <x:is>
@@ -12676,162 +12672,150 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="20" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B10" s="21" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="B10" s="21" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="C10" s="21" t="s">
-        <x:v>357</x:v>
-      </x:c>
       <x:c r="D10" s="21" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E10" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="21" t="s">
-        <x:v>358</x:v>
+        <x:v>357</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="16" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>360</x:v>
-      </x:c>
       <x:c r="D11" s="17" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E11" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F11" s="17" t="s">
-        <x:v>361</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="20" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B12" s="21" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="B12" s="21" t="s">
+      <x:c r="C12" s="21" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s">
-        <x:v>364</x:v>
-      </x:c>
       <x:c r="D12" s="21" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E12" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F12" s="21" t="s">
-        <x:v>365</x:v>
+        <x:v>364</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="16" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="s">
+      <x:c r="C13" s="17" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s">
+      <x:c r="D13" s="17" t="s">
         <x:v>368</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
-        <x:v>369</x:v>
       </x:c>
       <x:c r="E13" s="24" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F13" s="17" t="s">
-        <x:v>370</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="20" t="s">
-        <x:v>371</x:v>
-      </x:c>
-      <x:c r="B14" s="21" t="s">
-        <x:v>372</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="str">
-        <x:v>Activity history for members: posts liked, content purchased and payment history.</x:v>
-      </x:c>
-      <x:c r="D14" s="21" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="E14" s="24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F14" s="21" t="s">
-        <x:v>373</x:v>
-      </x:c>
+      <x:c r="A14" s="20"/>
+      <x:c r="B14" s="21"/>
+      <x:c r="C14" s="21"/>
+      <x:c r="D14" s="21"/>
+      <x:c r="E14" s="24"/>
+      <x:c r="F14" s="21"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="45" t="s">
-        <x:v>374</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B15" s="46" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C15" s="47" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="D15" s="46" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E15" s="48" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F15" s="47" t="s">
-        <x:v>377</x:v>
+        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="49" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B16" s="50" t="s">
-        <x:v>379</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C16" s="51" t="s">
-        <x:v>380</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D16" s="50" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E16" s="48" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F16" s="51" t="s">
-        <x:v>381</x:v>
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="52" t="s">
-        <x:v>382</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B17" s="53" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C17" s="54" t="s">
-        <x:v>383</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D17" s="53" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E17" s="48" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F17" s="54" t="s">
-        <x:v>384</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1"/>
@@ -13830,21 +13814,21 @@
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B3" s="14" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="55" t="s">
-        <x:v>388</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B4" s="58" t="str">
         <x:v>This workbook is reconciled with the repository, founder decisions, and merged PR #1–#3 baseline through August 16, 2026.</x:v>
@@ -13852,71 +13836,71 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="57" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B5" s="58" t="s">
-        <x:v>390</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="55" t="s">
-        <x:v>391</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B6" s="56" t="s">
-        <x:v>392</x:v>
+        <x:v>388</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="57" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B7" s="58" t="s">
-        <x:v>394</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="55" t="s">
-        <x:v>395</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B8" s="56" t="s">
-        <x:v>396</x:v>
+        <x:v>392</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="57" t="s">
-        <x:v>397</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B9" s="58" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="55" t="s">
-        <x:v>399</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B10" s="56" t="s">
-        <x:v>400</x:v>
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="57" t="s">
-        <x:v>401</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B11" s="58" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="55" t="s">
-        <x:v>403</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B12" s="56" t="s">
-        <x:v>404</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="57" t="s">
-        <x:v>405</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B13" s="58" t="str">
         <x:v>Phase 6 expanded — added: NSFW toggle, Settings, Help/Support, Activity, modal/drawer/chat fixes, creator dashboard.</x:v>
@@ -13924,7 +13908,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="55" t="s">
-        <x:v>406</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B14" s="56" t="str">
         <x:v>Midnight City is implemented as the second free default theme alongside Sakura Kiss, with browser-local selection.</x:v>
@@ -13932,55 +13916,55 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="57" t="s">
-        <x:v>407</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B15" s="58" t="s">
-        <x:v>408</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="s">
-        <x:v>409</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B18" s="60" t="s">
-        <x:v>411</x:v>
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B19" s="60" t="s">
-        <x:v>412</x:v>
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B20" s="60" t="s">
-        <x:v>413</x:v>
+        <x:v>409</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
       <x:c r="A21" s="59" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B21" s="60" t="s">
         <x:v>410</x:v>
-      </x:c>
-      <x:c r="B21" s="60" t="s">
-        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15.75" customHeight="1">
       <x:c r="A22" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B22" s="60" t="s">
-        <x:v>415</x:v>
+        <x:v>411</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">
@@ -13989,23 +13973,23 @@
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
       <x:c r="A24" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B24" s="60" t="s">
-        <x:v>416</x:v>
+        <x:v>412</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1">
       <x:c r="A25" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B25" s="60" t="s">
-        <x:v>417</x:v>
+        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15.75" customHeight="1">
       <x:c r="A26" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B26" s="60" t="str">
         <x:v>CCBill is the intended primary processor. Sales has replied; merchant/model approval and technical integration remain pending.</x:v>
@@ -14013,7 +13997,7 @@
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
       <x:c r="A27" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B27" s="60" t="str">
         <x:v>Epoch is the intended fallback. Outreach and account-specific cascade confirmation remain pending; no routing is implemented.</x:v>
@@ -14021,31 +14005,31 @@
     </x:row>
     <x:row r="28" ht="15.75" customHeight="1">
       <x:c r="A28" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B28" s="60" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
       <x:c r="A29" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B29" s="60" t="s">
-        <x:v>419</x:v>
+        <x:v>415</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15.75" customHeight="1">
       <x:c r="A30" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B30" s="60" t="s">
-        <x:v>420</x:v>
+        <x:v>416</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A31" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B31" s="60" t="str">
         <x:v>Admin operations: separate apps/admin shell; no public /admin. Public ADMIN sessions are insufficient for operations access. The dormant review router stays unmounted until signed operations identity, exact provisioning, phishing-resistant hardware-backed assurance, private-origin/CSRF, trusted-proxy, restricted DB-role, audit, and recovery gates pass.</x:v>
@@ -14053,7 +14037,7 @@
     </x:row>
     <x:row r="32" ht="15.75" customHeight="1">
       <x:c r="A32" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B32" s="60" t="str">
         <x:v>Midnight City: blue city rooftops, static desktop/mobile JPGs. Browser-local Settings selection implemented; account sync pending.</x:v>
@@ -14061,71 +14045,71 @@
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1">
       <x:c r="A33" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B33" s="60" t="s">
-        <x:v>421</x:v>
+        <x:v>417</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1">
       <x:c r="A34" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B34" s="60" t="s">
-        <x:v>422</x:v>
+        <x:v>418</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15.75" customHeight="1">
       <x:c r="A35" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B35" s="60" t="s">
-        <x:v>423</x:v>
+        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
       <x:c r="A36" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B36" s="60" t="s">
-        <x:v>424</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15.75" customHeight="1">
       <x:c r="A37" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B37" s="60" t="s">
-        <x:v>425</x:v>
+        <x:v>421</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15.75" customHeight="1">
       <x:c r="A38" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B38" s="60" t="s">
-        <x:v>426</x:v>
+        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15.75" customHeight="1">
       <x:c r="A39" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B39" s="60" t="s">
-        <x:v>427</x:v>
+        <x:v>423</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15.75" customHeight="1">
       <x:c r="A40" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B40" s="60" t="s">
-        <x:v>428</x:v>
+        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15.75" customHeight="1">
       <x:c r="A41" s="59" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B41" s="60" t="inlineStr">
         <x:is>
@@ -15664,7 +15648,7 @@
   <x:sheetData>
     <x:row r="1" ht="39.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -15688,22 +15672,22 @@
     </x:row>
     <x:row r="3" ht="25.5" customHeight="1">
       <x:c r="A3" s="68" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B3" s="68" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C3" s="68" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="D3" s="68" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="E3" s="68" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="F3" s="68" t="s">
         <x:v>430</x:v>
-      </x:c>
-      <x:c r="B3" s="68" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="C3" s="68" t="s">
-        <x:v>431</x:v>
-      </x:c>
-      <x:c r="D3" s="68" t="s">
-        <x:v>432</x:v>
-      </x:c>
-      <x:c r="E3" s="68" t="s">
-        <x:v>433</x:v>
-      </x:c>
-      <x:c r="F3" s="68" t="s">
-        <x:v>434</x:v>
       </x:c>
       <x:c r="G3" s="68" t="s">
         <x:v>4</x:v>
@@ -15714,7 +15698,7 @@
     </x:row>
     <x:row r="4" ht="25.5" customHeight="1">
       <x:c r="A4" s="15" t="s">
-        <x:v>435</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -15726,98 +15710,98 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="16" t="s">
-        <x:v>436</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C5" s="17" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D5" s="17">
         <x:v>500.0</x:v>
       </x:c>
       <x:c r="E5" s="17"/>
       <x:c r="F5" s="17" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="G5" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H5" s="17" t="s">
-        <x:v>441</x:v>
+        <x:v>437</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="s">
-        <x:v>442</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C6" s="21" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D6" s="21">
         <x:v>500.0</x:v>
       </x:c>
       <x:c r="E6" s="21"/>
       <x:c r="F6" s="21" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="G6" s="24" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="H6" s="21" t="s">
         <x:v>439</x:v>
-      </x:c>
-      <x:c r="G6" s="24" t="s">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="H6" s="21" t="s">
-        <x:v>443</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="16" t="s">
-        <x:v>444</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B7" s="17" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C7" s="17" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D7" s="17">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E7" s="17"/>
       <x:c r="F7" s="17" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="G7" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H7" s="17" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="20" t="s">
-        <x:v>446</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C8" s="21" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D8" s="21">
         <x:v>350.0</x:v>
       </x:c>
       <x:c r="E8" s="21"/>
       <x:c r="F8" s="21" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="G8" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H8" s="21" t="s">
-        <x:v>448</x:v>
+        <x:v>444</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -15835,10 +15819,10 @@
         <x:v>Kiban Digital Holdings LLC — Northwest formation</x:v>
       </x:c>
       <x:c r="B10" s="208" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C10" s="208" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D10" s="208">
         <x:v>155.0</x:v>
@@ -15847,7 +15831,7 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="F10" s="208" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="G10" s="213" t="str">
         <x:v>Paid / filed</x:v>
@@ -15861,10 +15845,10 @@
         <x:v>Policy documents — Suzanne Lawyer (Fiverr)</x:v>
       </x:c>
       <x:c r="B11" s="208" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C11" s="208" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D11" s="208">
         <x:v>125.0</x:v>
@@ -15873,7 +15857,7 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="F11" s="208" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="G11" s="214" t="str">
         <x:v>Paid / drafting</x:v>
@@ -15884,79 +15868,79 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="16" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B12" s="17" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C12" s="17" t="s">
-        <x:v>450</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="D12" s="17">
         <x:v>125.0</x:v>
       </x:c>
       <x:c r="E12" s="17"/>
       <x:c r="F12" s="17" t="s">
-        <x:v>451</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="G12" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H12" s="17" t="s">
-        <x:v>452</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="20" t="s">
-        <x:v>453</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B13" s="21" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C13" s="21" t="s">
-        <x:v>450</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="D13" s="21">
         <x:v>15.0</x:v>
       </x:c>
       <x:c r="E13" s="21"/>
       <x:c r="F13" s="21" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="G13" s="24" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="H13" s="21" t="s">
         <x:v>451</x:v>
-      </x:c>
-      <x:c r="G13" s="24" t="s">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="H13" s="21" t="s">
-        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="16.5" customHeight="1">
       <x:c r="A14" s="16" t="s">
-        <x:v>456</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B14" s="17" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s">
-        <x:v>450</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="D14" s="17">
         <x:v>30.0</x:v>
       </x:c>
       <x:c r="E14" s="17"/>
       <x:c r="F14" s="17" t="s">
-        <x:v>451</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="G14" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H14" s="17" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="15" t="s">
-        <x:v>458</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B15" s="2"/>
       <x:c r="C15" s="2"/>
@@ -15968,175 +15952,175 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="32" t="s">
-        <x:v>459</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B16" s="33" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C16" s="33" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D16" s="33">
         <x:v>18.0</x:v>
       </x:c>
       <x:c r="E16" s="33"/>
       <x:c r="F16" s="33" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G16" s="39" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H16" s="33" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="20" t="s">
-        <x:v>462</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B17" s="21" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C17" s="21" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D17" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E17" s="21"/>
       <x:c r="F17" s="21" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G17" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H17" s="21" t="s">
-        <x:v>463</x:v>
+        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="16" t="s">
-        <x:v>464</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B18" s="17" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C18" s="17" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D18" s="17">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E18" s="17"/>
       <x:c r="F18" s="17" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G18" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H18" s="17" t="s">
-        <x:v>465</x:v>
+        <x:v>461</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="20" t="s">
-        <x:v>466</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B19" s="21" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C19" s="21" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D19" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E19" s="21"/>
       <x:c r="F19" s="21" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G19" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H19" s="21" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="16" t="s">
-        <x:v>468</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B20" s="17" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D20" s="17">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E20" s="17"/>
       <x:c r="F20" s="17" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G20" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H20" s="17" t="s">
-        <x:v>469</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
       <x:c r="A21" s="20" t="s">
-        <x:v>470</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B21" s="21" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C21" s="21" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D21" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E21" s="21"/>
       <x:c r="F21" s="21" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G21" s="24" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H21" s="21" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="25.5" customHeight="1">
       <x:c r="A22" s="36" t="s">
-        <x:v>472</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B22" s="37" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C22" s="37" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D22" s="37">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E22" s="37"/>
       <x:c r="F22" s="37" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H22" s="37" t="s">
-        <x:v>473</x:v>
+        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">
       <x:c r="A23" s="15" t="s">
-        <x:v>474</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B23" s="2"/>
       <x:c r="C23" s="2"/>
@@ -16148,79 +16132,79 @@
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
       <x:c r="A24" s="32" t="s">
-        <x:v>475</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B24" s="33" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C24" s="33" t="s">
-        <x:v>476</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="D24" s="33">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E24" s="33"/>
       <x:c r="F24" s="33" t="s">
-        <x:v>477</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="G24" s="39" t="s">
-        <x:v>478</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="H24" s="33" t="s">
-        <x:v>479</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1">
       <x:c r="A25" s="20" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B25" s="21" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C25" s="21" t="s">
-        <x:v>476</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="D25" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E25" s="21"/>
       <x:c r="F25" s="21" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="G25" s="24" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="H25" s="21" t="s">
         <x:v>477</x:v>
-      </x:c>
-      <x:c r="G25" s="24" t="s">
-        <x:v>478</x:v>
-      </x:c>
-      <x:c r="H25" s="21" t="s">
-        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="25.5" customHeight="1">
       <x:c r="A26" s="36" t="s">
-        <x:v>482</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B26" s="37" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C26" s="37" t="s">
-        <x:v>476</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="D26" s="37">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E26" s="37"/>
       <x:c r="F26" s="37" t="s">
-        <x:v>483</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>478</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="H26" s="37" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
       <x:c r="A27" s="15" t="s">
-        <x:v>485</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B27" s="2"/>
       <x:c r="C27" s="2"/>
@@ -16232,80 +16216,80 @@
     </x:row>
     <x:row r="28" ht="15.75" customHeight="1">
       <x:c r="A28" s="32" t="s">
-        <x:v>486</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B28" s="33" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C28" s="33" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D28" s="33">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E28" s="33"/>
       <x:c r="F28" s="33" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G28" s="39" t="s">
-        <x:v>487</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="H28" s="33" t="s">
-        <x:v>488</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
       <x:c r="A29" s="20" t="s">
-        <x:v>489</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B29" s="21" t="s">
-        <x:v>490</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C29" s="21" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D29" s="21">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E29" s="21"/>
       <x:c r="F29" s="21" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G29" s="24" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="H29" s="21" t="s">
         <x:v>487</x:v>
-      </x:c>
-      <x:c r="H29" s="21" t="s">
-        <x:v>491</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15.75" customHeight="1">
       <x:c r="A30" s="16" t="s">
-        <x:v>492</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B30" s="17" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C30" s="17" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="D30" s="17">
         <x:v>0.0</x:v>
       </x:c>
       <x:c r="E30" s="17"/>
       <x:c r="F30" s="17" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G30" s="24" t="s">
-        <x:v>487</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="H30" s="17" t="s">
-        <x:v>493</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="25.5" customHeight="1"/>
     <x:row r="32" ht="15.75" customHeight="1">
       <x:c r="A32" s="15" t="s">
-        <x:v>494</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B32" s="2"/>
       <x:c r="C32" s="2"/>
@@ -16317,7 +16301,7 @@
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1">
       <x:c r="A33" s="6" t="s">
-        <x:v>495</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B33" s="69" t="n">
         <x:f>SUM(D5:D11)</x:f>
@@ -16326,7 +16310,7 @@
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1">
       <x:c r="A34" s="7" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B34" s="70" t="n">
         <x:f>SUM(D12:D14)</x:f>
@@ -16335,7 +16319,7 @@
     </x:row>
     <x:row r="35" ht="15.75" customHeight="1">
       <x:c r="A35" s="6" t="s">
-        <x:v>497</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B35" s="69" t="n">
         <x:f>SUM(D16:D22)</x:f>
@@ -16344,7 +16328,7 @@
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
       <x:c r="A36" s="7" t="s">
-        <x:v>498</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B36" s="70" t="n">
         <x:f>B33+B34+B35*12</x:f>
@@ -17375,7 +17359,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
-        <x:v>499</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B1"/>
       <x:c r="C1"/>
@@ -17386,7 +17370,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -17406,12 +17390,12 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>501</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B4"/>
       <x:c r="C4"/>
       <x:c r="D4" t="s">
-        <x:v>502</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="E4"/>
       <x:c r="F4"/>
@@ -17419,7 +17403,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>503</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B5" t="n">
         <x:f>COUNTIF('Master Tracker'!C4:C164,"✅ Done")+COUNTIF('Master Tracker'!C4:C164,"🔄 In Progress")+COUNTIF('Master Tracker'!C4:C164,"📋 Not Started")</x:f>
@@ -17427,11 +17411,11 @@
       </x:c>
       <x:c r="C5"/>
       <x:c r="D5" t="s">
-        <x:v>504</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E5" t="n">
         <x:f>COUNTA(Backlog!A2:A30)</x:f>
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F5"/>
       <x:c r="G5"/>
@@ -17450,7 +17434,7 @@
       </x:c>
       <x:c r="E6" t="n">
         <x:f>COUNTIF(Backlog!E2:E30,"📋 Not Started")</x:f>
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F6"/>
       <x:c r="G6"/>
@@ -17461,7 +17445,7 @@
       </x:c>
       <x:c r="B7" t="n">
         <x:f>COUNTIF('Master Tracker'!C4:C164,"🔄 In Progress")</x:f>
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C7"/>
       <x:c r="D7"/>
@@ -17475,7 +17459,7 @@
       </x:c>
       <x:c r="B8" t="n">
         <x:f>COUNTIF('Master Tracker'!C4:C164,"📋 Not Started")</x:f>
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C8"/>
       <x:c r="D8"/>
@@ -17485,7 +17469,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B9" t="n">
         <x:f>IF(B5=0,0,B6/B5)</x:f>
@@ -17517,11 +17501,11 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="s">
-        <x:v>506</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B12"/>
       <x:c r="C12" t="s">
-        <x:v>507</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D12"/>
       <x:c r="E12"/>
@@ -17547,7 +17531,7 @@
       </x:c>
       <x:c r="B14"/>
       <x:c r="C14" t="s">
-        <x:v>508</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="D14"/>
       <x:c r="E14"/>
@@ -17560,7 +17544,7 @@
       </x:c>
       <x:c r="B15"/>
       <x:c r="C15" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D15"/>
       <x:c r="E15"/>
@@ -17571,7 +17555,7 @@
       <x:c r="A16"/>
       <x:c r="B16"/>
       <x:c r="C16" t="s">
-        <x:v>510</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="D16"/>
       <x:c r="E16"/>
@@ -17582,7 +17566,7 @@
       <x:c r="A17"/>
       <x:c r="B17"/>
       <x:c r="C17" t="s">
-        <x:v>511</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -17593,7 +17577,7 @@
       <x:c r="A18"/>
       <x:c r="B18"/>
       <x:c r="C18" t="s">
-        <x:v>512</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="D18"/>
       <x:c r="E18"/>
@@ -17604,7 +17588,7 @@
       <x:c r="A19"/>
       <x:c r="B19"/>
       <x:c r="C19" t="s">
-        <x:v>513</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="D19"/>
       <x:c r="E19"/>
@@ -18841,15 +18825,15 @@
       </x:c>
       <x:c r="F12" s="111" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$B$4:$B$400,$A12)</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G12" s="119" t="n">
         <x:f>IF(F12=0,0,E12/F12)</x:f>
-        <x:v>0.4444444444444444</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="H12" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A12,'Delivery Tracker'!$H$4:$H$400,"In Progress")</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A12,'Delivery Tracker'!$H$4:$H$400,"In Review")</x:f>
@@ -18864,19 +18848,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L12" s="111" t="str">
-        <x:v>Connect discovery, Store and feed remain launch scope. Connect means online, price and language filters.</x:v>
+        <x:v>Feed, Store and Connect remain launch scope (online/price/language discovery). Your Activity /activity UI is an explicit example-data preview; real member history remains pending.</x:v>
       </x:c>
       <x:c r="M12" s="111" t="str">
-        <x:v>Integrate content and access controls. Define service/order and beta payment rules with the relevant slice.</x:v>
+        <x:v>Integrate content/access, service/order and beta payment rules. Connect Your Activity to authenticated P05/P06/P07 data.</x:v>
       </x:c>
       <x:c r="N12" s="111" t="str">
-        <x:v>Feed actions persist; Store uses real data; creator discovery filters work. Separately define service order/payment rules.</x:v>
+        <x:v>Feed actions persist; Store and Your Activity use real account data; creator discovery filters work. Service/order/payment rules separately defined.</x:v>
       </x:c>
       <x:c r="O12" s="111" t="str">
         <x:v>https://github.com/QK-Connoisseur/PDoki/blob/dev/PLAN.md#12-phase-8--feed-social-actions-store-and-connect</x:v>
       </x:c>
       <x:c r="P12" s="112" t="n">
-        <x:v>46274.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -19240,7 +19224,7 @@
       </x:c>
       <x:c r="F19" s="111" t="n">
         <x:f>COUNTIF('Delivery Tracker'!$B$4:$B$400,$A19)</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="119" t="n">
         <x:f>IF(F19=0,0,E19/F19)</x:f>
@@ -19260,7 +19244,7 @@
       </x:c>
       <x:c r="K19" s="111" t="n">
         <x:f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A19,'Delivery Tracker'!$H$4:$H$400,"Not Started")</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L19" s="111" t="str">
         <x:v>Live streaming, advanced recommendations, native apps, crypto, extra themes, and advanced group chat remain deferred.</x:v>
@@ -19301,7 +19285,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68c94d1baaac45d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1018c19920934ead"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23037,50 +23021,54 @@
         <x:v>LEG-MT-080</x:v>
       </x:c>
       <x:c r="B74" s="111" t="str">
-        <x:v>POST</x:v>
+        <x:v>P08</x:v>
       </x:c>
       <x:c r="C74" s="111" t="str">
-        <x:v>Post-MVP</x:v>
-      </x:c>
-      <x:c r="D74" s="111" t="str"/>
+        <x:v>Feed, social actions, Store, and Connect</x:v>
+      </x:c>
+      <x:c r="D74" s="111" t="str">
+        <x:v>P03, P05, P06, P07</x:v>
+      </x:c>
       <x:c r="E74" s="111" t="str">
         <x:v>Legacy-mapped task</x:v>
       </x:c>
       <x:c r="F74" s="111" t="str">
-        <x:v>Post-MVP</x:v>
+        <x:v>Feed, social actions, Store, and Connect</x:v>
       </x:c>
       <x:c r="G74" s="111" t="str">
         <x:v>Build 'Your Activity' page</x:v>
       </x:c>
       <x:c r="H74" s="111" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I74" s="111" t="str">
-        <x:v>N/A</x:v>
+        <x:v>UI Prototype</x:v>
       </x:c>
       <x:c r="J74" s="111" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="K74" s="111" t="str">
         <x:v>Engineering</x:v>
       </x:c>
       <x:c r="L74" s="111" t="str"/>
       <x:c r="M74" s="111" t="str">
-        <x:v>Confirm dependencies and owner, then define the first deliverable.</x:v>
+        <x:v>Connect authenticated API and persisted member history after P05/P06/P07. Replace example data when real event sources exist.</x:v>
       </x:c>
       <x:c r="N74" s="112"/>
-      <x:c r="O74" s="111" t="str"/>
+      <x:c r="O74" s="111" t="str">
+        <x:v>apps/web/src/pages/ActivityPage.jsx; ActivityPage.test.jsx; tests/e2e/activity.spec.js; PLAN.md §12.</x:v>
+      </x:c>
       <x:c r="P74" s="112" t="n">
-        <x:v>46250.666666666664</x:v>
+        <x:v>46275.666666666664</x:v>
       </x:c>
       <x:c r="Q74" s="111" t="str">
-        <x:v>Member activity history: posts liked, content purchased, subscriptions and payment history. Lower priority.</x:v>
+        <x:v>P08 member history: liked posts, purchases, subscriptions and payment history. UI preview first; account-backed events follow.</x:v>
       </x:c>
       <x:c r="R74" s="111" t="str">
-        <x:v>Nice-to-have post-launch. Defer if time is tight.</x:v>
+        <x:v>Promoted from Post-MVP to P08. /activity preview provides search/category filters and sidebar/header Your Activity links. Example data is explicitly labeled; authenticated account data, API and persistence remain pending. Focused UI tests passed.</x:v>
       </x:c>
       <x:c r="S74" s="111" t="str">
-        <x:v>Preserved Master Tracker row 80; legacy status: 📋 Not Started</x:v>
+        <x:v>Master Tracker row 80; promoted to P08 September 10, 2026. Former duplicate Backlog row 14 cleared.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="46" customHeight="1">
@@ -27734,7 +27722,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38016ecd093840d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48f51c6e063b438b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/product/Pumdoki_MasterTracker_V4.xlsx
+++ b/docs/product/Pumdoki_MasterTracker_V4.xlsx
@@ -7014,8 +7014,8 @@
       <c r="N1" s="94"/>
     </row>
     <row r="2" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A2" s="95" t="s">
-        <v>511</v>
+      <c r="A2" t="str" s="95">
+        <v>Updated September 16, 2026. Founder confirms Maryland approval and EIN receipt. Private R2 flow verified; local content review remains pending. Record counts are not launch readiness.</v>
       </c>
       <c r="B2" s="95"/>
       <c r="C2" s="95"/>
@@ -7183,12 +7183,12 @@
       <c r="B13" s="102"/>
       <c r="C13" s="101">
         <f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"Done")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="102"/>
       <c r="E13" s="101">
         <f>COUNTIF('Delivery Tracker'!$H$4:$H$400,"In Progress")</f>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" s="102"/>
       <c r="G13" s="101">
@@ -7208,7 +7208,7 @@
       <c r="L13" s="102"/>
       <c r="M13" s="105">
         <f>IF(A13=0,0,C13/A13)</f>
-        <v>0.20512820512820512</v>
+        <v>0.21153846153846154</v>
       </c>
       <c r="N13" s="102"/>
     </row>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="E22" s="62">
         <f>'Phase Roadmap'!E8</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" s="62">
         <f>'Phase Roadmap'!F8</f>
@@ -7550,11 +7550,11 @@
       </c>
       <c r="G22" s="65">
         <f>'Phase Roadmap'!G8</f>
-        <v>0.14285714285714285</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="H22" s="62">
         <f>'Phase Roadmap'!H8</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" s="62">
         <f>'Phase Roadmap'!I8</f>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="L22" s="62" t="str">
         <f>'Phase Roadmap'!L8</f>
-        <v>Slices 1–4 published; operations dormant. Maryland approval pending. Initial CCBill reply retained; proposed follow-up cancelled. Founder/provider work now accompanies each functional code slice.</v>
+        <v>Slices 1-4 published; operations dormant. Founder confirms Maryland approval and EIN receipt Sept 16. Legal review and business/provider dependencies remain open.</v>
       </c>
       <c r="M22" s="62" t="str">
         <f>'Phase Roadmap'!M8</f>
@@ -10023,19 +10023,43 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="62"/>
-      <c r="L12" s="62"/>
+    <row r="12" spans="1:12" ht="85" customHeight="1">
+      <c r="A12" t="n" s="63">
+        <v>46281</v>
+      </c>
+      <c r="B12" t="str" s="62">
+        <v>LEG-MT-158</v>
+      </c>
+      <c r="C12" t="str" s="62">
+        <v>P04</v>
+      </c>
+      <c r="D12" t="str" s="62">
+        <v>Record Maryland approval and EIN receipt.</v>
+      </c>
+      <c r="E12" t="str" s="62">
+        <v>Marked LLC formation complete; updated EIN, privacy and dependency records.</v>
+      </c>
+      <c r="F12" t="str" s="62">
+        <v>State formation and EIN are complete, per founder confirmation.</v>
+      </c>
+      <c r="G12" t="str" s="62">
+        <v>Banking, DBA and processor approval remain open. Product readiness unchanged.</v>
+      </c>
+      <c r="H12" t="str" s="62">
+        <v>Founder confirmed approval and supplied EIN in chat September 16, 2026.</v>
+      </c>
+      <c r="I12" t="str" s="62">
+        <v>Done</v>
+      </c>
+      <c r="J12" t="str" s="62">
+        <v>Original approval and IRS letter not independently inspected.</v>
+      </c>
+      <c r="K12" t="str" s="62">
+        <v>Resume the current legal questionnaire in PLAN.md section 20.</v>
+      </c>
+      <c r="L12" t="str" s="62">
+        <v>Codex</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="57.95" customHeight="1">
       <c r="A13" s="62"/>
@@ -11016,27 +11040,27 @@
       <c r="B9" s="62" t="s">
         <v>829</v>
       </c>
-      <c r="C9" s="62" t="s">
-        <v>1577</v>
+      <c r="C9" t="str" s="62">
+        <v>Maryland LLC approved; EIN obtained</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>808</v>
       </c>
       <c r="E9" s="63"/>
-      <c r="F9" s="62" t="s">
-        <v>529</v>
-      </c>
-      <c r="G9" s="62" t="s">
-        <v>1578</v>
-      </c>
-      <c r="H9" s="62" t="s">
-        <v>1579</v>
-      </c>
-      <c r="I9" s="62" t="s">
-        <v>1580</v>
-      </c>
-      <c r="J9" s="63">
-        <v>46275.666666666664</v>
+      <c r="F9" t="str" s="62">
+        <v>Done</v>
+      </c>
+      <c r="G9" t="str" s="62">
+        <v>Founder confirmed Maryland approval and EIN receipt Sept 16. Northwest formation cost: $196. Banking and DBA remain open.</v>
+      </c>
+      <c r="H9" t="str" s="62">
+        <v>Retain state approval and IRS confirmation privately. Resume the existing legal questionnaire; handle banking and DBA separately.</v>
+      </c>
+      <c r="I9" t="str" s="62">
+        <v>Founder confirmation, September 16, 2026. EIN supplied in chat; originals not independently inspected. $196 cost previously confirmed September 10.</v>
+      </c>
+      <c r="J9" t="n" s="63">
+        <v>46281</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="54.95" customHeight="1">
@@ -11088,15 +11112,17 @@
       <c r="F11" s="62" t="s">
         <v>531</v>
       </c>
-      <c r="G11" s="62" t="s">
-        <v>1587</v>
-      </c>
-      <c r="H11" s="62" t="s">
-        <v>1588</v>
-      </c>
-      <c r="I11" s="62"/>
-      <c r="J11" s="63">
-        <v>46255.666666666664</v>
+      <c r="G11" s="62" t="str">
+        <v>Automated member age assurance and creator identity checks planned. Ondato/Veriff candidates; selection, total costs, country coverage and privacy/retention terms remain unresolved.</v>
+      </c>
+      <c r="H11" s="62" t="str">
+        <v>Compare candidates against pilot needs and CCBill review requirements. Configure/test required flows before live adult access or real creator identity onboarding.</v>
+      </c>
+      <c r="I11" s="62" t="str">
+        <v>Founder approval Sept 13; PLAN.md §3.5/§20, Question 12.</v>
+      </c>
+      <c r="J11" s="63" t="n">
+        <v>46278</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="54.95" customHeight="1">
@@ -11148,17 +11174,17 @@
       <c r="F13" s="62" t="s">
         <v>531</v>
       </c>
-      <c r="G13" s="62" t="s">
-        <v>1595</v>
-      </c>
-      <c r="H13" s="62" t="s">
-        <v>1596</v>
-      </c>
-      <c r="I13" s="62" t="s">
-        <v>1597</v>
-      </c>
-      <c r="J13" s="63">
-        <v>46255.666666666664</v>
+      <c r="G13" s="62" t="str">
+        <v>Maryland operator; broad international creators and limited international member pilot approved. Automated checks/cash buffer planned; countries, limits, budgets and coverage unresolved.</v>
+      </c>
+      <c r="H13" s="62" t="str">
+        <v>Set pilot member cap, verification budget and cash buffer before live use; verify actual country coverage. Resolve creator tax documentation under LEG-MT-021.</v>
+      </c>
+      <c r="I13" s="62" t="str">
+        <v>PLAN.md §3.6/§20, Q9–10 (Sept 13 approval); docs/product/initial-business-definition.md (Sept 6 review).</v>
+      </c>
+      <c r="J13" s="63" t="n">
+        <v>46278</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="54.95" customHeight="1">
@@ -11180,17 +11206,17 @@
       <c r="F14" s="62" t="s">
         <v>531</v>
       </c>
-      <c r="G14" s="62" t="s">
-        <v>1600</v>
-      </c>
-      <c r="H14" s="62" t="s">
-        <v>1601</v>
-      </c>
-      <c r="I14" s="62" t="s">
-        <v>1597</v>
-      </c>
-      <c r="J14" s="63">
-        <v>46274.666666666664</v>
+      <c r="G14" s="62" t="str">
+        <v>Q131 approves a 20/80 target excluding sales tax; processing costs from platform share. Q132 applies standard fees to Founders, replacing cost-recovery terms.</v>
+      </c>
+      <c r="H14" s="62" t="str">
+        <v>Validate actual costs before firm pricing/live payments. Refund/chargeback allocation and payout fees pending. Budget prize events separately.</v>
+      </c>
+      <c r="I14" s="62" t="str">
+        <v>PLAN.md §3.8 and §20, Q131–132 approved September 22, 2026.</v>
+      </c>
+      <c r="J14" s="63" t="n">
+        <v>46287</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="54.95" customHeight="1">
@@ -11444,8 +11470,8 @@
       <c r="B23" s="69" t="s">
         <v>838</v>
       </c>
-      <c r="C23" s="69" t="s">
-        <v>1637</v>
+      <c r="C23" s="69" t="str">
+        <v>Founders acquisition and benefits</v>
       </c>
       <c r="D23" s="69" t="s">
         <v>808</v>
@@ -11454,17 +11480,17 @@
       <c r="F23" s="69" t="s">
         <v>529</v>
       </c>
-      <c r="G23" s="69" t="s">
-        <v>1638</v>
-      </c>
-      <c r="H23" s="69" t="s">
-        <v>1639</v>
-      </c>
-      <c r="I23" s="69" t="s">
-        <v>1597</v>
-      </c>
-      <c r="J23" s="70">
-        <v>46271.666666666664</v>
+      <c r="G23" s="69" t="str">
+        <v>Q132: Founders tag; Connect filter or Explore section below top sections; SFW Discord events; future event priority. Standard fees replace commission exemption.</v>
+      </c>
+      <c r="H23" s="69" t="str">
+        <v>Q133: define eligibility, cutoff/cap and duration. Specify placements and event terms; cash prizes optional, separately funded. No sales/ranking guarantee.</v>
+      </c>
+      <c r="I23" s="69" t="str">
+        <v>PLAN.md §20, Q132 approved September 22, 2026; Q133 pending.</v>
+      </c>
+      <c r="J23" s="70" t="n">
+        <v>46287</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="95.1" customHeight="1">
@@ -11916,8 +11942,8 @@
       <c r="C22" s="76">
         <v>300</v>
       </c>
-      <c r="D22" s="71" t="s">
-        <v>1696</v>
+      <c r="D22" t="str" s="71">
+        <v>Specific tax/accounting advice only when needed. Maryland approval and EIN receipt confirmed Sept 16. Unquoted allowance unchanged.</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="48" customHeight="1">
@@ -11946,8 +11972,8 @@
       <c r="C24" s="76">
         <v>900</v>
       </c>
-      <c r="D24" s="71" t="s">
-        <v>1700</v>
+      <c r="D24" t="str" s="71">
+        <v>Northwest formation: $196 confirmed paid. State approval and EIN receipt confirmed Sept 16. Actual recorded in Expense Tracker; planning allowance unchanged.</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="48" customHeight="1">
@@ -12667,8 +12693,8 @@
       <c r="C11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>27</v>
+      <c r="D11" s="8" t="str">
+        <v>Q34: 60 days; Q35: Maryland venue with mandatory-rights exceptions. Q33 advice, legal copy and live workflows pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -12681,8 +12707,8 @@
       <c r="C12" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>30</v>
+      <c r="D12" s="11" t="str">
+        <v>Q50: international privacy provisions where applicable. Q51 vendor terms pending. Controls/final review pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -12695,8 +12721,8 @@
       <c r="C13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>33</v>
+      <c r="D13" s="8" t="str">
+        <v>Q75 approved: serious-violation removal aligned with Q62-64. Final policy/controls pending. Active review: LEG-MT-015. PLAN.md §20.</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -12709,8 +12735,8 @@
       <c r="C14" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>36</v>
+      <c r="D14" s="11" t="str">
+        <v>Q64 reporting/preservation approved. AUP review pending; controls unimplemented. Community review: LEG-MT-013. PLAN.md §20.</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30">
@@ -12723,8 +12749,8 @@
       <c r="C15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>39</v>
+      <c r="D15" s="8" t="str">
+        <v>Q85 approved: creator notices/warnings, no guaranteed warning count. DMCA draft review done; final policy/controls pending. Active: LEG-MT-028. PLAN.md §20.</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30">
@@ -12737,8 +12763,8 @@
       <c r="C16" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>42</v>
+      <c r="D16" s="11" t="str">
+        <v>Q55: statutory records segregated from consent releases where §2257 applies. Custodian, forms and workflow pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30">
@@ -12793,8 +12819,8 @@
       <c r="C20" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>581</v>
+      <c r="D20" s="11" t="str">
+        <v>Q17 approved: CCBill intake received; no detailed checklist/approval. Use current Mastercard rules; align later. PLAN.md §20.</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1">
@@ -12804,11 +12830,11 @@
       <c r="B21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>56</v>
+      <c r="C21" s="91" t="str">
+        <v>🔄 In Progress</v>
+      </c>
+      <c r="D21" s="8" t="str">
+        <v>Q132 approved: Founders benefits replace fee exemption. Review Q133 duration and eligibility. PLAN.md §20.</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
@@ -12891,8 +12917,8 @@
       <c r="C27" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>584</v>
+      <c r="D27" s="8" t="str">
+        <v>Q107 approved; questionnaire reviewed. Draft/controls pending. Active: LEG-MT-032. PLAN.md §20.</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1">
@@ -12902,11 +12928,11 @@
       <c r="B28" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>74</v>
+      <c r="C28" s="13" t="str">
+        <v>🔄 In Progress</v>
+      </c>
+      <c r="D28" s="11" t="str">
+        <v>Q96 approved; NCII questionnaire reviewed. Final policy, neutral review and controls pending. Active: LEG-MT-027. PLAN.md §20.</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1">
@@ -12933,8 +12959,8 @@
       <c r="C30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>80</v>
+      <c r="D30" s="11" t="str">
+        <v>Q64 reporting direction approved; request-policy draft, NCMEC setup and evidence controls pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1">
@@ -12944,11 +12970,13 @@
       <c r="B31" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>83</v>
+      <c r="C31" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔄 In Progress</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="str">
+        <v>Q122 approved; appeals questions reviewed. Final policy/controls pending. Active: LEG-MT-021. PLAN.md §20.</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1">
@@ -12958,11 +12986,13 @@
       <c r="B32" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>86</v>
+      <c r="C32" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔄 In Progress</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="str">
+        <v>Q114 approved; complaint questions reviewed. Final policy/controls pending. Active: LEG-MT-031. PLAN.md §20.</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1">
@@ -13100,17 +13130,17 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A43" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>112</v>
+      <c r="A43" s="9" t="str">
+        <v>Define Founders recognition and benefits</v>
+      </c>
+      <c r="B43" s="10" t="str">
+        <v>Define Founders tag, Connect/Explore discovery and SFW events. Set eligibility, duration and prize terms.</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="11" t="s">
-        <v>113</v>
+      <c r="D43" s="11" t="str">
+        <v>Q132 approved Sept 22. Standard fees; no 500-person cap, member discount or permanent fee exemption. Q133 pending.</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="27.75" customHeight="1">
@@ -13329,14 +13359,14 @@
       <c r="A60" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>146</v>
+      <c r="B60" s="6" t="str">
+        <v>Age eligibility and required verification before adult-content access; separate from content opt-in.</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D60" s="8" t="s">
-        <v>602</v>
+      <c r="D60" s="8" t="str">
+        <v>Q20: 18+ or higher legal minimum; location-based checks before adult access. Attestation exists; verification pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="24" customHeight="1">
@@ -13785,8 +13815,8 @@
       <c r="C94" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="D94" s="11" t="s">
-        <v>619</v>
+      <c r="D94" s="11" t="str">
+        <v>Sales/site prep underway. Wallets deferred to future; direct pay stays. Processor approval and integration pending. PLAN.md §10.</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1">
@@ -13827,8 +13857,8 @@
       <c r="C97" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D97" s="11" t="s">
-        <v>622</v>
+      <c r="D97" s="11" t="str">
+        <v>Q23: self-service cancellation; paid-term access, refund exceptions and confirmation. Cutoff/setup pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1">
@@ -13855,8 +13885,8 @@
       <c r="C99" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D99" s="11" t="s">
-        <v>233</v>
+      <c r="D99" s="11" t="str">
+        <v>Q25: no unpaid pilot grace; retain paid access, pause at expiry until payment succeeds. Retry rules/setup pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1">
@@ -13883,14 +13913,14 @@
       <c r="A102" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B102" s="6" t="s">
-        <v>238</v>
+      <c r="B102" s="6" t="str">
+        <v>Standard platform/creator split and calculation base. Founders use the same commission model.</v>
       </c>
       <c r="C102" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D102" s="11" t="s">
-        <v>623</v>
+      <c r="D102" s="11" t="str">
+        <v>Q131: 20/80 target; processing from platform share. Validate costs. Q132: standard fees for Founders.</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1">
@@ -13903,8 +13933,8 @@
       <c r="C103" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D103" s="11" t="s">
-        <v>624</v>
+      <c r="D103" s="11" t="str">
+        <v>Q28 approved: proportionate dispute handling; protect good-faith disputes. Review/build/tests pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="27.75" customHeight="1">
@@ -14048,25 +14078,25 @@
       <c r="D114" s="8"/>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A115" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="B115" s="10" t="s">
-        <v>263</v>
+      <c r="A115" s="9" t="str">
+        <v>Build Founders admin management</v>
+      </c>
+      <c r="B115" s="10" t="str">
+        <v>Manage Founders eligibility and badge assignment. Enforce a cohort limit only if approved.</v>
       </c>
       <c r="C115" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D115" s="11" t="s">
-        <v>264</v>
+      <c r="D115" s="11" t="str">
+        <v>Programme direction approved Q132; eligibility, cap and duration pending Q133. No implementation yet.</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1">
       <c r="A116" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B116" s="6" t="s">
-        <v>266</v>
+      <c r="B116" s="6" t="str">
+        <v>Configure standard commission, content and feature flags, payout minimums and maintenance. No separate Founders rate.</v>
       </c>
       <c r="C116" s="13" t="s">
         <v>21</v>
@@ -14149,8 +14179,8 @@
       <c r="C122" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D122" s="8" t="s">
-        <v>281</v>
+      <c r="D122" s="8" t="str">
+        <v>Q16 daily urgent checks, including weekends; delegate when unavailable. Backup setup and workflow tests pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1">
@@ -14375,8 +14405,8 @@
       <c r="C139" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D139" s="11" t="s">
-        <v>323</v>
+      <c r="D139" s="11" t="str">
+        <v>Q18: no fixed date; CCBill timing unconfirmed. Limited pilot after approval and readiness checks. Checklist pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1">
@@ -14445,14 +14475,14 @@
       <c r="A146" s="9" t="s">
         <v>640</v>
       </c>
-      <c r="B146" s="10" t="s">
-        <v>641</v>
+      <c r="B146" s="10" t="str">
+        <v>Unlock individual creator content through approved hosted checkout, with ongoing access to the purchased version.</v>
       </c>
       <c r="C146" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D146" s="11" t="s">
-        <v>639</v>
+      <c r="D146" s="11" t="str">
+        <v>Q26: creator delisting preserves buyer access; legal/safety removals still apply. Paid flow pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="31.5" customHeight="1">
@@ -14549,8 +14579,8 @@
       <c r="C153" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D153" s="8" t="s">
-        <v>661</v>
+      <c r="D153" s="8" t="str">
+        <v>Q49: international pilot, separate role eligibility and active restrictions. Countries, budgets and implementation pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15" customHeight="1">
@@ -14571,14 +14601,14 @@
       <c r="A155" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="B155" s="6" t="s">
-        <v>666</v>
+      <c r="B155" s="6" t="str">
+        <v>Compare automated member age assurance and creator identity/age verification providers; preserve replaceable integration.</v>
       </c>
       <c r="C155" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D155" s="8" t="s">
-        <v>667</v>
+      <c r="D155" s="8" t="str">
+        <v>Sept 13: Ondato/Veriff candidates; provider, pricing and coverage unresolved. Coordinate CCBill review; no purchase approved. PLAN.md §20.</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15" customHeight="1">
@@ -14605,8 +14635,8 @@
       <c r="C157" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D157" s="8" t="s">
-        <v>673</v>
+      <c r="D157" s="8" t="str">
+        <v>Sept 13 Q15 approved: Workspace Business aliases created; setup/tests pending. SES/Resend unselected. SMTP/Mailpit foundation only; production delivery pending. PLAN.md §20.</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15" customHeight="1">
@@ -14627,14 +14657,14 @@
       <c r="A159" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="B159" s="6" t="s">
-        <v>678</v>
+      <c r="B159" s="6" t="str">
+        <v>Validate processing, refunds, chargebacks, taxes, standard commission, payouts and programme costs. No Founders discount.</v>
       </c>
       <c r="C159" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D159" s="8" t="s">
-        <v>679</v>
+      <c r="D159" s="8" t="str">
+        <v>Q131: 20/80 target, actual economics pending. Q132: standard fees for Founders; cash-prize events need separate budgets.</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="36" customHeight="1">
@@ -21433,7 +21463,7 @@
       </c>
       <c r="E8" s="62">
         <f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"Done")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="62">
         <f>COUNTIF('Delivery Tracker'!$B$4:$B$400,$A8)</f>
@@ -21441,11 +21471,11 @@
       </c>
       <c r="G8" s="65">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="H8" s="62">
         <f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"In Progress")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" s="62">
         <f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"In Review")</f>
@@ -21459,8 +21489,8 @@
         <f>COUNTIFS('Delivery Tracker'!$B$4:$B$400,$A8,'Delivery Tracker'!$H$4:$H$400,"Not Started")</f>
         <v>12</v>
       </c>
-      <c r="L8" s="62" t="s">
-        <v>901</v>
+      <c r="L8" t="str" s="62">
+        <v>Slices 1-4 published; operations dormant. Founder confirms Maryland approval and EIN receipt Sept 16. Legal review and business/provider dependencies remain open.</v>
       </c>
       <c r="M8" s="62" t="s">
         <v>902</v>
@@ -21471,8 +21501,8 @@
       <c r="O8" s="62" t="s">
         <v>904</v>
       </c>
-      <c r="P8" s="63">
-        <v>46271.666666666664</v>
+      <c r="P8" t="n" s="63">
+        <v>46281</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="57.95" customHeight="1">
@@ -23485,19 +23515,21 @@
         <v>814</v>
       </c>
       <c r="L27" s="62"/>
-      <c r="M27" s="62" t="s">
-        <v>970</v>
+      <c r="M27" s="62" t="str">
+        <v>Select SES/Resend for the hosted account flow after checking adult-business fit, cost and data handling; configure/test production delivery. PLAN.md §20.</v>
       </c>
       <c r="N27" s="63"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="63">
-        <v>46250.666666666664</v>
+      <c r="O27" s="62" t="str">
+        <v>Founder approval in chat, Sept 13; PLAN.md §20, Question 15.</v>
+      </c>
+      <c r="P27" s="63" t="n">
+        <v>46278</v>
       </c>
       <c r="Q27" s="62" t="s">
         <v>672</v>
       </c>
-      <c r="R27" s="62" t="s">
-        <v>673</v>
+      <c r="R27" s="62" t="str">
+        <v>Q15 approved. Workspace Business aliases created; setup/tests pending. SES/Resend unselected. SMTP/console and Mailpit implemented; production TLS, SPF/DKIM/DMARC, deliverability and bounce handling pending.</v>
       </c>
       <c r="S27" s="62" t="s">
         <v>1355</v>
@@ -24286,19 +24318,21 @@
         <v>808</v>
       </c>
       <c r="L42" s="62"/>
-      <c r="M42" s="62" t="s">
-        <v>974</v>
+      <c r="M42" s="62" t="str">
+        <v>Review approved answers in PLAN.md §20, including Q34's 60 days and Q35 venue exceptions. Obtain Q33 arbitration advice; finalize legal copy and live workflows. Plus deferred.</v>
       </c>
       <c r="N42" s="63"/>
-      <c r="O42" s="62"/>
-      <c r="P42" s="63">
-        <v>46250.666666666664</v>
+      <c r="O42" s="62" t="str">
+        <v>Founder approvals Sept 13–16; PLAN.md §20 Q21/Q27/Q30/Q32/Q33/Q34/Q35 and Plus note; apps/web/src/pages/RefundHelpPage.jsx (draft UI).</v>
+      </c>
+      <c r="P42" s="63" t="n">
+        <v>46281</v>
       </c>
       <c r="Q42" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="R42" s="62" t="s">
-        <v>975</v>
+      <c r="R42" s="62" t="str">
+        <v>Suzanne's $1,100 bundle awaits review. Q34: 60 days; Q35: Maryland with rights exceptions. Q33 provider undecided. Plus deferred; refund UI draft. AUP/final notices and live workflows remain pending.</v>
       </c>
       <c r="S42" s="62" t="s">
         <v>976</v>
@@ -24337,19 +24371,21 @@
         <v>808</v>
       </c>
       <c r="L43" s="62"/>
-      <c r="M43" s="62" t="s">
-        <v>978</v>
+      <c r="M43" s="62" t="str">
+        <v>Apply Q50 to actual launch processing. Confirm Q51 vendor retention terms and implement Q46-48 controls after final review. Test mailbox routing and the restricted request log. PLAN.md §20.</v>
       </c>
       <c r="N43" s="63"/>
-      <c r="O43" s="62"/>
-      <c r="P43" s="63">
-        <v>46250.666666666664</v>
+      <c r="O43" s="62" t="str">
+        <v>Founder approval Sept 16, PLAN.md §20 Q50. EDPB territorial-scope and ICO transfer guidance linked there. Q51 pending retained.</v>
+      </c>
+      <c r="P43" s="63" t="n">
+        <v>46286</v>
       </c>
       <c r="Q43" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="R43" s="62" t="s">
-        <v>30</v>
+      <c r="R43" s="62" t="str">
+        <v>Q50: draft for international creators/members. EU/UK provisions apply to covered processing, not nationality alone. Required controls precede processing. Vendor terms, implementation and review pending.</v>
       </c>
       <c r="S43" s="62" t="s">
         <v>979</v>
@@ -24378,8 +24414,8 @@
       <c r="H44" s="62" t="s">
         <v>529</v>
       </c>
-      <c r="I44" s="62" t="s">
-        <v>807</v>
+      <c r="I44" s="62" t="str">
+        <v>N/A</v>
       </c>
       <c r="J44" s="62" t="s">
         <v>368</v>
@@ -24388,19 +24424,21 @@
         <v>808</v>
       </c>
       <c r="L44" s="62"/>
-      <c r="M44" s="62" t="s">
-        <v>981</v>
+      <c r="M44" s="62" t="str">
+        <v>Finalize Community Rules from Q65-75 and implement enforcement before launch. Active founder review is under LEG-MT-015; no parallel founder task. PLAN.md §20.</v>
       </c>
       <c r="N44" s="63"/>
-      <c r="O44" s="62"/>
-      <c r="P44" s="63">
-        <v>46250.666666666664</v>
+      <c r="O44" s="62" t="str">
+        <v>Founder approval Sept 21, PLAN.md §20 Q75; Q74 retained as launch scope. Immediate-removal rules align with Q62-64, including review, preservation, notice and appeals.</v>
+      </c>
+      <c r="P44" s="63" t="n">
+        <v>46286</v>
       </c>
       <c r="Q44" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="R44" s="62" t="s">
-        <v>33</v>
+      <c r="R44" s="62" t="str">
+        <v>Q75: substantiated serious violations may mean immediate termination; urgent removal/suspension pending review. Reports alone do not justify permanent bans. Final policy and controls pending.</v>
       </c>
       <c r="S44" s="62" t="s">
         <v>982</v>
@@ -24441,19 +24479,21 @@
       <c r="L45" s="62" t="s">
         <v>984</v>
       </c>
-      <c r="M45" s="62" t="s">
-        <v>985</v>
+      <c r="M45" s="62" t="str">
+        <v>Finalize AUP from Q53-64 decisions and review processor requirements; implement reporting, evidence preservation, moderation, notices and appeals before live use. Community review: LEG-MT-013.</v>
       </c>
       <c r="N45" s="63"/>
-      <c r="O45" s="62"/>
-      <c r="P45" s="63">
-        <v>46250.666666666664</v>
+      <c r="O45" s="62" t="str">
+        <v>Founder approval Sept 21, PLAN.md §20 Q64; 18 USC 2258A/2702 and NCMEC REPORT Act guidance. Prior content/enforcement decisions retained.</v>
+      </c>
+      <c r="P45" s="63" t="n">
+        <v>46286</v>
       </c>
       <c r="Q45" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="R45" s="62" t="s">
-        <v>36</v>
+      <c r="R45" s="62" t="str">
+        <v>Q64: report apparent CSAM, child trafficking/enticement; emergency escalation and lawful disclosures. Secure evidence; covered CyberTipline material: one year from report. Setup/controls pending.</v>
       </c>
       <c r="S45" s="62" t="s">
         <v>986</v>
@@ -24482,8 +24522,8 @@
       <c r="H46" s="62" t="s">
         <v>529</v>
       </c>
-      <c r="I46" s="62" t="s">
-        <v>807</v>
+      <c r="I46" s="62" t="str">
+        <v>N/A</v>
       </c>
       <c r="J46" s="62" t="s">
         <v>368</v>
@@ -24492,19 +24532,21 @@
         <v>808</v>
       </c>
       <c r="L46" s="62"/>
-      <c r="M46" s="62" t="s">
-        <v>988</v>
+      <c r="M46" s="62" t="str">
+        <v>Finalize DMCA policy and case controls; complete contact setup, Q77 mail confirmation and registration before launch. Active founder review: LEG-MT-028. PLAN.md §20.</v>
       </c>
       <c r="N46" s="63"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="63">
-        <v>46250.666666666664</v>
+      <c r="O46" s="62" t="str">
+        <v>Founder approval Sept 21, PLAN.md §20 Q84-85: case-based enforcement, prompt notices and normal warnings; no fixed strike/warning allowance. Final policy and controls pending.</v>
+      </c>
+      <c r="P46" s="63" t="n">
+        <v>46286</v>
       </c>
       <c r="Q46" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="R46" s="62" t="s">
-        <v>39</v>
+      <c r="R46" s="62" t="str">
+        <v>Founder: "Copyright Agent"; LLC provider; Pumdoki/pumdoki.com alternate names; dmca@pumdoki.com planned. Northwest phone selected; number/setup/testing and mail receipt unverified. Registration pending.</v>
       </c>
       <c r="S46" s="62" t="s">
         <v>989</v>
@@ -24543,19 +24585,21 @@
         <v>814</v>
       </c>
       <c r="L47" s="62"/>
-      <c r="M47" s="62" t="s">
-        <v>991</v>
+      <c r="M47" s="62" t="str">
+        <v>Confirm applicable duties and qualified custodian. Define segregated statutory records, separate consent storage, access and retention under Q38/Q46/Q55. Implement and review before live use.</v>
       </c>
       <c r="N47" s="63"/>
-      <c r="O47" s="62"/>
-      <c r="P47" s="63">
-        <v>46250.666666666664</v>
+      <c r="O47" s="62" t="str">
+        <v>Founder approval Sept 21, PLAN.md §20 Q55; Q38/Q46 retained. 28 CFR §75.2 and Mastercard §9.4.1.</v>
+      </c>
+      <c r="P47" s="63" t="n">
+        <v>46286</v>
       </c>
       <c r="Q47" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="R47" s="62" t="s">
-        <v>42</v>
+      <c r="R47" s="62" t="str">
+        <v>Where §2257 applies, use a qualified custodian and segregate statutory records from consent files. One contracted provider may manage both. Producer duties remain; status/forms/provider not confirmed.</v>
       </c>
       <c r="S47" s="62" t="s">
         <v>992</v>
@@ -24753,21 +24797,21 @@
       <c r="L51" s="62" t="s">
         <v>997</v>
       </c>
-      <c r="M51" s="62" t="s">
-        <v>1004</v>
+      <c r="M51" s="62" t="str">
+        <v>Continue functioning-site/policy preparation. Apply current Mastercard adult rules and law; reconcile written CCBill/acquirer requirements before finalization.</v>
       </c>
       <c r="N51" s="63"/>
-      <c r="O51" s="62" t="s">
-        <v>1005</v>
-      </c>
-      <c r="P51" s="63">
-        <v>46275.666666666664</v>
+      <c r="O51" s="62" t="str">
+        <v>PLAN.md §20 Q17; docs/product/initial-ccbill-inquiry.md; Mastercard §9.4.1 (2026-08-04).</v>
+      </c>
+      <c r="P51" s="63" t="n">
+        <v>46278</v>
       </c>
       <c r="Q51" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="R51" s="62" t="s">
-        <v>1006</v>
+      <c r="R51" s="62" t="str">
+        <v>Q17 approved. CCBill intake only; password-protected functioning site allowed. No detailed checklist/approval. Safe-content/R2 verified; policy drafting commissioned. Model, fees/reserves and payouts unresolved.</v>
       </c>
       <c r="S51" s="62" t="s">
         <v>1007</v>
@@ -24795,8 +24839,8 @@
       <c r="G52" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="H52" s="62" t="s">
-        <v>532</v>
+      <c r="H52" s="62" t="str">
+        <v>In Progress</v>
       </c>
       <c r="I52" s="62" t="s">
         <v>836</v>
@@ -24807,22 +24851,24 @@
       <c r="K52" s="62" t="s">
         <v>808</v>
       </c>
-      <c r="L52" s="62" t="s">
-        <v>1010</v>
-      </c>
-      <c r="M52" s="62" t="s">
-        <v>970</v>
+      <c r="L52" s="62" t="str">
+        <v>Founder questionnaire review; commissioned draft pending</v>
+      </c>
+      <c r="M52" s="62" t="str">
+        <v>Review Q133 Founders duration and eligibility. Q132 benefits approved; exact placements and event/prize terms pending. PLAN.md §20.</v>
       </c>
       <c r="N52" s="63"/>
-      <c r="O52" s="62"/>
-      <c r="P52" s="63">
-        <v>46250.666666666664</v>
+      <c r="O52" s="62" t="str">
+        <v>Q132 approved Sept 22; Q133 pending. PLAN.md §20. Suzanne Lawyer bundle, Expense Tracker row 11; commissioned terms pending.</v>
+      </c>
+      <c r="P52" s="63" t="n">
+        <v>46287</v>
       </c>
       <c r="Q52" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="R52" s="62" t="s">
-        <v>56</v>
+      <c r="R52" s="62" t="str">
+        <v>Q22: approval before creator publishing/monetization; applicable performer records before publication. Tax/payout documents before withdrawal or earlier if required. Forms/timing and implementation pending.</v>
       </c>
       <c r="S52" s="62" t="s">
         <v>1011</v>
@@ -25015,22 +25061,24 @@
       <c r="K56" s="62" t="s">
         <v>808</v>
       </c>
-      <c r="L56" s="62" t="s">
-        <v>1021</v>
-      </c>
-      <c r="M56" s="62" t="s">
-        <v>1022</v>
+      <c r="L56" t="str" s="62">
+        <v>Public-record check</v>
+      </c>
+      <c r="M56" t="str" s="62">
+        <v>Check the public Maryland record against the approved filing. Keep tax and internal ownership records private.</v>
       </c>
       <c r="N56" s="63"/>
-      <c r="O56" s="62"/>
-      <c r="P56" s="63">
-        <v>46273.666666666664</v>
+      <c r="O56" t="str" s="62">
+        <v>Founder reviewed initial filing, resolution and operating agreement and confirmed the name appears only in internal documents. Chat, September 16, 2026.</v>
+      </c>
+      <c r="P56" t="n" s="63">
+        <v>46281</v>
       </c>
       <c r="Q56" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="R56" s="62" t="s">
-        <v>1023</v>
+      <c r="R56" t="str" s="62">
+        <v>Founder confirms state approval. Northwest address shown in dashboard; personal name absent from initial filing, present in internal resolution/agreement. Public SDAT record not independently checked.</v>
       </c>
       <c r="S56" s="62" t="s">
         <v>1024</v>
@@ -25068,18 +25116,18 @@
       <c r="K57" s="62" t="s">
         <v>808</v>
       </c>
-      <c r="L57" s="62" t="s">
-        <v>997</v>
-      </c>
-      <c r="M57" s="62" t="s">
-        <v>1028</v>
+      <c r="L57" s="62" t="str">
+        <v>Commissioned draft and substantive review pending</v>
+      </c>
+      <c r="M57" s="62" t="str">
+        <v>Review commissioned policy; assess specialist participation and processor requirements; implement/test controls. Active founder review: LEG-MT-032. PLAN.md §20.</v>
       </c>
       <c r="N57" s="63"/>
-      <c r="O57" s="62" t="s">
-        <v>1029</v>
-      </c>
-      <c r="P57" s="63">
-        <v>46275.666666666664</v>
+      <c r="O57" s="62" t="str">
+        <v>Q107 approved Sept 22; questionnaire reviewed. PLAN.md §20. Suzanne Lawyer $1,100 bundle recorded in Expense Tracker row 11; draft and controls pending.</v>
+      </c>
+      <c r="P57" s="63" t="n">
+        <v>46287</v>
       </c>
       <c r="Q57" s="62" t="s">
         <v>71</v>
@@ -25111,8 +25159,8 @@
       <c r="G58" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="H58" s="62" t="s">
-        <v>532</v>
+      <c r="H58" s="62" t="str">
+        <v>In Progress</v>
       </c>
       <c r="I58" s="62" t="s">
         <v>836</v>
@@ -25123,16 +25171,18 @@
       <c r="K58" s="62" t="s">
         <v>808</v>
       </c>
-      <c r="L58" s="62" t="s">
-        <v>997</v>
-      </c>
-      <c r="M58" s="62" t="s">
-        <v>970</v>
+      <c r="L58" s="62" t="str">
+        <v>Final policy and controls pending</v>
+      </c>
+      <c r="M58" s="62" t="str">
+        <v>Finalize policy, retention periods and applicable neutral-review arrangements; implement/test NCII controls. Active founder review: LEG-MT-027. PLAN.md §20.</v>
       </c>
       <c r="N58" s="63"/>
-      <c r="O58" s="62"/>
-      <c r="P58" s="63">
-        <v>46250.666666666664</v>
+      <c r="O58" s="62" t="str">
+        <v>Founder approval Sept 21, PLAN.md §20 Q96: human appeals, consent-based restoration and applicable neutral review at Pumdoki expense. Provider/controls pending.</v>
+      </c>
+      <c r="P58" s="63" t="n">
+        <v>46286</v>
       </c>
       <c r="Q58" s="62" t="s">
         <v>73</v>
@@ -25230,19 +25280,21 @@
       <c r="L60" s="62" t="s">
         <v>984</v>
       </c>
-      <c r="M60" s="62" t="s">
-        <v>970</v>
+      <c r="M60" s="62" t="str">
+        <v>Draft government-request handling using Q64 reporting/preservation boundaries. Define lawful disclosures, notices, emergency contacts, NCMEC setup and restricted evidence procedures before live use.</v>
       </c>
       <c r="N60" s="63"/>
-      <c r="O60" s="62"/>
-      <c r="P60" s="63">
-        <v>46250.666666666664</v>
+      <c r="O60" s="62" t="str">
+        <v>Founder approval Sept 21, PLAN.md §20 Q64; 18 USC 2258A/2702. Reporting direction recorded; full government-request policy remains undrafted.</v>
+      </c>
+      <c r="P60" s="63" t="n">
+        <v>46286</v>
       </c>
       <c r="Q60" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="R60" s="62" t="s">
-        <v>80</v>
+      <c r="R60" s="62" t="str">
+        <v>Q64: mandatory CyberTipline reports, urgent emergency escalation, lawful referrals/disclosures, secure preservation. Covered report material: one year; longer if required. Full policy/controls pending.</v>
       </c>
       <c r="S60" s="62" t="s">
         <v>1037</v>
@@ -25268,8 +25320,8 @@
       <c r="G61" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="H61" s="62" t="s">
-        <v>532</v>
+      <c r="H61" s="62" t="str">
+        <v>In Progress</v>
       </c>
       <c r="I61" s="62" t="s">
         <v>836</v>
@@ -25280,20 +25332,24 @@
       <c r="K61" s="62" t="s">
         <v>808</v>
       </c>
-      <c r="L61" s="62"/>
-      <c r="M61" s="62" t="s">
-        <v>970</v>
+      <c r="L61" s="62" t="str">
+        <v>Commissioned draft and substantive review pending</v>
+      </c>
+      <c r="M61" s="62" t="str">
+        <v>Review commissioned policy; implement/test appeals, notices, external review and financial corrections. Active founder review: LEG-MT-021. PLAN.md §20.</v>
       </c>
       <c r="N61" s="63"/>
-      <c r="O61" s="62"/>
-      <c r="P61" s="63">
-        <v>46250.666666666664</v>
+      <c r="O61" s="62" t="str">
+        <v>Q122 approved Sept 22; appeals questions reviewed. PLAN.md §20. Suzanne Lawyer bundle, Expense Tracker row 11; final policy and controls pending.</v>
+      </c>
+      <c r="P61" s="63" t="n">
+        <v>46287</v>
       </c>
       <c r="Q61" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="R61" s="62" t="s">
-        <v>83</v>
+      <c r="R61" s="62" t="str">
+        <v>Drafting commissioned in purchased bundle. Final review, applicable neutral-review arrangements and appeal controls pending before creator onboarding.</v>
       </c>
       <c r="S61" s="62" t="s">
         <v>1039</v>
@@ -25319,8 +25375,8 @@
       <c r="G62" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="H62" s="62" t="s">
-        <v>532</v>
+      <c r="H62" s="62" t="str">
+        <v>In Progress</v>
       </c>
       <c r="I62" s="62" t="s">
         <v>836</v>
@@ -25331,20 +25387,24 @@
       <c r="K62" s="62" t="s">
         <v>808</v>
       </c>
-      <c r="L62" s="62"/>
-      <c r="M62" s="62" t="s">
-        <v>970</v>
+      <c r="L62" s="62" t="str">
+        <v>Commissioned draft and substantive review pending</v>
+      </c>
+      <c r="M62" s="62" t="str">
+        <v>Review commissioned policy and implement/test intake, case tracking, deadlines and backup coverage. Active founder review: LEG-MT-031. PLAN.md §20.</v>
       </c>
       <c r="N62" s="63"/>
-      <c r="O62" s="62"/>
-      <c r="P62" s="63">
-        <v>46250.666666666664</v>
+      <c r="O62" s="62" t="str">
+        <v>Q114 approved Sept 22; complaint questions reviewed. PLAN.md §20. Complaints/appeals drafting in Suzanne Lawyer bundle (Expense Tracker row 11); delivery/approval pending.</v>
+      </c>
+      <c r="P62" s="63" t="n">
+        <v>46287</v>
       </c>
       <c r="Q62" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="R62" s="62" t="s">
-        <v>86</v>
+      <c r="R62" s="62" t="str">
+        <v>Q7 aliases created; routing/tests pending. Q16/Q98 backup and urgent coverage planned. Drafting purchased; final policy and 7-business-day/48-hour controls pending.</v>
       </c>
       <c r="S62" s="62" t="s">
         <v>1041</v>
@@ -25548,29 +25608,21 @@
           <t xml:space="preserve">Launch-country rules + provider/privacy review</t>
         </is>
       </c>
-      <c r="M66" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Define country triggers with LEG-MT-153; select a provider and retention rules. Then implement and test the age gate before live adult access.</t>
-        </is>
+      <c r="M66" s="62" t="str">
+        <v>Finalize location/risk triggers with LEG-MT-153 and provider/data handling with LEG-MT-155; implement/test required server-side checks before live adult access.</v>
       </c>
       <c r="N66" s="63"/>
-      <c r="O66" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://help.fansly.com/en/articles/11845000-global-age-verification-requirement</t>
-        </is>
-      </c>
-      <c r="P66" s="63">
-        <v>46275</v>
-      </c>
-      <c r="Q66" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jurisdiction-aware 18+ verification before restricted adult content: login/content-entry prompt, provider-hosted selfie/liveness check and ID fallback if required, persisted verified status, and retry/help states. Enforce required checks server-side. Keep this separate from content opt-in and creator identity/performer records.</t>
-        </is>
-      </c>
-      <c r="R66" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Registration records append-only age attestation and versioned Terms/Privacy acceptance; verified email gates creator-application submission. Entry-gate UI and actual identity/age verification remain pending. September 10: global flow added to scope; implementation not started. Fansly reference reviewed; its provider, country list, timing and retention claims are not adopted. Review actual coverage/data handling before live use.</t>
-        </is>
+      <c r="O66" s="62" t="str">
+        <v>PLAN.md §3.5/§20 Q20; founder approval Sept 13; https://help.fansly.com/en/articles/11845000-global-age-verification-requirement</v>
+      </c>
+      <c r="P66" s="63" t="n">
+        <v>46278</v>
+      </c>
+      <c r="Q66" s="62" t="str">
+        <v>18+ or higher legal minimum. Member checks follow jurisdiction/law, processor requirements and risk controls. Login/content-entry prompt; provider-hosted selfie/liveness and ID fallback if required; saved status and retry/help states. Enforce required checks server-side before adult access. Separate from content opt-in and creator identity/performer records.</v>
+      </c>
+      <c r="R66" s="62" t="str">
+        <v>Q20 approved. Age attestation and Terms/Privacy evidence exist; verified email gates creator applications. Required age checks cannot be replaced by attestation. Provider, country rules and verification setup/tests pending. Fansly details are not adopted.</v>
       </c>
       <c r="S66" s="62" t="s">
         <v>1115</v>
@@ -25664,19 +25716,21 @@
       <c r="L68" s="62" t="s">
         <v>1010</v>
       </c>
-      <c r="M68" s="62" t="s">
-        <v>970</v>
+      <c r="M68" s="62" t="str">
+        <v>Before pilot: confirm creator/member country lists, member cap, verification budget and cash buffer. Implement/test Q49 access restrictions. Creator tax forms: LEG-MT-021.</v>
       </c>
       <c r="N68" s="63"/>
-      <c r="O68" s="62"/>
-      <c r="P68" s="63">
-        <v>46250.666666666664</v>
+      <c r="O68" s="62" t="str">
+        <v>Founder approvals Sept 13 and 16. PLAN.md §3.6 and §20, Q9-10 and Q49. Published eligibility/age-check comparison sources linked there.</v>
+      </c>
+      <c r="P68" s="63" t="n">
+        <v>46281</v>
       </c>
       <c r="Q68" s="62" t="s">
         <v>660</v>
       </c>
-      <c r="R68" s="62" t="s">
-        <v>661</v>
+      <c r="R68" s="62" t="str">
+        <v>Q49 approved: broad international objective, separate creator/member eligibility, active restrictions and required age checks before adult access. Country lists, budgets, providers and controls pending.</v>
       </c>
       <c r="S68" s="62" t="s">
         <v>1346</v>
@@ -25770,19 +25824,21 @@
         <v>814</v>
       </c>
       <c r="L70" s="62"/>
-      <c r="M70" s="62" t="s">
-        <v>970</v>
+      <c r="M70" s="62" t="str">
+        <v>Compare Ondato/Veriff coverage, total pilot cost and privacy/retention terms; coordinate CCBill review requirements before selection.</v>
       </c>
       <c r="N70" s="63"/>
-      <c r="O70" s="62"/>
-      <c r="P70" s="63">
-        <v>46250.666666666664</v>
-      </c>
-      <c r="Q70" s="62" t="s">
-        <v>666</v>
-      </c>
-      <c r="R70" s="62" t="s">
-        <v>667</v>
+      <c r="O70" s="62" t="str">
+        <v>Founder approval in chat, Sept 13; PLAN.md §3.5 and §20, Question 12.</v>
+      </c>
+      <c r="P70" s="63" t="n">
+        <v>46278</v>
+      </c>
+      <c r="Q70" s="62" t="str">
+        <v>Compare automated member age assurance and creator identity/age verification providers; preserve replaceable integration.</v>
+      </c>
+      <c r="R70" s="62" t="str">
+        <v>Sept 13: Ondato/Veriff candidates; no provider selected. Automated flows planned; configure/test before live adult access or real creator identity onboarding. No purchase or fixed CCBill deadline approved.</v>
       </c>
       <c r="S70" s="62" t="s">
         <v>1351</v>
@@ -25808,8 +25864,8 @@
       <c r="G71" s="62" t="s">
         <v>1357</v>
       </c>
-      <c r="H71" s="62" t="s">
-        <v>529</v>
+      <c r="H71" t="str" s="62">
+        <v>Done</v>
       </c>
       <c r="I71" s="62" t="s">
         <v>836</v>
@@ -25820,22 +25876,22 @@
       <c r="K71" s="62" t="s">
         <v>808</v>
       </c>
-      <c r="L71" s="62" t="s">
-        <v>1358</v>
-      </c>
-      <c r="M71" s="62" t="s">
-        <v>1359</v>
+      <c r="L71" s="62"/>
+      <c r="M71" t="str" s="62">
+        <v>Retain state approval and IRS confirmation privately. Banking and DBA registration remain separate follow-ups.</v>
       </c>
       <c r="N71" s="63"/>
-      <c r="O71" s="62"/>
-      <c r="P71" s="63">
-        <v>46273.666666666664</v>
-      </c>
-      <c r="Q71" s="62" t="s">
-        <v>1360</v>
-      </c>
-      <c r="R71" s="62" t="s">
-        <v>1361</v>
+      <c r="O71" t="str" s="62">
+        <v>Founder confirmed Maryland approval and supplied the issued EIN in chat on September 16, 2026. PLAN.md section 20.</v>
+      </c>
+      <c r="P71" t="n" s="63">
+        <v>46281</v>
+      </c>
+      <c r="Q71" t="str" s="62">
+        <v>Kiban Digital Holdings LLC: Maryland formation approved and EIN obtained, confirmed by the founder September 16, 2026.</v>
+      </c>
+      <c r="R71" t="str" s="62">
+        <v>Filed through Northwest. Founder confirmed approval and EIN receipt Sept 16. Original state/IRS documents not independently inspected; EIN held outside Git. Banking/DBA remain open.</v>
       </c>
       <c r="S71" s="62" t="s">
         <v>1362</v>
@@ -26667,8 +26723,8 @@
       <c r="F87" s="62" t="s">
         <v>1069</v>
       </c>
-      <c r="G87" s="62" t="s">
-        <v>111</v>
+      <c r="G87" s="62" t="str">
+        <v>Define Founders recognition and benefits</v>
       </c>
       <c r="H87" s="62" t="s">
         <v>532</v>
@@ -26683,19 +26739,21 @@
         <v>814</v>
       </c>
       <c r="L87" s="62"/>
-      <c r="M87" s="62" t="s">
-        <v>1070</v>
+      <c r="M87" s="62" t="str">
+        <v>Define eligibility and duration after Q133. Plan Founders tag, Connect filter or Explore section, SFW Discord events and future event priority.</v>
       </c>
       <c r="N87" s="63"/>
-      <c r="O87" s="62"/>
-      <c r="P87" s="63">
-        <v>46271.666666666664</v>
-      </c>
-      <c r="Q87" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="R87" s="62" t="s">
-        <v>1071</v>
+      <c r="O87" s="62" t="str">
+        <v>Q132 approved Sept 22. PLAN.md §20 supersedes commission-free/cost-recovery terms; Q133 pending.</v>
+      </c>
+      <c r="P87" s="63" t="n">
+        <v>46287</v>
+      </c>
+      <c r="Q87" s="62" t="str">
+        <v>Founders tag; Connect filter or Explore section below top sections; SFW Discord events; future event priority. No special commission.</v>
+      </c>
+      <c r="R87" s="62" t="str">
+        <v>No fixed cohort, permanent ranking, member discount or Plus promise. Cash prizes optional and separately budgeted. Implementation not started.</v>
       </c>
       <c r="S87" s="62" t="s">
         <v>1072</v>
@@ -26838,21 +26896,21 @@
       <c r="L90" s="62" t="s">
         <v>997</v>
       </c>
-      <c r="M90" s="62" t="s">
-        <v>1206</v>
+      <c r="M90" s="62" t="str">
+        <v>Continue the functioning review site. Return to CCBill when review-ready; confirm direct-payment terms before integration. Wallet assessment/build are future work. PLAN.md §20.</v>
       </c>
       <c r="N90" s="63"/>
-      <c r="O90" s="62" t="s">
-        <v>1207</v>
-      </c>
-      <c r="P90" s="63">
-        <v>46275.666666666664</v>
+      <c r="O90" s="62" t="str">
+        <v>Initial CCBill inquiry record; Sept 13 final wallet deferral; PLAN.md Phase 6/§20 and HANDOFF.md.</v>
+      </c>
+      <c r="P90" s="63" t="n">
+        <v>46278</v>
       </c>
       <c r="Q90" s="62" t="s">
         <v>1208</v>
       </c>
-      <c r="R90" s="62" t="s">
-        <v>1209</v>
+      <c r="R90" s="62" t="str">
+        <v>Sales replied; functioning site required. Founder deferred wallets to future and resumed questionnaire. Candidate preserved; no active wallet assessment/build. Provider approval and payment backend pending.</v>
       </c>
       <c r="S90" s="62" t="s">
         <v>1210</v>
@@ -26999,19 +27057,21 @@
       <c r="L93" s="62" t="s">
         <v>997</v>
       </c>
-      <c r="M93" s="62" t="s">
-        <v>1220</v>
+      <c r="M93" s="62" t="str">
+        <v>Confirm processor-supported billing/cancellation flow, cutoff and account setup; implement trusted events and test cancellation, expiry and confirmation. PLAN.md §20 Q23.</v>
       </c>
       <c r="N93" s="63"/>
-      <c r="O93" s="62"/>
-      <c r="P93" s="63">
-        <v>46275.666666666664</v>
+      <c r="O93" s="62" t="str">
+        <v>Founder approval Sept 13; PLAN.md §20 Q23 and cited Fansly/CCBill sources.</v>
+      </c>
+      <c r="P93" s="63" t="n">
+        <v>46278</v>
       </c>
       <c r="Q93" s="62" t="s">
         <v>227</v>
       </c>
-      <c r="R93" s="62" t="s">
-        <v>1221</v>
+      <c r="R93" s="62" t="str">
+        <v>CCBill review-site preparation underway. Q23 cancellation approved: paid-term access, refund exceptions and confirmation. Cutoff unconfirmed; recurring billing, webhooks and cancellation remain unimplemented.</v>
       </c>
       <c r="S93" s="62" t="s">
         <v>1222</v>
@@ -27101,19 +27161,21 @@
         <v>814</v>
       </c>
       <c r="L95" s="62"/>
-      <c r="M95" s="62" t="s">
-        <v>970</v>
+      <c r="M95" s="62" t="str">
+        <v>Confirm processor retry/expiry semantics; implement trusted paid-through access and recovery after payment. Test that failure does not revoke other purchases. PLAN.md §20 Q25.</v>
       </c>
       <c r="N95" s="63"/>
-      <c r="O95" s="62"/>
-      <c r="P95" s="63">
-        <v>46250.666666666664</v>
+      <c r="O95" s="62" t="str">
+        <v>Founder approval Sept 13; PLAN.md §20 Q25 and cited CCBill event documentation.</v>
+      </c>
+      <c r="P95" s="63" t="n">
+        <v>46278</v>
       </c>
       <c r="Q95" s="62" t="s">
         <v>232</v>
       </c>
-      <c r="R95" s="62" t="s">
-        <v>233</v>
+      <c r="R95" s="62" t="str">
+        <v>Q25 approved: no automatic unpaid pilot grace. Retain paid access; pause affected subscription at expiry until payment confirmed. No whole-account suspension or loss of other purchases. Retry/status details pending.</v>
       </c>
       <c r="S95" s="62" t="s">
         <v>1226</v>
@@ -27207,19 +27269,21 @@
       <c r="L97" s="62" t="s">
         <v>997</v>
       </c>
-      <c r="M97" s="62" t="s">
-        <v>970</v>
+      <c r="M97" s="62" t="str">
+        <v>Validate Q131 20/80 target against actual provider and operating costs. Founders use standard commission. Final commercial terms pending.</v>
       </c>
       <c r="N97" s="63"/>
-      <c r="O97" s="62"/>
-      <c r="P97" s="63">
-        <v>46250.666666666664</v>
-      </c>
-      <c r="Q97" s="62" t="s">
-        <v>238</v>
-      </c>
-      <c r="R97" s="62" t="s">
-        <v>623</v>
+      <c r="O97" s="62" t="str">
+        <v>Q131–132 approved Sept 22. PLAN.md §3.8 and §20. No provider quote or live payment approval.</v>
+      </c>
+      <c r="P97" s="63" t="n">
+        <v>46287</v>
+      </c>
+      <c r="Q97" s="62" t="str">
+        <v>20% platform / 80% creator target excluding sales tax/VAT; ordinary processing costs from platform share. Same commission for Founders.</v>
+      </c>
+      <c r="R97" s="62" t="str">
+        <v>Validate sustainability before a firm offer or live payments. Refund/chargeback allocation, payout fees and paid-session commission pending.</v>
       </c>
       <c r="S97" s="62" t="s">
         <v>1230</v>
@@ -27260,19 +27324,21 @@
       <c r="L98" s="62" t="s">
         <v>997</v>
       </c>
-      <c r="M98" s="62" t="s">
-        <v>1232</v>
+      <c r="M98" s="62" t="str">
+        <v>Review Q28 with counsel/processor; define trusted dispute events, then implement and test transaction access, proportionate restrictions, authorized operations and audit. PLAN.md §20.</v>
       </c>
       <c r="N98" s="63"/>
-      <c r="O98" s="62"/>
-      <c r="P98" s="63">
-        <v>46275.666666666664</v>
+      <c r="O98" s="62" t="str">
+        <v>Founder approval Sept 14, 2026; PLAN.md §20 Q28; CFPB dispute guidance and Fansly/LoyalFans policy references recorded there.</v>
+      </c>
+      <c r="P98" s="63" t="n">
+        <v>46279</v>
       </c>
       <c r="Q98" s="62" t="s">
         <v>240</v>
       </c>
-      <c r="R98" s="62" t="s">
-        <v>1233</v>
+      <c r="R98" s="62" t="str">
+        <v>Q28: review disputed access; keep unrelated valid purchases. No penalty solely for good-faith disputes. Broader restrictions need justification. Legal/processor review, integration and handling pending.</v>
       </c>
       <c r="S98" s="62" t="s">
         <v>1234</v>
@@ -27362,19 +27428,21 @@
         <v>814</v>
       </c>
       <c r="L100" s="62"/>
-      <c r="M100" s="62" t="s">
-        <v>1322</v>
+      <c r="M100" s="62" t="str">
+        <v>Confirm processor terms; implement hosted checkout, verified payment, retained purchased versions and buyer access after creator delisting. Test required removals separately. PLAN.md §20 Q26.</v>
       </c>
       <c r="N100" s="63"/>
-      <c r="O100" s="62"/>
-      <c r="P100" s="63">
-        <v>46274.666666666664</v>
-      </c>
-      <c r="Q100" s="62" t="s">
-        <v>1323</v>
-      </c>
-      <c r="R100" s="62" t="s">
-        <v>1324</v>
+      <c r="O100" s="62" t="str">
+        <v>Founder approval Sept 13; PLAN.md §20 Q26 and cited Fansly sold-media guidance.</v>
+      </c>
+      <c r="P100" s="63" t="n">
+        <v>46278</v>
+      </c>
+      <c r="Q100" s="62" t="str">
+        <v>One-off hosted checkout for individual photos/videos or bundles; verified payment grants ongoing access to the purchased version. Ordinary creator delisting preserves buyer access.</v>
+      </c>
+      <c r="R100" s="62" t="str">
+        <v>Q26 approved: no scheduled purchase expiry. Retain media and buyer grants after ordinary delisting; legal/safety removals and Terms/Refund Policy still apply. Processor approval and paid flow remain pending.</v>
       </c>
       <c r="S100" s="62" t="s">
         <v>1325</v>
@@ -27415,19 +27483,21 @@
       <c r="L101" s="62" t="s">
         <v>997</v>
       </c>
-      <c r="M101" s="62" t="s">
-        <v>970</v>
+      <c r="M101" s="62" t="str">
+        <v>Model actual processing, taxes, refunds, chargebacks, payout timing and operating costs against Q131. Include optional Founders event budgets.</v>
       </c>
       <c r="N101" s="63"/>
-      <c r="O101" s="62"/>
-      <c r="P101" s="63">
-        <v>46250.666666666664</v>
-      </c>
-      <c r="Q101" s="62" t="s">
-        <v>678</v>
-      </c>
-      <c r="R101" s="62" t="s">
-        <v>679</v>
+      <c r="O101" s="62" t="str">
+        <v>Q131/Q132 approved. See PLAN.md section 20.</v>
+      </c>
+      <c r="P101" s="63" t="n">
+        <v>46287</v>
+      </c>
+      <c r="Q101" s="62" t="str">
+        <v>Validate standard commission and payout economics, including programme costs. No Founders discount or commission exemption.</v>
+      </c>
+      <c r="R101" s="62" t="str">
+        <v>20/80 is an approved target, not proven profitability. Prize amounts and recurring event spend are not approved.</v>
       </c>
       <c r="S101" s="62" t="s">
         <v>1364</v>
@@ -28753,8 +28823,8 @@
       <c r="F127" s="62" t="s">
         <v>1202</v>
       </c>
-      <c r="G127" s="62" t="s">
-        <v>262</v>
+      <c r="G127" s="62" t="str">
+        <v>Build Founders admin management</v>
       </c>
       <c r="H127" s="62" t="s">
         <v>532</v>
@@ -28771,19 +28841,19 @@
       <c r="L127" s="62" t="s">
         <v>1203</v>
       </c>
-      <c r="M127" s="62" t="s">
-        <v>970</v>
+      <c r="M127" s="62" t="str">
+        <v>After Q133 terms and private-operations gates, implement Founders eligibility and badge management. No fixed cohort cap assumed.</v>
       </c>
       <c r="N127" s="63"/>
       <c r="O127" s="62"/>
-      <c r="P127" s="63">
-        <v>46250.666666666664</v>
-      </c>
-      <c r="Q127" s="62" t="s">
-        <v>263</v>
-      </c>
-      <c r="R127" s="62" t="s">
-        <v>264</v>
+      <c r="P127" s="63" t="n">
+        <v>46287</v>
+      </c>
+      <c r="Q127" s="62" t="str">
+        <v>Manage Founders eligibility and badge assignment. Enforce a cohort limit only if approved.</v>
+      </c>
+      <c r="R127" s="62" t="str">
+        <v>Q132 programme direction approved; Q133 eligibility/duration pending. No member discount or separate Founders rate.</v>
       </c>
       <c r="S127" s="62" t="s">
         <v>1260</v>
@@ -28829,11 +28899,11 @@
       </c>
       <c r="N128" s="63"/>
       <c r="O128" s="62"/>
-      <c r="P128" s="63">
-        <v>46250.666666666664</v>
-      </c>
-      <c r="Q128" s="62" t="s">
-        <v>266</v>
+      <c r="P128" s="63" t="n">
+        <v>46287</v>
+      </c>
+      <c r="Q128" s="62" t="str">
+        <v>Configure standard commission, content/feature flags, payout minimums and maintenance. No separate Founders commission setting.</v>
       </c>
       <c r="R128" s="62" t="s">
         <v>267</v>
@@ -29456,19 +29526,21 @@
         <v>814</v>
       </c>
       <c r="L140" s="62"/>
-      <c r="M140" s="62" t="s">
-        <v>970</v>
+      <c r="M140" s="62" t="str">
+        <v>Configure email intake, receipts, urgent alerts and deadline tracking; arrange backup coverage and test before live use. PLAN.md §20, Q16.</v>
       </c>
       <c r="N140" s="63"/>
-      <c r="O140" s="62"/>
-      <c r="P140" s="63">
-        <v>46250.666666666664</v>
+      <c r="O140" s="62" t="str">
+        <v>Founder confirmation in chat, Sept 13; PLAN.md §20, Question 16.</v>
+      </c>
+      <c r="P140" s="63" t="n">
+        <v>46278</v>
       </c>
       <c r="Q140" s="62" t="s">
         <v>280</v>
       </c>
-      <c r="R140" s="62" t="s">
-        <v>281</v>
+      <c r="R140" s="62" t="str">
+        <v>Q16: founder email support; daily urgent checks including weekends; delegate when unavailable. No backup assigned. Routine human reply target: 2 business days. Complaint/NCII deadlines: PLAN.md §20.</v>
       </c>
       <c r="S140" s="62" t="s">
         <v>1272</v>
@@ -30180,19 +30252,21 @@
         <v>814</v>
       </c>
       <c r="L154" s="62"/>
-      <c r="M154" s="62" t="s">
-        <v>970</v>
+      <c r="M154" s="62" t="str">
+        <v>Define and verify limited-pilot readiness criteria alongside functional slices: processor approval plus product, legal, safety, security and support checks.</v>
       </c>
       <c r="N154" s="63"/>
-      <c r="O154" s="62"/>
-      <c r="P154" s="63">
-        <v>46250.666666666664</v>
+      <c r="O154" s="62" t="str">
+        <v>Founder approval, Sept 13; PLAN.md §20 Q18; docs/product/initial-ccbill-inquiry.md.</v>
+      </c>
+      <c r="P154" s="63" t="n">
+        <v>46278</v>
       </c>
       <c r="Q154" s="62" t="s">
         <v>322</v>
       </c>
-      <c r="R154" s="62" t="s">
-        <v>323</v>
+      <c r="R154" s="62" t="str">
+        <v>Q18 approved: no fixed date or confirmed underwriting duration. Limited member pilot after approval/checks; expansion depends on results, country coverage and capacity. Checklist remains incomplete.</v>
       </c>
       <c r="S154" s="62" t="s">
         <v>1311</v>

--- a/docs/product/Pumdoki_MasterTracker_V4.xlsx
+++ b/docs/product/Pumdoki_MasterTracker_V4.xlsx
@@ -11210,10 +11210,10 @@
         <v>Q131 approves a 20/80 target excluding sales tax; processing costs from platform share. Q132 applies standard fees to Founders, replacing cost-recovery terms.</v>
       </c>
       <c r="H14" s="62" t="str">
-        <v>Validate actual costs before firm pricing/live payments. Refund/chargeback allocation and payout fees pending. Budget prize events separately.</v>
+        <v>Validate actual costs under Q139–141 loss/fee rules. Provider payout fees remain unconfirmed. Budget prize events separately.</v>
       </c>
       <c r="I14" s="62" t="str">
-        <v>PLAN.md §3.8 and §20, Q131–132 approved September 22, 2026.</v>
+        <v>PLAN.md §§3.8,20: Q131–132 and Q139–141 approved September 22, 2026.</v>
       </c>
       <c r="J14" s="63" t="n">
         <v>46287</v>
@@ -11484,10 +11484,10 @@
         <v>Q132: Founders tag; Connect filter or Explore section below top sections; SFW Discord events; future event priority. Standard fees replace commission exemption.</v>
       </c>
       <c r="H23" s="69" t="str">
-        <v>Q133: define eligibility, cutoff/cap and duration. Specify placements and event terms; cash prizes optional, separately funded. No sales/ranking guarantee.</v>
+        <v>Q133: tag lasts for eligible account life; discovery/event priority conditional. Finalize eligibility, cutoff/cap and event terms; fund prizes separately.</v>
       </c>
       <c r="I23" s="69" t="str">
-        <v>PLAN.md §20, Q132 approved September 22, 2026; Q133 pending.</v>
+        <v>PLAN.md §20, Q132–133 approved September 22, 2026; eligibility and event details remain open.</v>
       </c>
       <c r="J23" s="70" t="n">
         <v>46287</v>
@@ -12834,7 +12834,7 @@
         <v>🔄 In Progress</v>
       </c>
       <c r="D21" s="8" t="str">
-        <v>Q132 approved: Founders benefits replace fee exemption. Review Q133 duration and eligibility. PLAN.md §20.</v>
+        <v>Final questionnaire corrections confirmed by founder. Await Suzanne response and drafts; provider/legal review pending. PLAN §20.</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
@@ -13140,7 +13140,7 @@
         <v>21</v>
       </c>
       <c r="D43" s="11" t="str">
-        <v>Q132 approved Sept 22. Standard fees; no 500-person cap, member discount or permanent fee exemption. Q133 pending.</v>
+        <v>Q132–133 approved: Founders tag lasts for eligible account life. Benefits conditional; eligibility/cap pending. Standard fees.</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="27.75" customHeight="1">
@@ -13899,8 +13899,8 @@
       <c r="C100" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D100" s="8" t="s">
-        <v>236</v>
+      <c r="D100" s="8" t="str">
+        <v>Q147: final settlement without automatic forfeiture. Confirm provider limits and checks before live use. PLAN §20.</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1">
@@ -13934,7 +13934,7 @@
         <v>21</v>
       </c>
       <c r="D103" s="11" t="str">
-        <v>Q28 approved: proportionate dispute handling; protect good-faith disputes. Review/build/tests pending. PLAN.md §20.</v>
+        <v>Q139: reverse shares; protect earned pay for platform errors. Q28 safeguards. Build/review pending. PLAN §20.</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="27.75" customHeight="1">
@@ -14088,7 +14088,7 @@
         <v>21</v>
       </c>
       <c r="D115" s="11" t="str">
-        <v>Programme direction approved Q132; eligibility, cap and duration pending Q133. No implementation yet.</v>
+        <v>Q133: lasting eligible-account tag; conditional benefits. Eligibility/cap and implementation pending.</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1">
@@ -24852,17 +24852,17 @@
         <v>808</v>
       </c>
       <c r="L52" s="62" t="str">
-        <v>Founder questionnaire review; commissioned draft pending</v>
+        <v>Suzanne response and commissioned drafts</v>
       </c>
       <c r="M52" s="62" t="str">
-        <v>Review Q133 Founders duration and eligibility. Q132 benefits approved; exact placements and event/prize terms pending. PLAN.md §20.</v>
+        <v>Review Suzanne response and drafts when received. Resolve flagged legal/provider points before final approval. PLAN §20.</v>
       </c>
       <c r="N52" s="63"/>
       <c r="O52" s="62" t="str">
-        <v>Q132 approved Sept 22; Q133 pending. PLAN.md §20. Suzanne Lawyer bundle, Expense Tracker row 11; commissioned terms pending.</v>
+        <v>Founder confirmed final questionnaire corrections; awaiting Suzanne Sept 23. Expense Tracker row 11 paid bundle; legal approval pending.</v>
       </c>
       <c r="P52" s="63" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="Q52" s="62" t="s">
         <v>55</v>
@@ -26740,11 +26740,11 @@
       </c>
       <c r="L87" s="62"/>
       <c r="M87" s="62" t="str">
-        <v>Define eligibility and duration after Q133. Plan Founders tag, Connect filter or Explore section, SFW Discord events and future event priority.</v>
+        <v>Finalize eligibility and enrollment cutoff/cap. Implement Q133 account-lifetime tag and conditional discovery/events; prize budgets remain separate.</v>
       </c>
       <c r="N87" s="63"/>
       <c r="O87" s="62" t="str">
-        <v>Q132 approved Sept 22. PLAN.md §20 supersedes commission-free/cost-recovery terms; Q133 pending.</v>
+        <v>Q132/Q133 approved Sept 22. PLAN.md section 20. Eligibility and event details pending.</v>
       </c>
       <c r="P87" s="63" t="n">
         <v>46287</v>
@@ -26753,7 +26753,7 @@
         <v>Founders tag; Connect filter or Explore section below top sections; SFW Discord events; future event priority. No special commission.</v>
       </c>
       <c r="R87" s="62" t="str">
-        <v>No fixed cohort, permanent ranking, member discount or Plus promise. Cash prizes optional and separately budgeted. Implementation not started.</v>
+        <v>Q133 approved: eligible account-lifetime tag; discovery/events follow terms and availability. No permanent ranking or recurring prizes. Build pending.</v>
       </c>
       <c r="S87" s="62" t="s">
         <v>1072</v>
@@ -27216,19 +27216,21 @@
       <c r="L96" s="62" t="s">
         <v>1010</v>
       </c>
-      <c r="M96" s="62" t="s">
-        <v>970</v>
+      <c r="M96" s="62" t="str">
+        <v>Design payout flow under Q134–147: eligibility, holds, fees and final settlement, including below-minimum balances. Confirm providers.</v>
       </c>
       <c r="N96" s="63"/>
-      <c r="O96" s="62"/>
-      <c r="P96" s="63">
-        <v>46250.666666666664</v>
+      <c r="O96" s="62" t="str">
+        <v>Q147 approved Sept 22, 2026. PLAN §§3.8,20; earlier payout policies retained. Provider details and implementation pending.</v>
+      </c>
+      <c r="P96" s="63" t="n">
+        <v>46287</v>
       </c>
       <c r="Q96" s="62" t="s">
         <v>235</v>
       </c>
-      <c r="R96" s="62" t="s">
-        <v>236</v>
+      <c r="R96" s="62" t="str">
+        <v>Approved policy only. Preserve payable balances after closure; final methods, fees and below-minimum resolution need legal/provider review.</v>
       </c>
       <c r="S96" s="62" t="s">
         <v>1228</v>
@@ -27325,14 +27327,14 @@
         <v>997</v>
       </c>
       <c r="M98" s="62" t="str">
-        <v>Review Q28 with counsel/processor; define trusted dispute events, then implement and test transaction access, proportionate restrictions, authorized operations and audit. PLAN.md §20.</v>
+        <v>Implement Q28/Q139 after legal/provider review: verified events, share reversals, platform-error protection, recovery, appeals and audit.</v>
       </c>
       <c r="N98" s="63"/>
       <c r="O98" s="62" t="str">
-        <v>Founder approval Sept 14, 2026; PLAN.md §20 Q28; CFPB dispute guidance and Fansly/LoyalFans policy references recorded there.</v>
+        <v>Q28 approved Sept 14; Q139 approved Sept 22, 2026. PLAN §20. Provider review and build/tests pending.</v>
       </c>
       <c r="P98" s="63" t="n">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="Q98" s="62" t="s">
         <v>240</v>
@@ -27484,11 +27486,11 @@
         <v>997</v>
       </c>
       <c r="M101" s="62" t="str">
-        <v>Model actual processing, taxes, refunds, chargebacks, payout timing and operating costs against Q131. Include optional Founders event budgets.</v>
+        <v>Model Q131 and Q139–141 allocations using actual provider costs, including failed recoveries and optional Founders event budgets.</v>
       </c>
       <c r="N101" s="63"/>
       <c r="O101" s="62" t="str">
-        <v>Q131/Q132 approved. See PLAN.md section 20.</v>
+        <v>Q131/Q132/Q139–141 approved Sept 22, 2026. Actual provider fees and cost validation remain pending. PLAN §§3.8,20.</v>
       </c>
       <c r="P101" s="63" t="n">
         <v>46287</v>
@@ -28842,7 +28844,7 @@
         <v>1203</v>
       </c>
       <c r="M127" s="62" t="str">
-        <v>After Q133 terms and private-operations gates, implement Founders eligibility and badge management. No fixed cohort cap assumed.</v>
+        <v>After cohort rules and private-operations gates, implement Q133 Founders eligibility and account-lifetime tag management. No fixed cap assumed.</v>
       </c>
       <c r="N127" s="63"/>
       <c r="O127" s="62"/>
@@ -28853,7 +28855,7 @@
         <v>Manage Founders eligibility and badge assignment. Enforce a cohort limit only if approved.</v>
       </c>
       <c r="R127" s="62" t="str">
-        <v>Q132 programme direction approved; Q133 eligibility/duration pending. No member discount or separate Founders rate.</v>
+        <v>Q132–133 approved: tag lasts for eligible account life; conditional benefits. Eligibility/cap pending. No member discount or special rate.</v>
       </c>
       <c r="S127" s="62" t="s">
         <v>1260</v>
